--- a/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785157337</t>
+          <t>1785189317</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,27 +635,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -663,11 +659,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Besiktas</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -675,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785154148</t>
+          <t>1785188885</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +739,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,12 +754,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.36789</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -777,7 +769,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -787,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785186773</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>9.866208</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,12 +851,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,12 +866,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -889,7 +881,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785186621</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +963,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,22 +978,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>65.95</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1011,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1048,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785131538</t>
+          <t>1785186464</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>177.643098</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,110 +1075,1102 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1785186313</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1785185868</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.2662</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1785182082</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>101.408451</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>98.9699</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.9187</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19577588</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1785178276</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1785438000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>107.72234</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1785157337</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1785154148</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.36789</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>9.866208</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>65.95</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.3713</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1785131538</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>177.643098</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>0x4a21e608f2a49d0d290d56e481810827c36c3a33b3cdfa52f47a9d205c9195a6</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>1.1213</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>SL Benfica FC</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>FC St. Gallen</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>0xfc195ce6529fc46edc42b440639cd20958bc0e5f58d88c7925cdd8563a01ebd2</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>L19577588</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>1785123830</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>1785438000</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>65.979381</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
+          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785189317</t>
+          <t>1785218406</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +643,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
+          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>85.47</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -667,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785188885</t>
+          <t>1785213181</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>254.185874</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,27 +747,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
+          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -767,11 +771,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -779,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785186773</t>
+          <t>1785189317</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,27 +851,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
+          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -879,11 +875,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -891,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785186621</t>
+          <t>1785188885</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +955,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1048,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785186464</t>
+          <t>1785186773</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1075,7 +1067,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1160,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785186313</t>
+          <t>1785186621</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1187,7 +1179,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1272,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785185868</t>
+          <t>1785186464</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1299,31 +1291,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785182082</t>
+          <t>1785186313</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>101.408451</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,12 +1403,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>98.9699</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.9187</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1443,27 +1443,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785178276</t>
+          <t>1785185868</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>107.72234</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,28 +1515,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1547,27 +1547,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785157337</t>
+          <t>1785182082</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>101.408451</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>98.9699</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.9187</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1659,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785154148</t>
+          <t>1785178276</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>107.72234</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,27 +1731,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.36789</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1759,34 +1755,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Besiktas</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>FC Midtjylland vs Besiktas</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Besiktas</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1816,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785157337</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1826,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>9.866208</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,7 +1835,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1928,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785154148</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1955,12 +1947,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1970,22 +1962,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>65.95</t>
+          <t>2.36789</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1995,27 +1987,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2040,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785131538</t>
+          <t>1785153790</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2050,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>177.643098</t>
+          <t>9.866208</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2067,110 +2059,334 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>65.95</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.3713</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1785131538</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>177.643098</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>0x4a21e608f2a49d0d290d56e481810827c36c3a33b3cdfa52f47a9d205c9195a6</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>1.1213</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>SL Benfica FC</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>FC St. Gallen</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>0xfc195ce6529fc46edc42b440639cd20958bc0e5f58d88c7925cdd8563a01ebd2</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>L19577588</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>1785123830</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>1785438000</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>65.979381</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
+          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>142.02999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.6663</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785218406</t>
+          <t>1785232812</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>213.178221</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,23 +643,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
+          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>193.23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -667,7 +671,11 @@
           <t>Europa League</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -690,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785213181</t>
+          <t>1785231712</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>254.185874</t>
+          <t>285.737523</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,23 +755,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
+          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -824,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785189317</t>
+          <t>1785227020</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>20.185185</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,31 +859,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
+          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>104.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -883,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785188885</t>
+          <t>1785224116</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>155.925373</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,12 +971,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
+          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -970,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -995,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785186773</t>
+          <t>1785223916</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>144.089552</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,27 +1083,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
+          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>70.47999</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1095,11 +1107,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1107,27 +1115,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,17 +1160,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785186621</t>
+          <t>1785220497</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>133.295489</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,7 +1187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1264,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785186464</t>
+          <t>1785218406</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1291,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1299,31 +1307,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>85.47</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1331,27 +1331,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785186313</t>
+          <t>1785213181</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>254.185874</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,27 +1403,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1431,11 +1427,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1443,27 +1435,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1488,17 +1480,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785185868</t>
+          <t>1785189317</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,28 +1507,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1547,27 +1539,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1592,17 +1584,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785182082</t>
+          <t>1785188885</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>101.408451</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,12 +1611,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1634,22 +1626,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>98.9699</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.9187</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1659,27 +1651,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,17 +1696,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785178276</t>
+          <t>1785186773</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>107.72234</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,7 +1723,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1739,15 +1731,19 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1755,7 +1751,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1763,27 +1763,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785157337</t>
+          <t>1785186621</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1875,27 +1875,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1920,17 +1920,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785154148</t>
+          <t>1785186464</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,12 +1947,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.36789</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2032,17 +2032,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785186313</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>9.866208</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2099,27 +2099,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2144,17 +2144,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785185868</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,39 +2171,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>65.95</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2211,27 +2203,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2256,17 +2248,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785131538</t>
+          <t>1785182082</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>177.643098</t>
+          <t>101.408451</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,110 +2275,774 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>98.9699</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.9187</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19577588</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1785178276</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1785438000</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>107.72234</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1785157337</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1785154148</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.36789</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>9.866208</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>65.95</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.3713</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1785131538</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>177.643098</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>0x4a21e608f2a49d0d290d56e481810827c36c3a33b3cdfa52f47a9d205c9195a6</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>1.1213</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>SL Benfica FC</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>FC St. Gallen</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>0xfc195ce6529fc46edc42b440639cd20958bc0e5f58d88c7925cdd8563a01ebd2</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>L19577588</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>1785123830</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>1785438000</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>65.979381</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
+          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>142.02999</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.6663</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785232812</t>
+          <t>1785253987</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>213.178221</t>
+          <t>15.737226</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
+          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,12 +650,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>193.23</t>
+          <t>142.02999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.6663</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -728,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785231712</t>
+          <t>1785232812</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>285.737523</t>
+          <t>213.178221</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,31 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
+          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>193.23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -787,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785227020</t>
+          <t>1785231712</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20.185185</t>
+          <t>285.737523</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,39 +859,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
+          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>104.47</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -899,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785224116</t>
+          <t>1785227020</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>155.925373</t>
+          <t>20.185185</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
+          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -986,7 +978,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>104.47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1056,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785223916</t>
+          <t>1785224116</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>144.089552</t>
+          <t>155.925373</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,31 +1075,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
+          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>70.47999</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1115,27 +1115,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785220497</t>
+          <t>1785223916</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>133.295489</t>
+          <t>144.089552</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,27 +1187,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
+          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>70.47999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1215,11 +1211,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1227,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1272,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785218406</t>
+          <t>1785220497</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>133.295489</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,7 +1291,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
+          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1307,23 +1299,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1331,27 +1331,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785213181</t>
+          <t>1785218406</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>254.185874</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,28 +1403,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
+          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>85.47</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1435,27 +1435,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785189317</t>
+          <t>1785213181</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>254.185874</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,7 +1507,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
+          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785188885</t>
+          <t>1785189317</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1611,27 +1611,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
+          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1639,11 +1635,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1651,27 +1643,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1696,17 +1688,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785186773</t>
+          <t>1785188885</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,7 +1715,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
+          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1808,7 +1800,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785186621</t>
+          <t>1785186773</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1835,7 +1827,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1920,7 +1912,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785186464</t>
+          <t>1785186621</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1947,7 +1939,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2032,7 +2024,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785186313</t>
+          <t>1785186464</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2059,7 +2051,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2144,7 +2136,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785185868</t>
+          <t>1785186313</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2171,31 +2163,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785182082</t>
+          <t>1785185868</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>101.408451</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2275,39 +2275,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>98.9699</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.9187</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SL Benfica FC</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2315,27 +2307,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2360,17 +2352,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785178276</t>
+          <t>1785182082</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>107.72234</t>
+          <t>101.408451</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2387,31 +2379,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>98.9699</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.9187</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2419,27 +2419,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2464,17 +2464,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785157337</t>
+          <t>1785178276</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>107.72234</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2491,27 +2491,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2519,34 +2515,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Besiktas</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>FC Midtjylland vs Besiktas</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Besiktas</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2576,7 +2568,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785154148</t>
+          <t>1785157337</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2586,7 +2578,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2603,12 +2595,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2618,7 +2610,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.36789</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2688,7 +2680,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785154148</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2698,7 +2690,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>9.866208</t>
+          <t>5.041667</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2715,12 +2707,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2730,7 +2722,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.36789</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2810,7 +2802,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>9.866208</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2827,12 +2819,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2842,22 +2834,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>65.95</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2867,27 +2859,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2912,7 +2904,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785131538</t>
+          <t>1785153790</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2922,7 +2914,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>177.643098</t>
+          <t>5.041667</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2939,110 +2931,222 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>65.95</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.3713</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1785131538</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>177.643098</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>0x4a21e608f2a49d0d290d56e481810827c36c3a33b3cdfa52f47a9d205c9195a6</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>1.1213</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>SL Benfica FC</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>FC St. Gallen</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>0xfc195ce6529fc46edc42b440639cd20958bc0e5f58d88c7925cdd8563a01ebd2</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>L19577588</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>1785123830</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>1785438000</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>65.979381</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
+          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3425</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785253987</t>
+          <t>1785282599</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>15.737226</t>
+          <t>101.012788</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,39 +635,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
+          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>142.02999</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.6663</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -675,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785232812</t>
+          <t>1785282154</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>213.178221</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,39 +739,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
+          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>193.23</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -787,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785231712</t>
+          <t>1785281829</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>285.737523</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,28 +843,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
+          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>4.7855</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -891,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785227020</t>
+          <t>1785267733</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>20.185185</t>
+          <t>14.446792</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,39 +947,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
+          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>104.47</t>
+          <t>4.8535</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1003,27 +979,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1048,17 +1024,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785224116</t>
+          <t>1785265830</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>155.925373</t>
+          <t>14.327675</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,12 +1051,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
+          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1090,22 +1066,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC -3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1115,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1160,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785223916</t>
+          <t>1785261286</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>144.089552</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,23 +1163,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
+          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>70.47999</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1264,7 +1240,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785220497</t>
+          <t>1785258767</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1250,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>133.295489</t>
+          <t>15.179487</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,7 +1267,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
+          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1299,31 +1275,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1331,27 +1299,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1344,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785218406</t>
+          <t>1785253987</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>15.737226</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,23 +1371,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
+          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>142.02999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.6663</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1427,7 +1399,11 @@
           <t>Europa League</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1450,7 +1426,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1480,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785213181</t>
+          <t>1785232812</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>254.185874</t>
+          <t>213.178221</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,31 +1483,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
+          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>193.23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1539,27 +1523,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1584,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785189317</t>
+          <t>1785231712</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1578,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>285.737523</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,23 +1595,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
+          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1688,7 +1672,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785188885</t>
+          <t>1785227020</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1698,7 +1682,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>20.185185</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,12 +1699,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
+          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1730,22 +1714,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>104.47</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1755,27 +1739,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1800,17 +1784,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785186773</t>
+          <t>1785224116</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>155.925373</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1827,12 +1811,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
+          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1842,22 +1826,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1867,27 +1851,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1912,17 +1896,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785186621</t>
+          <t>1785223916</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>144.089552</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,27 +1923,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>70.47999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1967,11 +1947,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1979,27 +1955,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2024,17 +2000,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785186464</t>
+          <t>1785220497</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>133.295489</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,7 +2027,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2136,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785186313</t>
+          <t>1785218406</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2163,7 +2139,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2171,31 +2147,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>85.47</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2203,27 +2171,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2248,17 +2216,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785185868</t>
+          <t>1785213181</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>254.185874</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2275,28 +2243,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2307,27 +2275,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2352,17 +2320,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785182082</t>
+          <t>1785189317</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>101.408451</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2379,39 +2347,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>98.9699</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.9187</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>SL Benfica FC</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2419,27 +2379,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2464,17 +2424,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785178276</t>
+          <t>1785188885</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>107.72234</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2491,7 +2451,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2499,15 +2459,19 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2515,7 +2479,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2523,27 +2491,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2568,12 +2536,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785157337</t>
+          <t>1785186773</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2595,12 +2563,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2610,12 +2578,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2625,7 +2593,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2635,27 +2603,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2680,17 +2648,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785154148</t>
+          <t>1785186621</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2707,12 +2675,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2722,12 +2690,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.36789</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2737,7 +2705,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2747,27 +2715,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2792,17 +2760,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785186464</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>9.866208</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2819,12 +2787,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2834,12 +2802,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2849,7 +2817,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2859,27 +2827,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2904,17 +2872,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785186313</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2931,12 +2899,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2946,22 +2914,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>65.95</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2971,27 +2939,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3016,17 +2984,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785131538</t>
+          <t>1785185868</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>177.643098</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3043,110 +3011,878 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.2662</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1785182082</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>101.408451</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>98.9699</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.9187</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19577588</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1785178276</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1785438000</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>107.72234</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1785157337</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1785154148</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2.36789</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>9.866208</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>65.95</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.3713</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1785131538</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>177.643098</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>0x4a21e608f2a49d0d290d56e481810827c36c3a33b3cdfa52f47a9d205c9195a6</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>1.1213</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>SL Benfica FC</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>FC St. Gallen</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>0xfc195ce6529fc46edc42b440639cd20958bc0e5f58d88c7925cdd8563a01ebd2</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>L19577588</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>1785123830</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>1785438000</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>65.979381</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
+          <t>0x993556c3cf15426b02b61df75d8fd0060a5e7634bee1409d10b85861b937670f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785282599</t>
+          <t>1785327349</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>101.012788</t>
+          <t>1.95599</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +643,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
+          <t>0x4faded42a032bd6a91d4916349230f502e8759f9944cbfef78288354f9340944</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>5.80275</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -667,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785282154</t>
+          <t>1785325667</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>9.181132</t>
+          <t>12.120627</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +747,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
+          <t>0x39c74108b106ba600e266454471670d092342df7435c478a184f31c5880fcb1c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -771,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785281829</t>
+          <t>1785325592</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>9.181132</t>
+          <t>378.067885</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,28 +851,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
+          <t>0x6e97ae46202c322fcc5e7c70be0be87e1574709ea5cf0024a945e7d45d548728</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.7855</t>
+          <t>179.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.4763</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -875,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -920,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785267733</t>
+          <t>1785325549</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>14.446792</t>
+          <t>376.461942</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,28 +955,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
+          <t>0x36f17b5f896b8f5c9301b3600be88ac0007d3ce06403ffe9b13d7389417fa953</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.8535</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -979,27 +987,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1024,17 +1032,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785265830</t>
+          <t>1785325496</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>14.327675</t>
+          <t>379.057592</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,39 +1059,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
+          <t>0xf2a45c2970e6d3af37fabd0ad34ce6efeecfe1f77cb4d5f43515fb342f7fcca2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SL Benfica FC -3</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1091,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785261286</t>
+          <t>1785325423</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>378.067885</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,28 +1163,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
+          <t>0xdd031e5f334a60c24ea47a7a807f20a2bead2b80c0227808f5afa24fa77a3d06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>190</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1195,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785258767</t>
+          <t>1785325348</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>15.179487</t>
+          <t>394.805195</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,28 +1267,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
+          <t>0x4c7bd245dd4665e7f9285a58768875e4fa752d61dfc244e87f7283d2907dcb15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>183</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3425</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1299,27 +1299,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785253987</t>
+          <t>1785325203</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>15.737226</t>
+          <t>383.246073</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,27 +1371,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
+          <t>0x13f73d60f1f96dd112ac2a53fa2a1a53f2e55f9bc0782a0d92732337ef7e7519</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>142.02999</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.6663</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1399,11 +1395,7 @@
           <t>Europa League</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1411,27 +1403,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1456,17 +1448,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785232812</t>
+          <t>1785325120</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>213.178221</t>
+          <t>166.287263</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,12 +1475,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
+          <t>0xd5759db5ffa02ee1c17bc11bdfbffb2bb73c6ff16a4fa6bf670dafa016fad84a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1498,22 +1490,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>193.23</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1523,27 +1515,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1568,7 +1560,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785231712</t>
+          <t>1785319802</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1578,7 +1570,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>285.737523</t>
+          <t>21.949861</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,23 +1587,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
+          <t>0x0fc529171c6c4f0c441f19435054a73905e5f2d2ed326778ddb79cd108c6ede1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1619,7 +1615,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xec30d6ed85c3851d5938108fae681432d7a35f2c741191462472aaa11d35b165</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785227020</t>
+          <t>1785317013</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>20.185185</t>
+          <t>7.929825</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
+          <t>0x2d47f0e85c65fcb84f5de7818b5845226e8638c4dc49fb9093b9a86fe895116b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1714,22 +1714,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>104.47</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1739,27 +1739,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785224116</t>
+          <t>1785316734</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>155.925373</t>
+          <t>20.38009</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,12 +1811,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
+          <t>0xe8fb252bc279aab31e6c6f4de96e27aca4bae9402699e12add62fecf7cc6090d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1851,27 +1851,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1896,17 +1896,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785223916</t>
+          <t>1785314887</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>144.089552</t>
+          <t>14.280543</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,23 +1923,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
+          <t>0x988d12bce5f972af9ca3a2a7a91ba784d379a454873fb5ad9267f635cfeabaae</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>70.47999</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1947,7 +1951,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2000,7 +2008,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785220497</t>
+          <t>1785314533</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2010,7 +2018,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>133.295489</t>
+          <t>273.426184</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,12 +2035,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
+          <t>0x78d34863dc5be51d39c855d3868e1af787b7281b3a9ba704567d82456b113d15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2042,12 +2050,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>178.48</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2057,7 +2065,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2067,27 +2075,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2112,17 +2120,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785218406</t>
+          <t>1785313946</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>397.727019</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,31 +2147,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
+          <t>0x5106f8b58142e7b5c50eb3e00b44385652098e82742605b478cd59c2271a33a0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2171,27 +2187,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2216,7 +2232,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785213181</t>
+          <t>1785313924</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2226,7 +2242,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>254.185874</t>
+          <t>668.523677</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2243,23 +2259,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
+          <t>0x6e2b82838c81a4891a03953f0ebaca7a027f4125fe2deaed52b0a95c44206dab</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2267,7 +2287,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2320,7 +2344,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785189317</t>
+          <t>1785313712</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2330,7 +2354,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>311.977716</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2347,23 +2371,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
+          <t>0x6a19a9357d731588796a01e05f4e8808a84076b6662f83356dcf6c6b00474e65</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2424,7 +2448,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785188885</t>
+          <t>1785313623</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2434,7 +2458,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>240.723982</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2451,12 +2475,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
+          <t>0x6484f0585336dfe74c291be479560bddc0741e80877c77ec5ca7fcb16d4374a5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2466,12 +2490,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2481,7 +2505,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2491,27 +2515,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2536,17 +2560,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785186773</t>
+          <t>1785313622</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>107.387187</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2563,12 +2587,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
+          <t>0x6906ce6d1047273d710579bf3d98367dbf415d0e24ecb41a8a528337a9506d3a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2578,12 +2602,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2593,7 +2617,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2603,27 +2627,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2648,17 +2672,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785186621</t>
+          <t>1785313432</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>12.612813</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2675,12 +2699,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+          <t>0x2c365a540f836041b72448aca3516556411b341658244ff388c1692fa15d2af0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2690,12 +2714,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2705,7 +2729,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2715,27 +2739,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2760,17 +2784,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785186464</t>
+          <t>1785313327</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>20.43454</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,12 +2811,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+          <t>0xe917c05092f572e2e95fee59d14b544fb6d4c549a9e9e7399b744a830680c0ef</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xd22BD9e1B7916fFE0ad765642788c86b6aa29075</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2802,12 +2826,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2817,7 +2841,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2827,27 +2851,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2872,17 +2896,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785186313</t>
+          <t>1785313211</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>13.894737</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,12 +2923,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+          <t>0x8d92cbf4088d40c4b2b67cbb02c218ebad12e894eda090162e17c4b4ec2423ec</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2914,12 +2938,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2929,7 +2953,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2939,27 +2963,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2984,17 +3008,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785185868</t>
+          <t>1785313190</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>11.390582</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3011,31 +3035,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+          <t>0x4858e2eb7b8bfa0a43a468cd0f4c8c41ecc4c6f3ede73f30251c7922e1a658eb</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3043,27 +3075,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3088,17 +3120,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785182082</t>
+          <t>1785313173</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>101.408451</t>
+          <t>20.387812</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3115,39 +3147,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+          <t>0xf0b6c79ec7c1905e25f5ff4b6433e8122df6bb18a211b77a66cc1962804b95cb</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>98.9699</t>
+          <t>56.13118</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.9187</t>
+          <t>1.545</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>SL Benfica FC</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3155,27 +3179,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3200,17 +3224,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785178276</t>
+          <t>1785313133</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>107.72234</t>
+          <t>102.992991</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3227,23 +3251,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3304,7 +3328,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785157337</t>
+          <t>1785282599</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3314,7 +3338,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>101.012788</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3331,27 +3355,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3359,11 +3379,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Besiktas</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3371,27 +3387,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3416,7 +3432,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785154148</t>
+          <t>1785282154</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3426,7 +3442,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,27 +3459,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.36789</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3471,11 +3483,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Besiktas</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3483,27 +3491,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3528,7 +3536,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785281829</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3538,7 +3546,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>9.866208</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3555,39 +3563,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>4.7855</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Besiktas</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3595,27 +3595,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3640,17 +3640,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785267733</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>14.446792</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3667,39 +3667,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>65.95</t>
+          <t>4.8535</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3707,27 +3699,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3752,17 +3744,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785131538</t>
+          <t>1785265830</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>177.643098</t>
+          <t>14.327675</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3779,110 +3771,2838 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>47.52</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SL Benfica FC -3</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19577588</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1785261286</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1785438000</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>148.5</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8.14</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.5362</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1785258767</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>15.179487</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>5.39</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.3425</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19577588</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1785253987</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1785438000</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>15.737226</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>142.02999</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.6663</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1785232812</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>213.178221</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>193.23</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.6763</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1785231712</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>285.737523</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1785227020</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>20.185185</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>104.47</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1785224116</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>155.925373</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>96.54</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1785223916</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>144.089552</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>70.47999</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.5288</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1785220497</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>133.295489</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1785218406</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>85.47</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.3362</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1785213181</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>254.185874</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4.881</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.5337</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1785189317</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>9.144731</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4.881</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.5337</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1785188885</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>9.144731</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1785186773</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1785186621</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1785186464</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1785186313</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1785185868</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.2662</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1785182082</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>101.408451</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>98.9699</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.9187</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19577588</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1785178276</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1785438000</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>107.72234</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1785157337</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1785154148</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2.36789</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>9.866208</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>65.95</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.3713</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1785131538</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>177.643098</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>0x4a21e608f2a49d0d290d56e481810827c36c3a33b3cdfa52f47a9d205c9195a6</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>1.1213</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>SL Benfica FC</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>FC St. Gallen</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>0xfc195ce6529fc46edc42b440639cd20958bc0e5f58d88c7925cdd8563a01ebd2</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>L19577588</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
         <is>
           <t>1785123830</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>1785438000</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>65.979381</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:V67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x993556c3cf15426b02b61df75d8fd0060a5e7634bee1409d10b85861b937670f</t>
+          <t>0x001e676afb8025a177fca2fafbab0c4b0588ee71a31776ebbfe2be57ac5db06e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5112</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0x781f333038176cef4c0433e190179bdff06422f2827828187d4d3847de53f791</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785327349</t>
+          <t>1785352509</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.95599</t>
+          <t>3.585624</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x4faded42a032bd6a91d4916349230f502e8759f9944cbfef78288354f9340944</t>
+          <t>0x9bc12eeb5e62fdab19026dd9c59a6d3d812a1647d656ec82e9b08932d05fc32a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.80275</t>
+          <t>104.66</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785325667</t>
+          <t>1785350915</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>12.120627</t>
+          <t>230.655647</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,31 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x39c74108b106ba600e266454471670d092342df7435c478a184f31c5880fcb1c</t>
+          <t>0x4cc9256963002abc26b03e2de5c65df247f06de8cd8caaeab5e5ab26e126b583</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>200.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -779,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785325592</t>
+          <t>1785350884</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>378.067885</t>
+          <t>442.336088</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,31 +867,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x6e97ae46202c322fcc5e7c70be0be87e1574709ea5cf0024a945e7d45d548728</t>
+          <t>0x24e8cf815969b014ea0bedb7d75a94f636bc090bb24e1787d78815f3e5a70920</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>179.29</t>
+          <t>222.91</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4763</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -883,27 +907,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785325549</t>
+          <t>1785350854</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>376.461942</t>
+          <t>491.261708</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,31 +979,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x36f17b5f896b8f5c9301b3600be88ac0007d3ce06403ffe9b13d7389417fa953</t>
+          <t>0x3729578f30b77e303f3460fb30277c2fcf85fb2049107b0dec479803d11515fe</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>246.56</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4775</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -987,27 +1019,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1032,17 +1064,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785325496</t>
+          <t>1785350824</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>379.057592</t>
+          <t>543.38292</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,31 +1091,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xf2a45c2970e6d3af37fabd0ad34ce6efeecfe1f77cb4d5f43515fb342f7fcca2</t>
+          <t>0xc94c50f0e5b4951b58fe15e51011784173d7fa5dea7800432eb5745354486b80</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1091,27 +1131,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1136,17 +1176,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785325423</t>
+          <t>1785350560</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>378.067885</t>
+          <t>128.391304</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,28 +1203,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xdd031e5f334a60c24ea47a7a807f20a2bead2b80c0227808f5afa24fa77a3d06</t>
+          <t>0xb98b07f3ed69cfe4b366fe2382029c20e5298a2c928a846c34e22585174d22a2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>503.79999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1195,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1240,17 +1280,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785325348</t>
+          <t>1785350534</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>394.805195</t>
+          <t>920.18263</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,28 +1307,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x4c7bd245dd4665e7f9285a58768875e4fa752d61dfc244e87f7283d2907dcb15</t>
+          <t>0xab48fb1edf1fe158898059d349b71fde37cf3bd3d854ff788e8cd23ed34410e3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>1364.53</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4775</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1299,27 +1339,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1344,17 +1384,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785325203</t>
+          <t>1785350511</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>383.246073</t>
+          <t>2515.262673</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,23 +1411,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x13f73d60f1f96dd112ac2a53fa2a1a53f2e55f9bc0782a0d92732337ef7e7519</t>
+          <t>0x54afc83137f5b39b38053c7ac6e311ead709a66ed6180c1bd3071eec1df83367</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>82.98999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.8613</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1395,7 +1439,11 @@
           <t>Europa League</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1403,27 +1451,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1448,17 +1496,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785325120</t>
+          <t>1785348315</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>166.287263</t>
+          <t>96.35993</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,12 +1523,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xd5759db5ffa02ee1c17bc11bdfbffb2bb73c6ff16a4fa6bf670dafa016fad84a</t>
+          <t>0x0dd08bf1a086493c6e680404308a2ef5ba5a320909569533d0dc8e4ad8fdea6a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1490,22 +1538,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.6925</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1515,27 +1563,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1560,7 +1608,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785319802</t>
+          <t>1785347423</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1570,7 +1618,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>21.949861</t>
+          <t>72.750903</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,12 +1635,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x0fc529171c6c4f0c441f19435054a73905e5f2d2ed326778ddb79cd108c6ede1</t>
+          <t>0x993556c3cf15426b02b61df75d8fd0060a5e7634bee1409d10b85861b937670f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1602,12 +1650,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1617,7 +1665,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1627,27 +1675,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xec30d6ed85c3851d5938108fae681432d7a35f2c741191462472aaa11d35b165</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1672,7 +1720,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785317013</t>
+          <t>1785327349</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1682,7 +1730,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>7.929825</t>
+          <t>1.95599</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,39 +1747,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x2d47f0e85c65fcb84f5de7818b5845226e8638c4dc49fb9093b9a86fe895116b</t>
+          <t>0x4faded42a032bd6a91d4916349230f502e8759f9944cbfef78288354f9340944</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11.26</t>
+          <t>5.80275</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1739,27 +1779,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1784,17 +1824,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785316734</t>
+          <t>1785325667</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>20.38009</t>
+          <t>12.120627</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,39 +1851,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xe8fb252bc279aab31e6c6f4de96e27aca4bae9402699e12add62fecf7cc6090d</t>
+          <t>0x39c74108b106ba600e266454471670d092342df7435c478a184f31c5880fcb1c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1851,27 +1883,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1896,17 +1928,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785314887</t>
+          <t>1785325592</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>14.280543</t>
+          <t>378.067885</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,39 +1955,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x988d12bce5f972af9ca3a2a7a91ba784d379a454873fb5ad9267f635cfeabaae</t>
+          <t>0x6e97ae46202c322fcc5e7c70be0be87e1574709ea5cf0024a945e7d45d548728</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>122.7</t>
+          <t>179.29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4763</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1963,27 +1987,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2008,17 +2032,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785314533</t>
+          <t>1785325549</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>273.426184</t>
+          <t>376.461942</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,39 +2059,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x78d34863dc5be51d39c855d3868e1af787b7281b3a9ba704567d82456b113d15</t>
+          <t>0x36f17b5f896b8f5c9301b3600be88ac0007d3ce06403ffe9b13d7389417fa953</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>178.48</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2075,27 +2091,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2120,17 +2136,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785313946</t>
+          <t>1785325496</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>397.727019</t>
+          <t>379.057592</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,39 +2163,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x5106f8b58142e7b5c50eb3e00b44385652098e82742605b478cd59c2271a33a0</t>
+          <t>0xf2a45c2970e6d3af37fabd0ad34ce6efeecfe1f77cb4d5f43515fb342f7fcca2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2187,27 +2195,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2232,17 +2240,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785313924</t>
+          <t>1785325423</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>668.523677</t>
+          <t>378.067885</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,39 +2267,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x6e2b82838c81a4891a03953f0ebaca7a027f4125fe2deaed52b0a95c44206dab</t>
+          <t>0xdd031e5f334a60c24ea47a7a807f20a2bead2b80c0227808f5afa24fa77a3d06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>190</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2299,27 +2299,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2344,17 +2344,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785313712</t>
+          <t>1785325348</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>311.977716</t>
+          <t>394.805195</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,28 +2371,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x6a19a9357d731588796a01e05f4e8808a84076b6662f83356dcf6c6b00474e65</t>
+          <t>0x4c7bd245dd4665e7f9285a58768875e4fa752d61dfc244e87f7283d2907dcb15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>183</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2403,27 +2403,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2448,17 +2448,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785313623</t>
+          <t>1785325203</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>240.723982</t>
+          <t>383.246073</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,39 +2475,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x6484f0585336dfe74c291be479560bddc0741e80877c77ec5ca7fcb16d4374a5</t>
+          <t>0x13f73d60f1f96dd112ac2a53fa2a1a53f2e55f9bc0782a0d92732337ef7e7519</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.19</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2515,27 +2507,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2560,17 +2552,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785313622</t>
+          <t>1785325120</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>107.387187</t>
+          <t>166.287263</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2587,12 +2579,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x6906ce6d1047273d710579bf3d98367dbf415d0e24ecb41a8a528337a9506d3a</t>
+          <t>0xd5759db5ffa02ee1c17bc11bdfbffb2bb73c6ff16a4fa6bf670dafa016fad84a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2602,7 +2594,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2672,7 +2664,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785313432</t>
+          <t>1785319802</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2682,7 +2674,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>12.612813</t>
+          <t>21.949861</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2699,12 +2691,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x2c365a540f836041b72448aca3516556411b341658244ff388c1692fa15d2af0</t>
+          <t>0x0fc529171c6c4f0c441f19435054a73905e5f2d2ed326778ddb79cd108c6ede1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2714,12 +2706,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2729,32 +2721,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>Tromso</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove vs Tromso</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xec30d6ed85c3851d5938108fae681432d7a35f2c741191462472aaa11d35b165</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2784,7 +2776,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785313327</t>
+          <t>1785317013</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2794,7 +2786,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>20.43454</t>
+          <t>7.929825</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2811,12 +2803,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xe917c05092f572e2e95fee59d14b544fb6d4c549a9e9e7399b744a830680c0ef</t>
+          <t>0x2d47f0e85c65fcb84f5de7818b5845226e8638c4dc49fb9093b9a86fe895116b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xd22BD9e1B7916fFE0ad765642788c86b6aa29075</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2826,22 +2818,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2851,27 +2843,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2896,17 +2888,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785313211</t>
+          <t>1785316734</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>13.894737</t>
+          <t>20.38009</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2923,12 +2915,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x8d92cbf4088d40c4b2b67cbb02c218ebad12e894eda090162e17c4b4ec2423ec</t>
+          <t>0xe8fb252bc279aab31e6c6f4de96e27aca4bae9402699e12add62fecf7cc6090d</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2938,22 +2930,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2963,27 +2955,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3008,17 +3000,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785313190</t>
+          <t>1785314887</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>11.390582</t>
+          <t>14.280543</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3035,12 +3027,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x4858e2eb7b8bfa0a43a468cd0f4c8c41ecc4c6f3ede73f30251c7922e1a658eb</t>
+          <t>0x988d12bce5f972af9ca3a2a7a91ba784d379a454873fb5ad9267f635cfeabaae</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3050,12 +3042,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3120,7 +3112,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785313173</t>
+          <t>1785314533</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3130,7 +3122,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>20.387812</t>
+          <t>273.426184</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3147,23 +3139,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xf0b6c79ec7c1905e25f5ff4b6433e8122df6bb18a211b77a66cc1962804b95cb</t>
+          <t>0x78d34863dc5be51d39c855d3868e1af787b7281b3a9ba704567d82456b113d15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>56.13118</t>
+          <t>178.48</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3171,7 +3167,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785313133</t>
+          <t>1785313946</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>102.992991</t>
+          <t>397.727019</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3251,23 +3251,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
+          <t>0x5106f8b58142e7b5c50eb3e00b44385652098e82742605b478cd59c2271a33a0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3275,7 +3279,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3283,27 +3291,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3328,7 +3336,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785282599</t>
+          <t>1785313924</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3338,7 +3346,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>101.012788</t>
+          <t>668.523677</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3355,23 +3363,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
+          <t>0x6e2b82838c81a4891a03953f0ebaca7a027f4125fe2deaed52b0a95c44206dab</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3379,7 +3391,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3432,7 +3448,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785282154</t>
+          <t>1785313712</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3442,7 +3458,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>9.181132</t>
+          <t>311.977716</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3459,23 +3475,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
+          <t>0x6a19a9357d731588796a01e05f4e8808a84076b6662f83356dcf6c6b00474e65</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3536,7 +3552,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785281829</t>
+          <t>1785313623</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3546,7 +3562,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>9.181132</t>
+          <t>240.723982</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3563,31 +3579,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
+          <t>0x6484f0585336dfe74c291be479560bddc0741e80877c77ec5ca7fcb16d4374a5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.7855</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3595,27 +3619,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3640,17 +3664,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785267733</t>
+          <t>1785313622</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>14.446792</t>
+          <t>107.387187</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3667,31 +3691,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
+          <t>0x6906ce6d1047273d710579bf3d98367dbf415d0e24ecb41a8a528337a9506d3a</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.8535</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3699,27 +3731,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3744,17 +3776,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785265830</t>
+          <t>1785313432</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>14.327675</t>
+          <t>12.612813</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3771,12 +3803,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
+          <t>0x2c365a540f836041b72448aca3516556411b341658244ff388c1692fa15d2af0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3786,22 +3818,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SL Benfica FC -3</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3811,27 +3843,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3856,17 +3888,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785261286</t>
+          <t>1785313327</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>20.43454</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3883,23 +3915,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
+          <t>0xe917c05092f572e2e95fee59d14b544fb6d4c549a9e9e7399b744a830680c0ef</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0xd22BD9e1B7916fFE0ad765642788c86b6aa29075</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3907,7 +3943,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3960,7 +4000,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785258767</t>
+          <t>1785313211</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3970,7 +4010,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>15.179487</t>
+          <t>13.894737</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3987,31 +4027,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
+          <t>0x8d92cbf4088d40c4b2b67cbb02c218ebad12e894eda090162e17c4b4ec2423ec</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.3425</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4019,27 +4067,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4064,17 +4112,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785253987</t>
+          <t>1785313190</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>15.737226</t>
+          <t>11.390582</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4091,12 +4139,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
+          <t>0x4858e2eb7b8bfa0a43a468cd0f4c8c41ecc4c6f3ede73f30251c7922e1a658eb</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4106,22 +4154,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>142.02999</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.6663</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4131,27 +4179,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4176,7 +4224,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785232812</t>
+          <t>1785313173</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4186,7 +4234,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>213.178221</t>
+          <t>20.387812</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4203,39 +4251,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
+          <t>0xf0b6c79ec7c1905e25f5ff4b6433e8122df6bb18a211b77a66cc1962804b95cb</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>193.23</t>
+          <t>56.13118</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.545</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4243,27 +4283,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4288,7 +4328,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785231712</t>
+          <t>1785313133</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4298,7 +4338,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>285.737523</t>
+          <t>102.992991</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4315,23 +4355,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
+          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4347,27 +4387,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4392,7 +4432,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785227020</t>
+          <t>1785282599</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4402,7 +4442,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>20.185185</t>
+          <t>101.012788</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4419,39 +4459,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
+          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>104.47</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4459,27 +4491,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4504,7 +4536,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785224116</t>
+          <t>1785282154</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4514,7 +4546,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>155.925373</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4531,39 +4563,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
+          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4571,27 +4595,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4616,7 +4640,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785223916</t>
+          <t>1785281829</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4626,7 +4650,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>144.089552</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4643,28 +4667,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
+          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>70.47999</t>
+          <t>4.7855</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4675,27 +4699,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4720,17 +4744,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785220497</t>
+          <t>1785267733</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>133.295489</t>
+          <t>14.446792</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4747,39 +4771,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
+          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>4.8535</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4787,27 +4803,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4832,17 +4848,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785218406</t>
+          <t>1785265830</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>14.327675</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4859,7 +4875,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
+          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4867,23 +4883,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SL Benfica FC -3</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4891,27 +4915,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
+          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4936,17 +4960,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785213181</t>
+          <t>1785261286</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>254.185874</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4963,23 +4987,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
+          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5040,7 +5064,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785189317</t>
+          <t>1785258767</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5050,7 +5074,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>15.179487</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5067,28 +5091,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
+          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5099,27 +5123,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5144,17 +5168,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785188885</t>
+          <t>1785253987</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>15.737226</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5171,12 +5195,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
+          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5186,22 +5210,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>142.02999</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.6663</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5211,27 +5235,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5256,17 +5280,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785186773</t>
+          <t>1785232812</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>213.178221</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5283,12 +5307,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
+          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5298,22 +5322,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>193.23</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5323,27 +5347,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5368,17 +5392,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785186621</t>
+          <t>1785231712</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>285.737523</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5395,27 +5419,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5423,11 +5443,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5435,27 +5451,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5480,17 +5496,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785186464</t>
+          <t>1785227020</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>20.185185</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5507,12 +5523,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5522,22 +5538,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>104.47</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5547,27 +5563,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5592,17 +5608,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785186313</t>
+          <t>1785224116</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>155.925373</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5619,12 +5635,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5634,22 +5650,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5659,27 +5675,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5704,17 +5720,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785185868</t>
+          <t>1785223916</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>144.089552</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5731,28 +5747,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>70.47999</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5763,27 +5779,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5808,17 +5824,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785182082</t>
+          <t>1785220497</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>101.408451</t>
+          <t>133.295489</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5835,12 +5851,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5850,22 +5866,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>98.9699</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.9187</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5875,27 +5891,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5920,17 +5936,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785178276</t>
+          <t>1785218406</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>107.72234</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5947,7 +5963,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5958,17 +5974,17 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>85.47</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5994,7 +6010,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6024,7 +6040,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785157337</t>
+          <t>1785213181</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6034,7 +6050,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>254.185874</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6051,27 +6067,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6079,11 +6091,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Besiktas</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6091,27 +6099,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6136,7 +6144,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785154148</t>
+          <t>1785189317</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6146,7 +6154,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6163,27 +6171,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.36789</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6191,11 +6195,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Besiktas</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6203,27 +6203,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785188885</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>9.866208</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6275,12 +6275,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6290,12 +6290,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6315,27 +6315,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6360,17 +6360,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785186773</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6387,12 +6387,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6402,22 +6402,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>65.95</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6427,27 +6427,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6472,17 +6472,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785131538</t>
+          <t>1785186621</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>177.643098</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6499,110 +6499,1214 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1785186464</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1785186313</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1785185868</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.2662</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1785182082</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>101.408451</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>98.9699</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.9187</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19577588</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1785178276</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1785438000</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>107.72234</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1785157337</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1785154148</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2.36789</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>9.866208</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>65.95</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.3713</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1785131538</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>177.643098</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>0x4a21e608f2a49d0d290d56e481810827c36c3a33b3cdfa52f47a9d205c9195a6</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>1.1213</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>SL Benfica FC</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>FC St. Gallen</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>0xfc195ce6529fc46edc42b440639cd20958bc0e5f58d88c7925cdd8563a01ebd2</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>L19577588</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
         <is>
           <t>1785123830</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>1785438000</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>65.979381</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V67"/>
+  <dimension ref="A1:V74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x001e676afb8025a177fca2fafbab0c4b0588ee71a31776ebbfe2be57ac5db06e</t>
+          <t>0xe8d3398ff301339e290daf01ae6876fd68d47e759c9d409ef00bbc858bae53d1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x781f333038176cef4c0433e190179bdff06422f2827828187d4d3847de53f791</t>
+          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785352509</t>
+          <t>1785358486</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3.585624</t>
+          <t>15.023729</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x9bc12eeb5e62fdab19026dd9c59a6d3d812a1647d656ec82e9b08932d05fc32a</t>
+          <t>0x6caf1354e289f361f3527f9fab48eb02c23c0756ae001e45930362caf84237dc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,19 +651,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>104.66</t>
+          <t>30.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -671,11 +667,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -683,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785350915</t>
+          <t>1785358266</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>230.655647</t>
+          <t>39.03645</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x4cc9256963002abc26b03e2de5c65df247f06de8cd8caaeab5e5ab26e126b583</t>
+          <t>0x93785b3a7d055c5e2c869f1c6ed046a0c16cd38f39a06deaefeabb59967bf72c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,22 +762,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>200.71</t>
+          <t>9.5122</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4ab76a4a1fa597ca197135de1fba0710473970c8adaef292b0acea5fe28788f8</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785350884</t>
+          <t>1785358055</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>442.336088</t>
+          <t>19.512205</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x24e8cf815969b014ea0bedb7d75a94f636bc090bb24e1787d78815f3e5a70920</t>
+          <t>0xe9c4a1ecf56e1210003b8a7c5c9dedc347ba38e18d81ea653d600cfae0406ee7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,22 +874,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>222.91</t>
+          <t>1.99999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -907,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785350854</t>
+          <t>1785357507</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>491.261708</t>
+          <t>3.278672</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x3729578f30b77e303f3460fb30277c2fcf85fb2049107b0dec479803d11515fe</t>
+          <t>0x91839b38bfe01bb58e0542f3e4844d2996af26b2e1159a45b719e543c59d0061</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -994,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>246.56</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1019,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785350824</t>
+          <t>1785357504</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>543.38292</t>
+          <t>18.721311</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,27 +1083,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xc94c50f0e5b4951b58fe15e51011784173d7fa5dea7800432eb5745354486b80</t>
+          <t>0x12fa97e26b4d1fe9bc62fd353b41531c2d1e3636d5808e00f72cda223c5b7275</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.7637</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1119,11 +1107,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1131,27 +1115,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xba7019cc98094442aac3dcde57fe2ab308f401a1a9e55c251da54769aa97bf2b</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1176,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785350560</t>
+          <t>1785357342</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1186,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>128.391304</t>
+          <t>30.180033</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1203,23 +1187,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xb98b07f3ed69cfe4b366fe2382029c20e5298a2c928a846c34e22585174d22a2</t>
+          <t>0x580c7d1b576d43e738d64f6bb0fc1b2a6d6762d7d285da29ae6814cfcd809ae2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>503.79999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1227,7 +1215,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1235,27 +1227,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd794b506219d24bb3d154b82e776aef773d5c44cbbd3c35da4709144cfa915ea</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785350534</t>
+          <t>1785357285</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1290,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>920.18263</t>
+          <t>43.715847</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,31 +1299,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xab48fb1edf1fe158898059d349b71fde37cf3bd3d854ff788e8cd23ed34410e3</t>
+          <t>0x001e676afb8025a177fca2fafbab0c4b0588ee71a31776ebbfe2be57ac5db06e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1364.53</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1339,27 +1339,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x781f333038176cef4c0433e190179bdff06422f2827828187d4d3847de53f791</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1384,17 +1384,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785350511</t>
+          <t>1785352509</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2515.262673</t>
+          <t>3.585624</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x54afc83137f5b39b38053c7ac6e311ead709a66ed6180c1bd3071eec1df83367</t>
+          <t>0x9bc12eeb5e62fdab19026dd9c59a6d3d812a1647d656ec82e9b08932d05fc32a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>82.98999</t>
+          <t>104.66</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.8613</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785348315</t>
+          <t>1785350915</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>96.35993</t>
+          <t>230.655647</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x0dd08bf1a086493c6e680404308a2ef5ba5a320909569533d0dc8e4ad8fdea6a</t>
+          <t>0x4cc9256963002abc26b03e2de5c65df247f06de8cd8caaeab5e5ab26e126b583</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1538,22 +1538,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>200.71</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.6925</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1563,27 +1563,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785347423</t>
+          <t>1785350884</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>72.750903</t>
+          <t>442.336088</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x993556c3cf15426b02b61df75d8fd0060a5e7634bee1409d10b85861b937670f</t>
+          <t>0x24e8cf815969b014ea0bedb7d75a94f636bc090bb24e1787d78815f3e5a70920</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>222.91</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5112</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1675,27 +1675,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785327349</t>
+          <t>1785350854</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.95599</t>
+          <t>491.261708</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,31 +1747,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x4faded42a032bd6a91d4916349230f502e8759f9944cbfef78288354f9340944</t>
+          <t>0x3729578f30b77e303f3460fb30277c2fcf85fb2049107b0dec479803d11515fe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5.80275</t>
+          <t>246.56</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1779,27 +1787,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1824,17 +1832,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785325667</t>
+          <t>1785350824</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>12.120627</t>
+          <t>543.38292</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1851,31 +1859,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x39c74108b106ba600e266454471670d092342df7435c478a184f31c5880fcb1c</t>
+          <t>0xc94c50f0e5b4951b58fe15e51011784173d7fa5dea7800432eb5745354486b80</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1883,27 +1899,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1928,17 +1944,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785325592</t>
+          <t>1785350560</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>378.067885</t>
+          <t>128.391304</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,28 +1971,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x6e97ae46202c322fcc5e7c70be0be87e1574709ea5cf0024a945e7d45d548728</t>
+          <t>0xb98b07f3ed69cfe4b366fe2382029c20e5298a2c928a846c34e22585174d22a2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>179.29</t>
+          <t>503.79999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4763</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1987,27 +2003,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2032,17 +2048,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785325549</t>
+          <t>1785350534</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>376.461942</t>
+          <t>920.18263</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,28 +2075,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x36f17b5f896b8f5c9301b3600be88ac0007d3ce06403ffe9b13d7389417fa953</t>
+          <t>0xab48fb1edf1fe158898059d349b71fde37cf3bd3d854ff788e8cd23ed34410e3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>1364.53</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4775</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2091,27 +2107,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2136,17 +2152,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785325496</t>
+          <t>1785350511</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>379.057592</t>
+          <t>2515.262673</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2163,23 +2179,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xf2a45c2970e6d3af37fabd0ad34ce6efeecfe1f77cb4d5f43515fb342f7fcca2</t>
+          <t>0x54afc83137f5b39b38053c7ac6e311ead709a66ed6180c1bd3071eec1df83367</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>82.98999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.8613</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2187,7 +2207,11 @@
           <t>Europa League</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2195,27 +2219,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2240,17 +2264,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785325423</t>
+          <t>1785348315</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>378.067885</t>
+          <t>96.35993</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2267,23 +2291,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xdd031e5f334a60c24ea47a7a807f20a2bead2b80c0227808f5afa24fa77a3d06</t>
+          <t>0x0dd08bf1a086493c6e680404308a2ef5ba5a320909569533d0dc8e4ad8fdea6a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.6925</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2291,7 +2319,11 @@
           <t>Europa League</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pafos FC</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2299,27 +2331,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2344,17 +2376,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785325348</t>
+          <t>1785347423</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>394.805195</t>
+          <t>72.750903</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,31 +2403,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x4c7bd245dd4665e7f9285a58768875e4fa752d61dfc244e87f7283d2907dcb15</t>
+          <t>0x993556c3cf15426b02b61df75d8fd0060a5e7634bee1409d10b85861b937670f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4775</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2403,27 +2443,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2448,17 +2488,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785325203</t>
+          <t>1785327349</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>383.246073</t>
+          <t>1.95599</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,7 +2515,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x13f73d60f1f96dd112ac2a53fa2a1a53f2e55f9bc0782a0d92732337ef7e7519</t>
+          <t>0x4faded42a032bd6a91d4916349230f502e8759f9944cbfef78288354f9340944</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2486,12 +2526,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>5.80275</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2522,7 +2562,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2552,7 +2592,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785325120</t>
+          <t>1785325667</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2562,7 +2602,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>166.287263</t>
+          <t>12.120627</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2579,39 +2619,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xd5759db5ffa02ee1c17bc11bdfbffb2bb73c6ff16a4fa6bf670dafa016fad84a</t>
+          <t>0x39c74108b106ba600e266454471670d092342df7435c478a184f31c5880fcb1c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2619,27 +2651,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2664,17 +2696,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785319802</t>
+          <t>1785325592</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>21.949861</t>
+          <t>378.067885</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2691,39 +2723,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x0fc529171c6c4f0c441f19435054a73905e5f2d2ed326778ddb79cd108c6ede1</t>
+          <t>0x6e97ae46202c322fcc5e7c70be0be87e1574709ea5cf0024a945e7d45d548728</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>179.29</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.4763</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2731,27 +2755,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xec30d6ed85c3851d5938108fae681432d7a35f2c741191462472aaa11d35b165</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2776,17 +2800,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785317013</t>
+          <t>1785325549</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>7.929825</t>
+          <t>376.461942</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2803,39 +2827,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x2d47f0e85c65fcb84f5de7818b5845226e8638c4dc49fb9093b9a86fe895116b</t>
+          <t>0x36f17b5f896b8f5c9301b3600be88ac0007d3ce06403ffe9b13d7389417fa953</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11.26</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2843,27 +2859,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2888,17 +2904,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785316734</t>
+          <t>1785325496</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>20.38009</t>
+          <t>379.057592</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2915,39 +2931,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xe8fb252bc279aab31e6c6f4de96e27aca4bae9402699e12add62fecf7cc6090d</t>
+          <t>0xf2a45c2970e6d3af37fabd0ad34ce6efeecfe1f77cb4d5f43515fb342f7fcca2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2955,27 +2963,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3000,17 +3008,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785314887</t>
+          <t>1785325423</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>14.280543</t>
+          <t>378.067885</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,39 +3035,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x988d12bce5f972af9ca3a2a7a91ba784d379a454873fb5ad9267f635cfeabaae</t>
+          <t>0xdd031e5f334a60c24ea47a7a807f20a2bead2b80c0227808f5afa24fa77a3d06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>122.7</t>
+          <t>190</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3067,27 +3067,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3112,17 +3112,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785314533</t>
+          <t>1785325348</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>273.426184</t>
+          <t>394.805195</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3139,39 +3139,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x78d34863dc5be51d39c855d3868e1af787b7281b3a9ba704567d82456b113d15</t>
+          <t>0x4c7bd245dd4665e7f9285a58768875e4fa752d61dfc244e87f7283d2907dcb15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>178.48</t>
+          <t>183</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3179,27 +3171,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3224,17 +3216,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785313946</t>
+          <t>1785325203</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>397.727019</t>
+          <t>383.246073</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3251,39 +3243,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x5106f8b58142e7b5c50eb3e00b44385652098e82742605b478cd59c2271a33a0</t>
+          <t>0x13f73d60f1f96dd112ac2a53fa2a1a53f2e55f9bc0782a0d92732337ef7e7519</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3291,27 +3275,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3336,17 +3320,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785313924</t>
+          <t>1785325120</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>668.523677</t>
+          <t>166.287263</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3363,12 +3347,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x6e2b82838c81a4891a03953f0ebaca7a027f4125fe2deaed52b0a95c44206dab</t>
+          <t>0xd5759db5ffa02ee1c17bc11bdfbffb2bb73c6ff16a4fa6bf670dafa016fad84a</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3378,7 +3362,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3448,7 +3432,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785313712</t>
+          <t>1785319802</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3458,7 +3442,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>311.977716</t>
+          <t>21.949861</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3475,23 +3459,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x6a19a9357d731588796a01e05f4e8808a84076b6662f83356dcf6c6b00474e65</t>
+          <t>0x0fc529171c6c4f0c441f19435054a73905e5f2d2ed326778ddb79cd108c6ede1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3499,7 +3487,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3522,7 +3514,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xec30d6ed85c3851d5938108fae681432d7a35f2c741191462472aaa11d35b165</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3552,7 +3544,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785313623</t>
+          <t>1785317013</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3562,7 +3554,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>240.723982</t>
+          <t>7.929825</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3579,12 +3571,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x6484f0585336dfe74c291be479560bddc0741e80877c77ec5ca7fcb16d4374a5</t>
+          <t>0x2d47f0e85c65fcb84f5de7818b5845226e8638c4dc49fb9093b9a86fe895116b</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3594,22 +3586,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.19</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3619,27 +3611,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3664,17 +3656,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785313622</t>
+          <t>1785316734</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>107.387187</t>
+          <t>20.38009</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3691,12 +3683,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x6906ce6d1047273d710579bf3d98367dbf415d0e24ecb41a8a528337a9506d3a</t>
+          <t>0xe8fb252bc279aab31e6c6f4de96e27aca4bae9402699e12add62fecf7cc6090d</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3706,22 +3698,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3731,27 +3723,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3776,17 +3768,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785313432</t>
+          <t>1785314887</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>12.612813</t>
+          <t>14.280543</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3803,12 +3795,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x2c365a540f836041b72448aca3516556411b341658244ff388c1692fa15d2af0</t>
+          <t>0x988d12bce5f972af9ca3a2a7a91ba784d379a454873fb5ad9267f635cfeabaae</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3818,7 +3810,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3888,7 +3880,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785313327</t>
+          <t>1785314533</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3898,7 +3890,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>20.43454</t>
+          <t>273.426184</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3915,12 +3907,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xe917c05092f572e2e95fee59d14b544fb6d4c549a9e9e7399b744a830680c0ef</t>
+          <t>0x78d34863dc5be51d39c855d3868e1af787b7281b3a9ba704567d82456b113d15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xd22BD9e1B7916fFE0ad765642788c86b6aa29075</t>
+          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3930,12 +3922,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>178.48</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4000,7 +3992,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785313211</t>
+          <t>1785313946</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4010,7 +4002,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>13.894737</t>
+          <t>397.727019</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4027,12 +4019,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x8d92cbf4088d40c4b2b67cbb02c218ebad12e894eda090162e17c4b4ec2423ec</t>
+          <t>0x5106f8b58142e7b5c50eb3e00b44385652098e82742605b478cd59c2271a33a0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4042,12 +4034,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4112,7 +4104,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785313190</t>
+          <t>1785313924</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4122,7 +4114,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>11.390582</t>
+          <t>668.523677</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4139,12 +4131,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x4858e2eb7b8bfa0a43a468cd0f4c8c41ecc4c6f3ede73f30251c7922e1a658eb</t>
+          <t>0x6e2b82838c81a4891a03953f0ebaca7a027f4125fe2deaed52b0a95c44206dab</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4154,12 +4146,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4224,7 +4216,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785313173</t>
+          <t>1785313712</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4234,7 +4226,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>20.387812</t>
+          <t>311.977716</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4251,7 +4243,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xf0b6c79ec7c1905e25f5ff4b6433e8122df6bb18a211b77a66cc1962804b95cb</t>
+          <t>0x6a19a9357d731588796a01e05f4e8808a84076b6662f83356dcf6c6b00474e65</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4262,12 +4254,12 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>56.13118</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4328,7 +4320,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785313133</t>
+          <t>1785313623</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4338,7 +4330,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>102.992991</t>
+          <t>240.723982</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4355,23 +4347,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
+          <t>0x6484f0585336dfe74c291be479560bddc0741e80877c77ec5ca7fcb16d4374a5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4379,7 +4375,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4387,27 +4387,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785282599</t>
+          <t>1785313622</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>101.012788</t>
+          <t>107.387187</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4459,23 +4459,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
+          <t>0x6906ce6d1047273d710579bf3d98367dbf415d0e24ecb41a8a528337a9506d3a</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4483,7 +4487,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4536,7 +4544,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785282154</t>
+          <t>1785313432</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4546,7 +4554,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>9.181132</t>
+          <t>12.612813</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4563,23 +4571,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
+          <t>0x2c365a540f836041b72448aca3516556411b341658244ff388c1692fa15d2af0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4587,7 +4599,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4640,7 +4656,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785281829</t>
+          <t>1785313327</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4650,7 +4666,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>9.181132</t>
+          <t>20.43454</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4667,31 +4683,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
+          <t>0xe917c05092f572e2e95fee59d14b544fb6d4c549a9e9e7399b744a830680c0ef</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0xd22BD9e1B7916fFE0ad765642788c86b6aa29075</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4.7855</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4699,27 +4723,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4744,17 +4768,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785267733</t>
+          <t>1785313211</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>14.446792</t>
+          <t>13.894737</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4771,31 +4795,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
+          <t>0x8d92cbf4088d40c4b2b67cbb02c218ebad12e894eda090162e17c4b4ec2423ec</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4.8535</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4803,27 +4835,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4848,17 +4880,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785265830</t>
+          <t>1785313190</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>14.327675</t>
+          <t>11.390582</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4875,12 +4907,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
+          <t>0x4858e2eb7b8bfa0a43a468cd0f4c8c41ecc4c6f3ede73f30251c7922e1a658eb</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4890,22 +4922,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SL Benfica FC -3</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4915,27 +4947,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4960,17 +4992,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785261286</t>
+          <t>1785313173</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>20.387812</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4987,23 +5019,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
+          <t>0xf0b6c79ec7c1905e25f5ff4b6433e8122df6bb18a211b77a66cc1962804b95cb</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>56.13118</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.545</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5064,7 +5096,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785258767</t>
+          <t>1785313133</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5074,7 +5106,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>15.179487</t>
+          <t>102.992991</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5091,28 +5123,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
+          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.3425</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5123,27 +5155,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5168,17 +5200,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785253987</t>
+          <t>1785282599</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>15.737226</t>
+          <t>101.012788</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5195,39 +5227,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
+          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>142.02999</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.6663</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5235,27 +5259,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5280,7 +5304,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785232812</t>
+          <t>1785282154</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5290,7 +5314,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>213.178221</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5307,39 +5331,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
+          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>193.23</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5347,27 +5363,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5392,7 +5408,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785231712</t>
+          <t>1785281829</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5402,7 +5418,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>285.737523</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5419,28 +5435,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
+          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>4.7855</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5451,27 +5467,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5496,17 +5512,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785227020</t>
+          <t>1785267733</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>20.185185</t>
+          <t>14.446792</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5523,39 +5539,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
+          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>104.47</t>
+          <t>4.8535</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5563,27 +5571,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5608,17 +5616,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785224116</t>
+          <t>1785265830</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>155.925373</t>
+          <t>14.327675</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5635,12 +5643,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
+          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5650,22 +5658,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC -3</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5675,27 +5683,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5720,17 +5728,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785223916</t>
+          <t>1785261286</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>144.089552</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5747,23 +5755,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
+          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>70.47999</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5824,7 +5832,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785220497</t>
+          <t>1785258767</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5834,7 +5842,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>133.295489</t>
+          <t>15.179487</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5851,7 +5859,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
+          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5859,31 +5867,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5891,27 +5891,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5936,17 +5936,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785218406</t>
+          <t>1785253987</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>15.737226</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5963,23 +5963,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
+          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>142.02999</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.6663</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5987,7 +5991,11 @@
           <t>Europa League</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6010,7 +6018,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6040,7 +6048,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785213181</t>
+          <t>1785232812</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6050,7 +6058,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>254.185874</t>
+          <t>213.178221</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6067,31 +6075,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
+          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>193.23</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6099,27 +6115,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6144,7 +6160,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785189317</t>
+          <t>1785231712</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6154,7 +6170,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>285.737523</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6171,23 +6187,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
+          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6248,7 +6264,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785188885</t>
+          <t>1785227020</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6258,7 +6274,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>20.185185</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6275,12 +6291,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
+          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6290,22 +6306,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>104.47</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6315,27 +6331,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6360,17 +6376,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785186773</t>
+          <t>1785224116</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>155.925373</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6387,12 +6403,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
+          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6402,22 +6418,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6427,27 +6443,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6472,17 +6488,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785186621</t>
+          <t>1785223916</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>144.089552</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6499,27 +6515,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>70.47999</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6527,11 +6539,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6539,27 +6547,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6584,17 +6592,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785186464</t>
+          <t>1785220497</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>133.295489</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6611,7 +6619,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6696,7 +6704,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785186313</t>
+          <t>1785218406</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6723,7 +6731,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6731,31 +6739,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>85.47</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6763,27 +6763,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785185868</t>
+          <t>1785213181</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>254.185874</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6835,28 +6835,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -6867,27 +6867,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6912,17 +6912,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785182082</t>
+          <t>1785189317</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>101.408451</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6939,39 +6939,31 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>98.9699</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.9187</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>SL Benfica FC</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6979,27 +6971,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -7024,17 +7016,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785178276</t>
+          <t>1785188885</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>107.72234</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7051,7 +7043,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7059,15 +7051,19 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7075,7 +7071,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7083,27 +7083,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785157337</t>
+          <t>1785186773</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -7155,12 +7155,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7195,27 +7195,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7240,17 +7240,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785154148</t>
+          <t>1785186621</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7267,12 +7267,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7282,12 +7282,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2.36789</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7307,27 +7307,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7352,17 +7352,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785186464</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>9.866208</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7379,12 +7379,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7419,27 +7419,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7464,17 +7464,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785186313</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7491,12 +7491,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7506,22 +7506,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>65.95</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7531,27 +7531,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7576,17 +7576,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785131538</t>
+          <t>1785185868</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>177.643098</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7603,110 +7603,878 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.2662</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1785182082</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>101.408451</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>98.9699</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.9187</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19577588</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1785178276</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1785438000</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>107.72234</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1785157337</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1785154148</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2.36789</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>9.866208</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>65.95</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.3713</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1785131538</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>177.643098</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>0x4a21e608f2a49d0d290d56e481810827c36c3a33b3cdfa52f47a9d205c9195a6</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>1.1213</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>SL Benfica FC</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>FC St. Gallen</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>0xfc195ce6529fc46edc42b440639cd20958bc0e5f58d88c7925cdd8563a01ebd2</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>L19577588</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
         <is>
           <t>1785123830</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>1785438000</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>65.979381</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="V74" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V74"/>
+  <dimension ref="A1:V80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xe8d3398ff301339e290daf01ae6876fd68d47e759c9d409ef00bbc858bae53d1</t>
+          <t>0x41aafd361fbdbc090304c361aa96e3d7d1986ad198e757cc1ed42d3a36d60feb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,31 +539,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
+          <t>0x38894b4e2a8e5d7e486f731ef1c20c3f048cafb9a2d74debe9378b5d273c6bae</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785358486</t>
+          <t>1785362098</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>15.023729</t>
+          <t>37.641278</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x6caf1354e289f361f3527f9fab48eb02c23c0756ae001e45930362caf84237dc</t>
+          <t>0xe548f2f667138f07fba5f8b56872f6e05a380228941a477ad0be28b68346322c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,23 +643,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>4.82999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7887</t>
+          <t>1.7163</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pafos FC 0</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -675,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PAOK vs FC Dynamo Kyiv</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>FC Dynamo Kyiv</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
+          <t>0x372966a20c1cb92145662d4191d1ea402efa119df308298395ad72ee4927083e</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19577850</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785358266</t>
+          <t>1785362057</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785433500</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>39.03645</t>
+          <t>6.743442</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x93785b3a7d055c5e2c869f1c6ed046a0c16cd38f39a06deaefeabb59967bf72c</t>
+          <t>0xe8695e613b59508aa7ca7d5747a15d00bcfbed5e4f9653ed44f2df97fd577dfc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -762,22 +762,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9.5122</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x4ab76a4a1fa597ca197135de1fba0710473970c8adaef292b0acea5fe28788f8</t>
+          <t>0xb7cd00a89de154596fb5ed105b39373600b95939a4d9c11792f78fa57728b1fc</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785358055</t>
+          <t>1785362047</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>19.512205</t>
+          <t>18.306636</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xe9c4a1ecf56e1210003b8a7c5c9dedc347ba38e18d81ea653d600cfae0406ee7</t>
+          <t>0x592ca05e5d2e598f37fef187e9bd4564705367d06c16f7ed3162e4659d773d8d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.99999</t>
+          <t>30.67998</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.7125</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
+          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785357507</t>
+          <t>1785362047</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3.278672</t>
+          <t>43.059621</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x91839b38bfe01bb58e0542f3e4844d2996af26b2e1159a45b719e543c59d0061</t>
+          <t>0x57f4d612536438737c246a83cb4a06a364b2ba5f0d5bffa44b2d450c599f005c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -986,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Pafos FC -1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1011,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
+          <t>0x963e029345e2eec87a8efe31b92941a4225d7b0339bd00d1d2b34c4b1ef0c388</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785357504</t>
+          <t>1785362047</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>18.721311</t>
+          <t>25.723473</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,31 +1083,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x12fa97e26b4d1fe9bc62fd353b41531c2d1e3636d5808e00f72cda223c5b7275</t>
+          <t>0xa8f611211f253b096f6e8910a8e6d6614836d3fec79ca646c8cff14aa6cf4fe3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.7637</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1130,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xba7019cc98094442aac3dcde57fe2ab308f401a1a9e55c251da54769aa97bf2b</t>
+          <t>0x76c9ba7a74843dcbf4f3d6b5e6055a7b6d28e43c811b91c405bc0dbc814a4a23</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785357342</t>
+          <t>1785360745</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>30.180033</t>
+          <t>6.337662</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,7 +1195,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x580c7d1b576d43e738d64f6bb0fc1b2a6d6762d7d285da29ae6814cfcd809ae2</t>
+          <t>0xe8d3398ff301339e290daf01ae6876fd68d47e759c9d409ef00bbc858bae53d1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1202,47 +1210,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pafos FC vs Hajduk Split</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Pafos FC</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>Hajduk Split</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Pafos FC vs Hajduk Split</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Pafos FC</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Hajduk Split</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xd794b506219d24bb3d154b82e776aef773d5c44cbbd3c35da4709144cfa915ea</t>
+          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1272,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785357285</t>
+          <t>1785358486</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>43.715847</t>
+          <t>15.023729</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,7 +1307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x001e676afb8025a177fca2fafbab0c4b0588ee71a31776ebbfe2be57ac5db06e</t>
+          <t>0x6caf1354e289f361f3527f9fab48eb02c23c0756ae001e45930362caf84237dc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1307,31 +1315,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>30.79</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>RSC Anderlecht</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1339,27 +1339,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x781f333038176cef4c0433e190179bdff06422f2827828187d4d3847de53f791</t>
+          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1384,17 +1384,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785352509</t>
+          <t>1785358266</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3.585624</t>
+          <t>39.03645</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x9bc12eeb5e62fdab19026dd9c59a6d3d812a1647d656ec82e9b08932d05fc32a</t>
+          <t>0x93785b3a7d055c5e2c869f1c6ed046a0c16cd38f39a06deaefeabb59967bf72c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>104.66</t>
+          <t>9.5122</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4ab76a4a1fa597ca197135de1fba0710473970c8adaef292b0acea5fe28788f8</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785350915</t>
+          <t>1785358055</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>230.655647</t>
+          <t>19.512205</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x4cc9256963002abc26b03e2de5c65df247f06de8cd8caaeab5e5ab26e126b583</t>
+          <t>0xe9c4a1ecf56e1210003b8a7c5c9dedc347ba38e18d81ea653d600cfae0406ee7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1538,22 +1538,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>200.71</t>
+          <t>1.99999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1563,27 +1563,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1608,17 +1608,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785350884</t>
+          <t>1785357507</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>442.336088</t>
+          <t>3.278672</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1635,7 +1635,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x24e8cf815969b014ea0bedb7d75a94f636bc090bb24e1787d78815f3e5a70920</t>
+          <t>0x91839b38bfe01bb58e0542f3e4844d2996af26b2e1159a45b719e543c59d0061</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1650,22 +1650,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>222.91</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1675,27 +1675,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1720,17 +1720,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785350854</t>
+          <t>1785357504</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>491.261708</t>
+          <t>18.721311</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,27 +1747,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x3729578f30b77e303f3460fb30277c2fcf85fb2049107b0dec479803d11515fe</t>
+          <t>0x12fa97e26b4d1fe9bc62fd353b41531c2d1e3636d5808e00f72cda223c5b7275</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>246.56</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.7637</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1775,11 +1771,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1787,27 +1779,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xba7019cc98094442aac3dcde57fe2ab308f401a1a9e55c251da54769aa97bf2b</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1832,7 +1824,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785350824</t>
+          <t>1785357342</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1842,7 +1834,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>543.38292</t>
+          <t>30.180033</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1859,7 +1851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xc94c50f0e5b4951b58fe15e51011784173d7fa5dea7800432eb5745354486b80</t>
+          <t>0x580c7d1b576d43e738d64f6bb0fc1b2a6d6762d7d285da29ae6814cfcd809ae2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1874,12 +1866,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1889,7 +1881,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1899,27 +1891,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd794b506219d24bb3d154b82e776aef773d5c44cbbd3c35da4709144cfa915ea</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1944,7 +1936,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785350560</t>
+          <t>1785357285</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1954,7 +1946,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>128.391304</t>
+          <t>43.715847</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1971,31 +1963,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xb98b07f3ed69cfe4b366fe2382029c20e5298a2c928a846c34e22585174d22a2</t>
+          <t>0x001e676afb8025a177fca2fafbab0c4b0588ee71a31776ebbfe2be57ac5db06e</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>503.79999</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2003,27 +2003,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x781f333038176cef4c0433e190179bdff06422f2827828187d4d3847de53f791</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2048,17 +2048,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785350534</t>
+          <t>1785352509</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>920.18263</t>
+          <t>3.585624</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2075,23 +2075,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xab48fb1edf1fe158898059d349b71fde37cf3bd3d854ff788e8cd23ed34410e3</t>
+          <t>0x9bc12eeb5e62fdab19026dd9c59a6d3d812a1647d656ec82e9b08932d05fc32a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1364.53</t>
+          <t>104.66</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2099,7 +2103,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2152,7 +2160,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785350511</t>
+          <t>1785350915</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2162,7 +2170,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2515.262673</t>
+          <t>230.655647</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2179,7 +2187,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x54afc83137f5b39b38053c7ac6e311ead709a66ed6180c1bd3071eec1df83367</t>
+          <t>0x4cc9256963002abc26b03e2de5c65df247f06de8cd8caaeab5e5ab26e126b583</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2194,22 +2202,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>82.98999</t>
+          <t>200.71</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.8613</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2219,27 +2227,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2264,17 +2272,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785348315</t>
+          <t>1785350884</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>96.35993</t>
+          <t>442.336088</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2291,7 +2299,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x0dd08bf1a086493c6e680404308a2ef5ba5a320909569533d0dc8e4ad8fdea6a</t>
+          <t>0x24e8cf815969b014ea0bedb7d75a94f636bc090bb24e1787d78815f3e5a70920</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2306,22 +2314,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>222.91</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.6925</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2331,27 +2339,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2376,7 +2384,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785347423</t>
+          <t>1785350854</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2386,7 +2394,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>72.750903</t>
+          <t>491.261708</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2403,12 +2411,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x993556c3cf15426b02b61df75d8fd0060a5e7634bee1409d10b85861b937670f</t>
+          <t>0x3729578f30b77e303f3460fb30277c2fcf85fb2049107b0dec479803d11515fe</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2418,12 +2426,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>246.56</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5112</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2433,7 +2441,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2443,27 +2451,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2488,7 +2496,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785327349</t>
+          <t>1785350824</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2498,7 +2506,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.95599</t>
+          <t>543.38292</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2515,31 +2523,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x4faded42a032bd6a91d4916349230f502e8759f9944cbfef78288354f9340944</t>
+          <t>0xc94c50f0e5b4951b58fe15e51011784173d7fa5dea7800432eb5745354486b80</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5.80275</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2547,27 +2563,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2592,17 +2608,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785325667</t>
+          <t>1785350560</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>12.120627</t>
+          <t>128.391304</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2619,28 +2635,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x39c74108b106ba600e266454471670d092342df7435c478a184f31c5880fcb1c</t>
+          <t>0xb98b07f3ed69cfe4b366fe2382029c20e5298a2c928a846c34e22585174d22a2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>503.79999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2651,27 +2667,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2696,17 +2712,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785325592</t>
+          <t>1785350534</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>378.067885</t>
+          <t>920.18263</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2723,28 +2739,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x6e97ae46202c322fcc5e7c70be0be87e1574709ea5cf0024a945e7d45d548728</t>
+          <t>0xab48fb1edf1fe158898059d349b71fde37cf3bd3d854ff788e8cd23ed34410e3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>179.29</t>
+          <t>1364.53</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4763</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2755,27 +2771,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2800,17 +2816,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785325549</t>
+          <t>1785350511</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>376.461942</t>
+          <t>2515.262673</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2827,23 +2843,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x36f17b5f896b8f5c9301b3600be88ac0007d3ce06403ffe9b13d7389417fa953</t>
+          <t>0x54afc83137f5b39b38053c7ac6e311ead709a66ed6180c1bd3071eec1df83367</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>82.98999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4775</t>
+          <t>1.8613</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2851,7 +2871,11 @@
           <t>Europa League</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2859,27 +2883,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2904,17 +2928,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785325496</t>
+          <t>1785348315</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>379.057592</t>
+          <t>96.35993</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2931,23 +2955,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xf2a45c2970e6d3af37fabd0ad34ce6efeecfe1f77cb4d5f43515fb342f7fcca2</t>
+          <t>0x0dd08bf1a086493c6e680404308a2ef5ba5a320909569533d0dc8e4ad8fdea6a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.6925</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2955,7 +2983,11 @@
           <t>Europa League</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pafos FC</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2963,27 +2995,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3008,17 +3040,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785325423</t>
+          <t>1785347423</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>378.067885</t>
+          <t>72.750903</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3035,31 +3067,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xdd031e5f334a60c24ea47a7a807f20a2bead2b80c0227808f5afa24fa77a3d06</t>
+          <t>0x993556c3cf15426b02b61df75d8fd0060a5e7634bee1409d10b85861b937670f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3067,27 +3107,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3112,17 +3152,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785325348</t>
+          <t>1785327349</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>394.805195</t>
+          <t>1.95599</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3139,7 +3179,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x4c7bd245dd4665e7f9285a58768875e4fa752d61dfc244e87f7283d2907dcb15</t>
+          <t>0x4faded42a032bd6a91d4916349230f502e8759f9944cbfef78288354f9340944</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3150,12 +3190,12 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>5.80275</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4775</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3216,7 +3256,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785325203</t>
+          <t>1785325667</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3226,7 +3266,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>383.246073</t>
+          <t>12.120627</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3243,7 +3283,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x13f73d60f1f96dd112ac2a53fa2a1a53f2e55f9bc0782a0d92732337ef7e7519</t>
+          <t>0x39c74108b106ba600e266454471670d092342df7435c478a184f31c5880fcb1c</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3254,12 +3294,12 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3290,7 +3330,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3320,7 +3360,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785325120</t>
+          <t>1785325592</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3330,7 +3370,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>166.287263</t>
+          <t>378.067885</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3347,39 +3387,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xd5759db5ffa02ee1c17bc11bdfbffb2bb73c6ff16a4fa6bf670dafa016fad84a</t>
+          <t>0x6e97ae46202c322fcc5e7c70be0be87e1574709ea5cf0024a945e7d45d548728</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>179.29</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4763</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3387,27 +3419,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3432,17 +3464,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785319802</t>
+          <t>1785325549</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>21.949861</t>
+          <t>376.461942</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3459,39 +3491,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x0fc529171c6c4f0c441f19435054a73905e5f2d2ed326778ddb79cd108c6ede1</t>
+          <t>0x36f17b5f896b8f5c9301b3600be88ac0007d3ce06403ffe9b13d7389417fa953</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3499,27 +3523,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xec30d6ed85c3851d5938108fae681432d7a35f2c741191462472aaa11d35b165</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3544,17 +3568,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785317013</t>
+          <t>1785325496</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>7.929825</t>
+          <t>379.057592</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3571,39 +3595,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x2d47f0e85c65fcb84f5de7818b5845226e8638c4dc49fb9093b9a86fe895116b</t>
+          <t>0xf2a45c2970e6d3af37fabd0ad34ce6efeecfe1f77cb4d5f43515fb342f7fcca2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11.26</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3611,27 +3627,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3656,17 +3672,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785316734</t>
+          <t>1785325423</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>20.38009</t>
+          <t>378.067885</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3683,39 +3699,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xe8fb252bc279aab31e6c6f4de96e27aca4bae9402699e12add62fecf7cc6090d</t>
+          <t>0xdd031e5f334a60c24ea47a7a807f20a2bead2b80c0227808f5afa24fa77a3d06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>190</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3723,27 +3731,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3768,17 +3776,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785314887</t>
+          <t>1785325348</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>14.280543</t>
+          <t>394.805195</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3795,39 +3803,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x988d12bce5f972af9ca3a2a7a91ba784d379a454873fb5ad9267f635cfeabaae</t>
+          <t>0x4c7bd245dd4665e7f9285a58768875e4fa752d61dfc244e87f7283d2907dcb15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>122.7</t>
+          <t>183</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3835,27 +3835,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3880,17 +3880,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785314533</t>
+          <t>1785325203</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>273.426184</t>
+          <t>383.246073</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3907,39 +3907,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x78d34863dc5be51d39c855d3868e1af787b7281b3a9ba704567d82456b113d15</t>
+          <t>0x13f73d60f1f96dd112ac2a53fa2a1a53f2e55f9bc0782a0d92732337ef7e7519</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>178.48</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3947,27 +3939,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3992,17 +3984,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785313946</t>
+          <t>1785325120</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>397.727019</t>
+          <t>166.287263</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4019,12 +4011,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x5106f8b58142e7b5c50eb3e00b44385652098e82742605b478cd59c2271a33a0</t>
+          <t>0xd5759db5ffa02ee1c17bc11bdfbffb2bb73c6ff16a4fa6bf670dafa016fad84a</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4034,7 +4026,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4104,7 +4096,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785313924</t>
+          <t>1785319802</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4114,7 +4106,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>668.523677</t>
+          <t>21.949861</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4131,12 +4123,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x6e2b82838c81a4891a03953f0ebaca7a027f4125fe2deaed52b0a95c44206dab</t>
+          <t>0x0fc529171c6c4f0c441f19435054a73905e5f2d2ed326778ddb79cd108c6ede1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
+          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4146,12 +4138,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4161,32 +4153,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>Tromso</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove vs Tromso</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xec30d6ed85c3851d5938108fae681432d7a35f2c741191462472aaa11d35b165</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4216,7 +4208,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785313712</t>
+          <t>1785317013</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4226,7 +4218,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>311.977716</t>
+          <t>7.929825</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4243,18 +4235,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x6a19a9357d731588796a01e05f4e8808a84076b6662f83356dcf6c6b00474e65</t>
+          <t>0x2d47f0e85c65fcb84f5de7818b5845226e8638c4dc49fb9093b9a86fe895116b</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4264,10 +4260,14 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4275,27 +4275,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4320,17 +4320,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785313623</t>
+          <t>1785316734</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>240.723982</t>
+          <t>20.38009</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4347,12 +4347,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x6484f0585336dfe74c291be479560bddc0741e80877c77ec5ca7fcb16d4374a5</t>
+          <t>0xe8fb252bc279aab31e6c6f4de96e27aca4bae9402699e12add62fecf7cc6090d</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4362,22 +4362,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>48.19</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4387,27 +4387,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4432,17 +4432,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785313622</t>
+          <t>1785314887</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>107.387187</t>
+          <t>14.280543</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4459,12 +4459,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x6906ce6d1047273d710579bf3d98367dbf415d0e24ecb41a8a528337a9506d3a</t>
+          <t>0x988d12bce5f972af9ca3a2a7a91ba784d379a454873fb5ad9267f635cfeabaae</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785313432</t>
+          <t>1785314533</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>12.612813</t>
+          <t>273.426184</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4571,12 +4571,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x2c365a540f836041b72448aca3516556411b341658244ff388c1692fa15d2af0</t>
+          <t>0x78d34863dc5be51d39c855d3868e1af787b7281b3a9ba704567d82456b113d15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>178.48</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785313327</t>
+          <t>1785313946</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>20.43454</t>
+          <t>397.727019</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4683,12 +4683,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xe917c05092f572e2e95fee59d14b544fb6d4c549a9e9e7399b744a830680c0ef</t>
+          <t>0x5106f8b58142e7b5c50eb3e00b44385652098e82742605b478cd59c2271a33a0</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xd22BD9e1B7916fFE0ad765642788c86b6aa29075</t>
+          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785313211</t>
+          <t>1785313924</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>13.894737</t>
+          <t>668.523677</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4795,12 +4795,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x8d92cbf4088d40c4b2b67cbb02c218ebad12e894eda090162e17c4b4ec2423ec</t>
+          <t>0x6e2b82838c81a4891a03953f0ebaca7a027f4125fe2deaed52b0a95c44206dab</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785313190</t>
+          <t>1785313712</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>11.390582</t>
+          <t>311.977716</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4907,27 +4907,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x4858e2eb7b8bfa0a43a468cd0f4c8c41ecc4c6f3ede73f30251c7922e1a658eb</t>
+          <t>0x6a19a9357d731588796a01e05f4e8808a84076b6662f83356dcf6c6b00474e65</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4935,31 +4931,27 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Tromso</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove vs Tromso</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
@@ -4992,7 +4984,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785313173</t>
+          <t>1785313623</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5002,7 +4994,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>20.387812</t>
+          <t>240.723982</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5019,23 +5011,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xf0b6c79ec7c1905e25f5ff4b6433e8122df6bb18a211b77a66cc1962804b95cb</t>
+          <t>0x6484f0585336dfe74c291be479560bddc0741e80877c77ec5ca7fcb16d4374a5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>56.13118</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5043,7 +5039,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785313133</t>
+          <t>1785313622</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>102.992991</t>
+          <t>107.387187</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5123,23 +5123,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
+          <t>0x6906ce6d1047273d710579bf3d98367dbf415d0e24ecb41a8a528337a9506d3a</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5147,7 +5151,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5155,27 +5163,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5200,7 +5208,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785282599</t>
+          <t>1785313432</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5210,7 +5218,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>101.012788</t>
+          <t>12.612813</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5227,23 +5235,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
+          <t>0x2c365a540f836041b72448aca3516556411b341658244ff388c1692fa15d2af0</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5251,7 +5263,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5304,7 +5320,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785282154</t>
+          <t>1785313327</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5314,7 +5330,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>9.181132</t>
+          <t>20.43454</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5331,23 +5347,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
+          <t>0xe917c05092f572e2e95fee59d14b544fb6d4c549a9e9e7399b744a830680c0ef</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>0xd22BD9e1B7916fFE0ad765642788c86b6aa29075</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5355,7 +5375,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5408,7 +5432,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785281829</t>
+          <t>1785313211</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5418,7 +5442,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>9.181132</t>
+          <t>13.894737</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5435,31 +5459,39 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
+          <t>0x8d92cbf4088d40c4b2b67cbb02c218ebad12e894eda090162e17c4b4ec2423ec</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.7855</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5467,27 +5499,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5512,17 +5544,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785267733</t>
+          <t>1785313190</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>14.446792</t>
+          <t>11.390582</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5539,31 +5571,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
+          <t>0x4858e2eb7b8bfa0a43a468cd0f4c8c41ecc4c6f3ede73f30251c7922e1a658eb</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4.8535</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5571,27 +5611,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5616,17 +5656,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785265830</t>
+          <t>1785313173</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>14.327675</t>
+          <t>20.387812</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5643,39 +5683,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
+          <t>0xf0b6c79ec7c1905e25f5ff4b6433e8122df6bb18a211b77a66cc1962804b95cb</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>56.13118</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.545</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>SL Benfica FC -3</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5683,27 +5715,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5728,17 +5760,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785261286</t>
+          <t>1785313133</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>102.992991</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5755,23 +5787,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
+          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5787,27 +5819,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5832,7 +5864,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785258767</t>
+          <t>1785282599</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5842,7 +5874,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>15.179487</t>
+          <t>101.012788</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5859,28 +5891,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
+          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.3425</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5891,27 +5923,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5936,17 +5968,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785253987</t>
+          <t>1785282154</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>15.737226</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5963,39 +5995,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
+          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>142.02999</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.6663</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6003,27 +6027,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6048,7 +6072,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785232812</t>
+          <t>1785281829</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6058,7 +6082,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>213.178221</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6075,39 +6099,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
+          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>193.23</t>
+          <t>4.7855</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6115,27 +6131,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6160,17 +6176,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785231712</t>
+          <t>1785267733</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>285.737523</t>
+          <t>14.446792</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6187,28 +6203,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
+          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>4.8535</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6219,27 +6235,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6264,17 +6280,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785227020</t>
+          <t>1785265830</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>20.185185</t>
+          <t>14.327675</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6291,12 +6307,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
+          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6306,22 +6322,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>104.47</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC -3</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6331,27 +6347,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6376,17 +6392,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785224116</t>
+          <t>1785261286</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>155.925373</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6403,39 +6419,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
+          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6443,27 +6451,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6488,7 +6496,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785223916</t>
+          <t>1785258767</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6498,7 +6506,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>144.089552</t>
+          <t>15.179487</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6515,28 +6523,28 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
+          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>70.47999</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6547,27 +6555,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6592,17 +6600,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785220497</t>
+          <t>1785253987</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>133.295489</t>
+          <t>15.737226</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6619,12 +6627,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
+          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6634,22 +6642,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>142.02999</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.6663</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6659,27 +6667,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6704,17 +6712,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785218406</t>
+          <t>1785232812</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>213.178221</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6731,23 +6739,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
+          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>193.23</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6755,7 +6767,11 @@
           <t>Europa League</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6778,7 +6794,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6808,7 +6824,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785213181</t>
+          <t>1785231712</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6818,7 +6834,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>254.185874</t>
+          <t>285.737523</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6835,23 +6851,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
+          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6912,7 +6928,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785189317</t>
+          <t>1785227020</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6922,7 +6938,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>20.185185</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6939,31 +6955,39 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
+          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>104.47</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6971,27 +6995,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -7016,7 +7040,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785188885</t>
+          <t>1785224116</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7026,7 +7050,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>155.925373</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7043,12 +7067,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
+          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7058,22 +7082,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7083,27 +7107,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7128,17 +7152,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785186773</t>
+          <t>1785223916</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>144.089552</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7155,27 +7179,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
+          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>70.47999</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7183,11 +7203,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7195,27 +7211,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7240,17 +7256,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785186621</t>
+          <t>1785220497</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>133.295489</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7267,7 +7283,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7352,7 +7368,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785186464</t>
+          <t>1785218406</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7379,7 +7395,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7387,31 +7403,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>85.47</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7419,27 +7427,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7464,17 +7472,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785186313</t>
+          <t>1785213181</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>254.185874</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7491,27 +7499,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7519,11 +7523,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7531,27 +7531,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7576,17 +7576,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785185868</t>
+          <t>1785189317</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7603,28 +7603,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -7635,27 +7635,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7680,17 +7680,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785182082</t>
+          <t>1785188885</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>101.408451</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7707,12 +7707,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7722,22 +7722,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>98.9699</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.9187</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7747,27 +7747,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7792,17 +7792,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785178276</t>
+          <t>1785186773</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>107.72234</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7819,7 +7819,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7827,15 +7827,19 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7843,7 +7847,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7851,27 +7859,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7896,12 +7904,12 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785157337</t>
+          <t>1785186621</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -7923,12 +7931,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7938,12 +7946,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7953,7 +7961,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7963,27 +7971,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -8008,17 +8016,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785154148</t>
+          <t>1785186464</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8035,12 +8043,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8050,12 +8058,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2.36789</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8065,7 +8073,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8075,27 +8083,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8120,17 +8128,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785186313</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>9.866208</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8147,12 +8155,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8162,12 +8170,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8177,7 +8185,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8187,27 +8195,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8232,17 +8240,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785185868</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8259,39 +8267,31 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>65.95</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -8299,27 +8299,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8344,17 +8344,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785131538</t>
+          <t>1785182082</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>177.643098</t>
+          <t>101.408451</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8371,110 +8371,774 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>98.9699</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.9187</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19577588</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1785178276</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1785438000</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>107.72234</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1785157337</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1785154148</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2.36789</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>9.866208</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>65.95</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.3713</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1785131538</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>177.643098</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>0x4a21e608f2a49d0d290d56e481810827c36c3a33b3cdfa52f47a9d205c9195a6</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>1.1213</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>SL Benfica FC</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>FC St. Gallen</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>0xfc195ce6529fc46edc42b440639cd20958bc0e5f58d88c7925cdd8563a01ebd2</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>L19577588</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
         <is>
           <t>1785123830</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>1785438000</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>65.979381</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="V80" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V80"/>
+  <dimension ref="A1:V90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x41aafd361fbdbc090304c361aa96e3d7d1986ad198e757cc1ed42d3a36d60feb</t>
+          <t>0xb25e4ba5b290a3a9d1569a873de49e2e7804f94728fefb25bc1b8eb95be5415f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,17 +542,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>1.27999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.795</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x38894b4e2a8e5d7e486f731ef1c20c3f048cafb9a2d74debe9378b5d273c6bae</t>
+          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785362098</t>
+          <t>1785369276</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>37.641278</t>
+          <t>1.61005</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xe548f2f667138f07fba5f8b56872f6e05a380228941a477ad0be28b68346322c</t>
+          <t>0xd467c62d6aa2ecab07ea59a887f62479dd15fab24cad69c0a3ebcfd8511ee9f2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.82999</t>
+          <t>59.20997</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7163</t>
+          <t>1.8825</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pafos FC 0</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -675,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x372966a20c1cb92145662d4191d1ea402efa119df308298395ad72ee4927083e</t>
+          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785362057</t>
+          <t>1785368865</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6.743442</t>
+          <t>67.09345</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xe8695e613b59508aa7ca7d5747a15d00bcfbed5e4f9653ed44f2df97fd577dfc</t>
+          <t>0x40b0eae71c0a0bd0cb5ff7ac8cacb47e388bf7fa99c7ce39154934066cd1ef74</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>64.57</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xb7cd00a89de154596fb5ed105b39373600b95939a4d9c11792f78fa57728b1fc</t>
+          <t>0xb96335c20a7cfa4ae2dd89e2cd8cdb045cc2ade055bdd75f1c34b0d83e0c1570</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785362047</t>
+          <t>1785367844</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>18.306636</t>
+          <t>249.545894</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x592ca05e5d2e598f37fef187e9bd4564705367d06c16f7ed3162e4659d773d8d</t>
+          <t>0x1ab3b75ef95b12db8d5d9c9f939cc0282aa6560cab50e9a374e87a1498fdd1c3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30.67998</t>
+          <t>38.96</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7125</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
+          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785362047</t>
+          <t>1785367720</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>43.059621</t>
+          <t>63.738241</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x57f4d612536438737c246a83cb4a06a364b2ba5f0d5bffa44b2d450c599f005c</t>
+          <t>0x95dd162a39f741daf09ec1ee6ce0f034aac56839a6ef1644143d50d2c5960b5a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pafos FC -1</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1011,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x963e029345e2eec87a8efe31b92941a4225d7b0339bd00d1d2b34c4b1ef0c388</t>
+          <t>0xb96335c20a7cfa4ae2dd89e2cd8cdb045cc2ade055bdd75f1c34b0d83e0c1570</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785362047</t>
+          <t>1785367020</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>25.723473</t>
+          <t>26.357488</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xa8f611211f253b096f6e8910a8e6d6614836d3fec79ca646c8cff14aa6cf4fe3</t>
+          <t>0x1cd4bc7ac782dfeb41e63fec20d8a9bf3592fd0bf81350409e2147d40aed1252</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2888</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x76c9ba7a74843dcbf4f3d6b5e6055a7b6d28e43c811b91c405bc0dbc814a4a23</t>
+          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785360745</t>
+          <t>1785366635</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>6.337662</t>
+          <t>9.681356</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xe8d3398ff301339e290daf01ae6876fd68d47e759c9d409ef00bbc858bae53d1</t>
+          <t>0x21690cd9f64beaf84ff39e5d9167ff61ec45c3a6878ca6af24f70cb7a7dac51f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785358486</t>
+          <t>1785366550</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>15.023729</t>
+          <t>5.423729</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x6caf1354e289f361f3527f9fab48eb02c23c0756ae001e45930362caf84237dc</t>
+          <t>0xc21d414dfe738f0cc4050e3ca76880dd3b107f7b1f09fcb635b8321fb5dc0edf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1315,23 +1315,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.7887</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1339,27 +1347,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PAOK vs FC Dynamo Kyiv</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>FC Dynamo Kyiv</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
+          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19577850</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1384,17 +1392,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785358266</t>
+          <t>1785366547</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785433500</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>39.03645</t>
+          <t>8.623729</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,7 +1419,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x93785b3a7d055c5e2c869f1c6ed046a0c16cd38f39a06deaefeabb59967bf72c</t>
+          <t>0x8c9dfb9ff69df47c8ea5940a21855ffdd8eda4b64dc38fe98e2e2934f3d87538</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1419,31 +1427,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9.5122</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.5625</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x4ab76a4a1fa597ca197135de1fba0710473970c8adaef292b0acea5fe28788f8</t>
+          <t>0x8b7152b0bd00d827f374ce80d037c7f4423fc9121c18baeb864ae421a667b40f</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785358055</t>
+          <t>1785365217</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>19.512205</t>
+          <t>2.275556</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,39 +1523,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xe9c4a1ecf56e1210003b8a7c5c9dedc347ba38e18d81ea653d600cfae0406ee7</t>
+          <t>0x3657290ba2b8218d1552b68d792780f1911e7dc3600c885e6f81b7b21a4f4771</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.99999</t>
+          <t>1.66999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1563,27 +1555,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
+          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1608,17 +1600,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785357507</t>
+          <t>1785365171</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3.278672</t>
+          <t>2.113911</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1635,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x91839b38bfe01bb58e0542f3e4844d2996af26b2e1159a45b719e543c59d0061</t>
+          <t>0x41aafd361fbdbc090304c361aa96e3d7d1986ad198e757cc1ed42d3a36d60feb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1643,31 +1635,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1675,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
+          <t>0x38894b4e2a8e5d7e486f731ef1c20c3f048cafb9a2d74debe9378b5d273c6bae</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1720,17 +1704,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785357504</t>
+          <t>1785362098</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>18.721311</t>
+          <t>37.641278</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,31 +1731,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x12fa97e26b4d1fe9bc62fd353b41531c2d1e3636d5808e00f72cda223c5b7275</t>
+          <t>0xe548f2f667138f07fba5f8b56872f6e05a380228941a477ad0be28b68346322c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>4.82999</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.7637</t>
+          <t>1.7163</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pafos FC 0</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1794,7 +1786,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xba7019cc98094442aac3dcde57fe2ab308f401a1a9e55c251da54769aa97bf2b</t>
+          <t>0x372966a20c1cb92145662d4191d1ea402efa119df308298395ad72ee4927083e</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1824,7 +1816,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785357342</t>
+          <t>1785362057</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1834,7 +1826,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>30.180033</t>
+          <t>6.743442</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1851,7 +1843,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x580c7d1b576d43e738d64f6bb0fc1b2a6d6762d7d285da29ae6814cfcd809ae2</t>
+          <t>0xe8695e613b59508aa7ca7d5747a15d00bcfbed5e4f9653ed44f2df97fd577dfc</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1871,7 +1863,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1881,32 +1873,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>Pafos FC</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pafos FC vs Hajduk Split</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Pafos FC</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>Hajduk Split</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Pafos FC vs Hajduk Split</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Pafos FC</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Hajduk Split</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xd794b506219d24bb3d154b82e776aef773d5c44cbbd3c35da4709144cfa915ea</t>
+          <t>0xb7cd00a89de154596fb5ed105b39373600b95939a4d9c11792f78fa57728b1fc</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1936,7 +1928,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785357285</t>
+          <t>1785362047</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1946,7 +1938,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>43.715847</t>
+          <t>18.306636</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1963,7 +1955,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x001e676afb8025a177fca2fafbab0c4b0588ee71a31776ebbfe2be57ac5db06e</t>
+          <t>0x592ca05e5d2e598f37fef187e9bd4564705367d06c16f7ed3162e4659d773d8d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1978,12 +1970,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>30.67998</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.7125</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1993,7 +1985,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2003,27 +1995,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x781f333038176cef4c0433e190179bdff06422f2827828187d4d3847de53f791</t>
+          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2048,17 +2040,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785352509</t>
+          <t>1785362047</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>3.585624</t>
+          <t>43.059621</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2075,7 +2067,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x9bc12eeb5e62fdab19026dd9c59a6d3d812a1647d656ec82e9b08932d05fc32a</t>
+          <t>0x57f4d612536438737c246a83cb4a06a364b2ba5f0d5bffa44b2d450c599f005c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2090,22 +2082,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>104.66</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Pafos FC -1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2115,27 +2107,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x963e029345e2eec87a8efe31b92941a4225d7b0339bd00d1d2b34c4b1ef0c388</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2160,7 +2152,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785350915</t>
+          <t>1785362047</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2170,7 +2162,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>230.655647</t>
+          <t>25.723473</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2187,7 +2179,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x4cc9256963002abc26b03e2de5c65df247f06de8cd8caaeab5e5ab26e126b583</t>
+          <t>0xa8f611211f253b096f6e8910a8e6d6614836d3fec79ca646c8cff14aa6cf4fe3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2202,22 +2194,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>200.71</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2227,27 +2219,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x76c9ba7a74843dcbf4f3d6b5e6055a7b6d28e43c811b91c405bc0dbc814a4a23</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2272,7 +2264,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785350884</t>
+          <t>1785360745</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2282,7 +2274,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>442.336088</t>
+          <t>6.337662</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2299,7 +2291,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x24e8cf815969b014ea0bedb7d75a94f636bc090bb24e1787d78815f3e5a70920</t>
+          <t>0xe8d3398ff301339e290daf01ae6876fd68d47e759c9d409ef00bbc858bae53d1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2314,22 +2306,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>222.91</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2339,27 +2331,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2384,7 +2376,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785350854</t>
+          <t>1785358486</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2394,7 +2386,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>491.261708</t>
+          <t>15.023729</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2411,7 +2403,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x3729578f30b77e303f3460fb30277c2fcf85fb2049107b0dec479803d11515fe</t>
+          <t>0x6caf1354e289f361f3527f9fab48eb02c23c0756ae001e45930362caf84237dc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2419,19 +2411,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>246.56</t>
+          <t>30.79</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2439,11 +2427,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2451,27 +2435,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2496,17 +2480,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785350824</t>
+          <t>1785358266</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>543.38292</t>
+          <t>39.03645</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2523,7 +2507,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xc94c50f0e5b4951b58fe15e51011784173d7fa5dea7800432eb5745354486b80</t>
+          <t>0x93785b3a7d055c5e2c869f1c6ed046a0c16cd38f39a06deaefeabb59967bf72c</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2538,22 +2522,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>9.5122</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2563,27 +2547,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4ab76a4a1fa597ca197135de1fba0710473970c8adaef292b0acea5fe28788f8</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2608,17 +2592,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785350560</t>
+          <t>1785358055</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>128.391304</t>
+          <t>19.512205</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2635,31 +2619,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xb98b07f3ed69cfe4b366fe2382029c20e5298a2c928a846c34e22585174d22a2</t>
+          <t>0xe9c4a1ecf56e1210003b8a7c5c9dedc347ba38e18d81ea653d600cfae0406ee7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>503.79999</t>
+          <t>1.99999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2667,27 +2659,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2712,17 +2704,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785350534</t>
+          <t>1785357507</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>920.18263</t>
+          <t>3.278672</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2739,31 +2731,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xab48fb1edf1fe158898059d349b71fde37cf3bd3d854ff788e8cd23ed34410e3</t>
+          <t>0x91839b38bfe01bb58e0542f3e4844d2996af26b2e1159a45b719e543c59d0061</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1364.53</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2771,27 +2771,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2816,17 +2816,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785350511</t>
+          <t>1785357504</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2515.262673</t>
+          <t>18.721311</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2843,39 +2843,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x54afc83137f5b39b38053c7ac6e311ead709a66ed6180c1bd3071eec1df83367</t>
+          <t>0x12fa97e26b4d1fe9bc62fd353b41531c2d1e3636d5808e00f72cda223c5b7275</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>82.98999</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.8613</t>
+          <t>1.7637</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Maccabi Tel Aviv</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2883,27 +2875,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
+          <t>0xba7019cc98094442aac3dcde57fe2ab308f401a1a9e55c251da54769aa97bf2b</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2928,17 +2920,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785348315</t>
+          <t>1785357342</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>96.35993</t>
+          <t>30.180033</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2955,7 +2947,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x0dd08bf1a086493c6e680404308a2ef5ba5a320909569533d0dc8e4ad8fdea6a</t>
+          <t>0x580c7d1b576d43e738d64f6bb0fc1b2a6d6762d7d285da29ae6814cfcd809ae2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2970,39 +2962,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.6925</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Pafos FC vs Hajduk Split</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>Pafos FC</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Pafos FC vs Hajduk Split</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Pafos FC</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Hajduk Split</t>
@@ -3010,7 +3002,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
+          <t>0xd794b506219d24bb3d154b82e776aef773d5c44cbbd3c35da4709144cfa915ea</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3040,7 +3032,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785347423</t>
+          <t>1785357285</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3050,7 +3042,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>72.750903</t>
+          <t>43.715847</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3067,12 +3059,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x993556c3cf15426b02b61df75d8fd0060a5e7634bee1409d10b85861b937670f</t>
+          <t>0x001e676afb8025a177fca2fafbab0c4b0588ee71a31776ebbfe2be57ac5db06e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3082,22 +3074,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5112</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3107,27 +3099,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0x781f333038176cef4c0433e190179bdff06422f2827828187d4d3847de53f791</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3152,17 +3144,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785327349</t>
+          <t>1785352509</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.95599</t>
+          <t>3.585624</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3179,31 +3171,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x4faded42a032bd6a91d4916349230f502e8759f9944cbfef78288354f9340944</t>
+          <t>0x9bc12eeb5e62fdab19026dd9c59a6d3d812a1647d656ec82e9b08932d05fc32a</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5.80275</t>
+          <t>104.66</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3211,27 +3211,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3256,17 +3256,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785325667</t>
+          <t>1785350915</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>12.120627</t>
+          <t>230.655647</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3283,31 +3283,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x39c74108b106ba600e266454471670d092342df7435c478a184f31c5880fcb1c</t>
+          <t>0x4cc9256963002abc26b03e2de5c65df247f06de8cd8caaeab5e5ab26e126b583</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>200.71</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3315,27 +3323,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3360,17 +3368,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785325592</t>
+          <t>1785350884</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>378.067885</t>
+          <t>442.336088</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3387,31 +3395,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x6e97ae46202c322fcc5e7c70be0be87e1574709ea5cf0024a945e7d45d548728</t>
+          <t>0x24e8cf815969b014ea0bedb7d75a94f636bc090bb24e1787d78815f3e5a70920</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>179.29</t>
+          <t>222.91</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4763</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3419,27 +3435,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3464,17 +3480,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785325549</t>
+          <t>1785350854</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>376.461942</t>
+          <t>491.261708</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3491,31 +3507,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x36f17b5f896b8f5c9301b3600be88ac0007d3ce06403ffe9b13d7389417fa953</t>
+          <t>0x3729578f30b77e303f3460fb30277c2fcf85fb2049107b0dec479803d11515fe</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>246.56</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4775</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3523,27 +3547,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3568,17 +3592,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785325496</t>
+          <t>1785350824</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>379.057592</t>
+          <t>543.38292</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3595,31 +3619,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xf2a45c2970e6d3af37fabd0ad34ce6efeecfe1f77cb4d5f43515fb342f7fcca2</t>
+          <t>0xc94c50f0e5b4951b58fe15e51011784173d7fa5dea7800432eb5745354486b80</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3627,27 +3659,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3672,17 +3704,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785325423</t>
+          <t>1785350560</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>378.067885</t>
+          <t>128.391304</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3699,28 +3731,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xdd031e5f334a60c24ea47a7a807f20a2bead2b80c0227808f5afa24fa77a3d06</t>
+          <t>0xb98b07f3ed69cfe4b366fe2382029c20e5298a2c928a846c34e22585174d22a2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>503.79999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3731,27 +3763,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3776,17 +3808,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785325348</t>
+          <t>1785350534</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>394.805195</t>
+          <t>920.18263</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3803,28 +3835,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x4c7bd245dd4665e7f9285a58768875e4fa752d61dfc244e87f7283d2907dcb15</t>
+          <t>0xab48fb1edf1fe158898059d349b71fde37cf3bd3d854ff788e8cd23ed34410e3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>1364.53</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4775</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3835,27 +3867,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3880,17 +3912,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785325203</t>
+          <t>1785350511</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>383.246073</t>
+          <t>2515.262673</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3907,23 +3939,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x13f73d60f1f96dd112ac2a53fa2a1a53f2e55f9bc0782a0d92732337ef7e7519</t>
+          <t>0x54afc83137f5b39b38053c7ac6e311ead709a66ed6180c1bd3071eec1df83367</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>82.98999</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.8613</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3931,7 +3967,11 @@
           <t>Europa League</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3939,27 +3979,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3984,17 +4024,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785325120</t>
+          <t>1785348315</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>166.287263</t>
+          <t>96.35993</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4011,12 +4051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xd5759db5ffa02ee1c17bc11bdfbffb2bb73c6ff16a4fa6bf670dafa016fad84a</t>
+          <t>0x0dd08bf1a086493c6e680404308a2ef5ba5a320909569533d0dc8e4ad8fdea6a</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4026,22 +4066,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.6925</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4051,27 +4091,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4096,7 +4136,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785319802</t>
+          <t>1785347423</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>21.949861</t>
+          <t>72.750903</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4123,12 +4163,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x0fc529171c6c4f0c441f19435054a73905e5f2d2ed326778ddb79cd108c6ede1</t>
+          <t>0x993556c3cf15426b02b61df75d8fd0060a5e7634bee1409d10b85861b937670f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4138,12 +4178,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4153,7 +4193,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4163,27 +4203,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xec30d6ed85c3851d5938108fae681432d7a35f2c741191462472aaa11d35b165</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4208,7 +4248,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785317013</t>
+          <t>1785327349</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4218,7 +4258,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>7.929825</t>
+          <t>1.95599</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4235,39 +4275,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x2d47f0e85c65fcb84f5de7818b5845226e8638c4dc49fb9093b9a86fe895116b</t>
+          <t>0x4faded42a032bd6a91d4916349230f502e8759f9944cbfef78288354f9340944</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11.26</t>
+          <t>5.80275</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4275,27 +4307,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4320,17 +4352,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785316734</t>
+          <t>1785325667</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>20.38009</t>
+          <t>12.120627</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4347,39 +4379,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xe8fb252bc279aab31e6c6f4de96e27aca4bae9402699e12add62fecf7cc6090d</t>
+          <t>0x39c74108b106ba600e266454471670d092342df7435c478a184f31c5880fcb1c</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4387,27 +4411,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4432,17 +4456,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785314887</t>
+          <t>1785325592</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>14.280543</t>
+          <t>378.067885</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4459,39 +4483,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x988d12bce5f972af9ca3a2a7a91ba784d379a454873fb5ad9267f635cfeabaae</t>
+          <t>0x6e97ae46202c322fcc5e7c70be0be87e1574709ea5cf0024a945e7d45d548728</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>122.7</t>
+          <t>179.29</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4763</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4499,27 +4515,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4544,17 +4560,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785314533</t>
+          <t>1785325549</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>273.426184</t>
+          <t>376.461942</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4571,39 +4587,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x78d34863dc5be51d39c855d3868e1af787b7281b3a9ba704567d82456b113d15</t>
+          <t>0x36f17b5f896b8f5c9301b3600be88ac0007d3ce06403ffe9b13d7389417fa953</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>178.48</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4611,27 +4619,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4656,17 +4664,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785313946</t>
+          <t>1785325496</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>397.727019</t>
+          <t>379.057592</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4683,39 +4691,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x5106f8b58142e7b5c50eb3e00b44385652098e82742605b478cd59c2271a33a0</t>
+          <t>0xf2a45c2970e6d3af37fabd0ad34ce6efeecfe1f77cb4d5f43515fb342f7fcca2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4723,27 +4723,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4768,17 +4768,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785313924</t>
+          <t>1785325423</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>668.523677</t>
+          <t>378.067885</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4795,39 +4795,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x6e2b82838c81a4891a03953f0ebaca7a027f4125fe2deaed52b0a95c44206dab</t>
+          <t>0xdd031e5f334a60c24ea47a7a807f20a2bead2b80c0227808f5afa24fa77a3d06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>190</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4835,27 +4827,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4880,17 +4872,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785313712</t>
+          <t>1785325348</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>311.977716</t>
+          <t>394.805195</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4907,28 +4899,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x6a19a9357d731588796a01e05f4e8808a84076b6662f83356dcf6c6b00474e65</t>
+          <t>0x4c7bd245dd4665e7f9285a58768875e4fa752d61dfc244e87f7283d2907dcb15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>183</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4939,27 +4931,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4984,17 +4976,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785313623</t>
+          <t>1785325203</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>240.723982</t>
+          <t>383.246073</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5011,39 +5003,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x6484f0585336dfe74c291be479560bddc0741e80877c77ec5ca7fcb16d4374a5</t>
+          <t>0x13f73d60f1f96dd112ac2a53fa2a1a53f2e55f9bc0782a0d92732337ef7e7519</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>48.19</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5051,27 +5035,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5096,17 +5080,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785313622</t>
+          <t>1785325120</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>107.387187</t>
+          <t>166.287263</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5123,12 +5107,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x6906ce6d1047273d710579bf3d98367dbf415d0e24ecb41a8a528337a9506d3a</t>
+          <t>0xd5759db5ffa02ee1c17bc11bdfbffb2bb73c6ff16a4fa6bf670dafa016fad84a</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5138,7 +5122,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5208,7 +5192,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785313432</t>
+          <t>1785319802</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5218,7 +5202,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>12.612813</t>
+          <t>21.949861</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5235,12 +5219,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x2c365a540f836041b72448aca3516556411b341658244ff388c1692fa15d2af0</t>
+          <t>0x0fc529171c6c4f0c441f19435054a73905e5f2d2ed326778ddb79cd108c6ede1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5250,12 +5234,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5265,32 +5249,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>Tromso</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove vs Tromso</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xec30d6ed85c3851d5938108fae681432d7a35f2c741191462472aaa11d35b165</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5320,7 +5304,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785313327</t>
+          <t>1785317013</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5330,7 +5314,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>20.43454</t>
+          <t>7.929825</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5347,12 +5331,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xe917c05092f572e2e95fee59d14b544fb6d4c549a9e9e7399b744a830680c0ef</t>
+          <t>0x2d47f0e85c65fcb84f5de7818b5845226e8638c4dc49fb9093b9a86fe895116b</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xd22BD9e1B7916fFE0ad765642788c86b6aa29075</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5362,22 +5346,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5387,27 +5371,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5432,17 +5416,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785313211</t>
+          <t>1785316734</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>13.894737</t>
+          <t>20.38009</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5459,12 +5443,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x8d92cbf4088d40c4b2b67cbb02c218ebad12e894eda090162e17c4b4ec2423ec</t>
+          <t>0xe8fb252bc279aab31e6c6f4de96e27aca4bae9402699e12add62fecf7cc6090d</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5474,22 +5458,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5499,27 +5483,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5544,17 +5528,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785313190</t>
+          <t>1785314887</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>11.390582</t>
+          <t>14.280543</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5571,12 +5555,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x4858e2eb7b8bfa0a43a468cd0f4c8c41ecc4c6f3ede73f30251c7922e1a658eb</t>
+          <t>0x988d12bce5f972af9ca3a2a7a91ba784d379a454873fb5ad9267f635cfeabaae</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5586,12 +5570,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5656,7 +5640,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785313173</t>
+          <t>1785314533</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5666,7 +5650,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>20.387812</t>
+          <t>273.426184</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5683,23 +5667,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xf0b6c79ec7c1905e25f5ff4b6433e8122df6bb18a211b77a66cc1962804b95cb</t>
+          <t>0x78d34863dc5be51d39c855d3868e1af787b7281b3a9ba704567d82456b113d15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>56.13118</t>
+          <t>178.48</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5707,7 +5695,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5760,7 +5752,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785313133</t>
+          <t>1785313946</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5770,7 +5762,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>102.992991</t>
+          <t>397.727019</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5787,23 +5779,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
+          <t>0x5106f8b58142e7b5c50eb3e00b44385652098e82742605b478cd59c2271a33a0</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5811,7 +5807,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5819,27 +5819,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785282599</t>
+          <t>1785313924</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>101.012788</t>
+          <t>668.523677</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5891,23 +5891,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
+          <t>0x6e2b82838c81a4891a03953f0ebaca7a027f4125fe2deaed52b0a95c44206dab</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5915,7 +5919,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5968,7 +5976,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785282154</t>
+          <t>1785313712</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5978,7 +5986,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>9.181132</t>
+          <t>311.977716</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5995,23 +6003,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
+          <t>0x6a19a9357d731588796a01e05f4e8808a84076b6662f83356dcf6c6b00474e65</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6072,7 +6080,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785281829</t>
+          <t>1785313623</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6082,7 +6090,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>9.181132</t>
+          <t>240.723982</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6099,31 +6107,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
+          <t>0x6484f0585336dfe74c291be479560bddc0741e80877c77ec5ca7fcb16d4374a5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4.7855</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6131,27 +6147,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6176,17 +6192,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785267733</t>
+          <t>1785313622</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>14.446792</t>
+          <t>107.387187</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6203,31 +6219,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
+          <t>0x6906ce6d1047273d710579bf3d98367dbf415d0e24ecb41a8a528337a9506d3a</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4.8535</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6235,27 +6259,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6280,17 +6304,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785265830</t>
+          <t>1785313432</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>14.327675</t>
+          <t>12.612813</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6307,12 +6331,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
+          <t>0x2c365a540f836041b72448aca3516556411b341658244ff388c1692fa15d2af0</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6322,22 +6346,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SL Benfica FC -3</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6347,27 +6371,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6392,17 +6416,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785261286</t>
+          <t>1785313327</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>20.43454</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6419,23 +6443,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
+          <t>0xe917c05092f572e2e95fee59d14b544fb6d4c549a9e9e7399b744a830680c0ef</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>0xd22BD9e1B7916fFE0ad765642788c86b6aa29075</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6443,7 +6471,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6496,7 +6528,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785258767</t>
+          <t>1785313211</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6506,7 +6538,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>15.179487</t>
+          <t>13.894737</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6523,31 +6555,39 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
+          <t>0x8d92cbf4088d40c4b2b67cbb02c218ebad12e894eda090162e17c4b4ec2423ec</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.3425</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6555,27 +6595,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6600,17 +6640,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785253987</t>
+          <t>1785313190</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>15.737226</t>
+          <t>11.390582</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6627,12 +6667,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
+          <t>0x4858e2eb7b8bfa0a43a468cd0f4c8c41ecc4c6f3ede73f30251c7922e1a658eb</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6642,22 +6682,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>142.02999</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.6663</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6667,27 +6707,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6712,7 +6752,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785232812</t>
+          <t>1785313173</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6722,7 +6762,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>213.178221</t>
+          <t>20.387812</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6739,39 +6779,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
+          <t>0xf0b6c79ec7c1905e25f5ff4b6433e8122df6bb18a211b77a66cc1962804b95cb</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>193.23</t>
+          <t>56.13118</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.545</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6779,27 +6811,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6824,7 +6856,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785231712</t>
+          <t>1785313133</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6834,7 +6866,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>285.737523</t>
+          <t>102.992991</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6851,23 +6883,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
+          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6883,27 +6915,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6928,7 +6960,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785227020</t>
+          <t>1785282599</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6938,7 +6970,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>20.185185</t>
+          <t>101.012788</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6955,39 +6987,31 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
+          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>104.47</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6995,27 +7019,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -7040,7 +7064,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785224116</t>
+          <t>1785282154</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7050,7 +7074,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>155.925373</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7067,39 +7091,31 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
+          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7107,27 +7123,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7152,7 +7168,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785223916</t>
+          <t>1785281829</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7162,7 +7178,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>144.089552</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7179,28 +7195,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
+          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>70.47999</t>
+          <t>4.7855</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -7211,27 +7227,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7256,17 +7272,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785220497</t>
+          <t>1785267733</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>133.295489</t>
+          <t>14.446792</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7283,39 +7299,31 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
+          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>4.8535</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7323,27 +7331,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7368,17 +7376,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785218406</t>
+          <t>1785265830</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>14.327675</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7395,7 +7403,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
+          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7403,23 +7411,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SL Benfica FC -3</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7427,27 +7443,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
+          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7472,17 +7488,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785213181</t>
+          <t>1785261286</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>254.185874</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7499,23 +7515,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
+          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7576,7 +7592,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785189317</t>
+          <t>1785258767</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7586,7 +7602,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>15.179487</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7603,28 +7619,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
+          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -7635,27 +7651,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7680,17 +7696,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785188885</t>
+          <t>1785253987</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>15.737226</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7707,12 +7723,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
+          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7722,22 +7738,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>142.02999</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.6663</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7747,27 +7763,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7792,17 +7808,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785186773</t>
+          <t>1785232812</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>213.178221</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7819,12 +7835,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
+          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7834,22 +7850,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>193.23</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7859,27 +7875,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7904,17 +7920,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785186621</t>
+          <t>1785231712</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>285.737523</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7931,27 +7947,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7959,11 +7971,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7971,27 +7979,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -8016,17 +8024,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785186464</t>
+          <t>1785227020</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>20.185185</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8043,12 +8051,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8058,22 +8066,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>104.47</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8083,27 +8091,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8128,17 +8136,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785186313</t>
+          <t>1785224116</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>155.925373</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8155,12 +8163,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8170,22 +8178,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8195,27 +8203,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8240,17 +8248,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785185868</t>
+          <t>1785223916</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>144.089552</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8267,28 +8275,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>70.47999</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8299,27 +8307,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8344,17 +8352,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785182082</t>
+          <t>1785220497</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>101.408451</t>
+          <t>133.295489</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8371,12 +8379,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8386,22 +8394,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>98.9699</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.9187</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8411,27 +8419,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8456,17 +8464,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785178276</t>
+          <t>1785218406</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>107.72234</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8483,7 +8491,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8494,17 +8502,17 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>85.47</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -8530,7 +8538,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8560,7 +8568,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785157337</t>
+          <t>1785213181</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8570,7 +8578,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>254.185874</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8587,27 +8595,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8615,11 +8619,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Besiktas</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -8627,27 +8627,27 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785154148</t>
+          <t>1785189317</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8699,27 +8699,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2.36789</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8727,11 +8723,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Besiktas</t>
-        </is>
-      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -8739,27 +8731,27 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -8784,7 +8776,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785188885</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8794,7 +8786,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>9.866208</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8811,12 +8803,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8826,12 +8818,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8841,7 +8833,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8851,27 +8843,27 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8896,17 +8888,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785186773</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8923,12 +8915,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8938,22 +8930,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>65.95</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8963,27 +8955,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -9008,17 +9000,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785131538</t>
+          <t>1785186621</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>177.643098</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9035,110 +9027,1214 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1785186464</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1785186313</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1785185868</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.2662</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1785182082</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>101.408451</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>98.9699</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.9187</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>L19577588</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1785178276</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1785438000</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>107.72234</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1785157337</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1785154148</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2.36789</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>9.866208</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>65.95</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.3713</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1785131538</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>177.643098</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>0x4a21e608f2a49d0d290d56e481810827c36c3a33b3cdfa52f47a9d205c9195a6</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>1.1213</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>SL Benfica FC</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>FC St. Gallen</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>0xfc195ce6529fc46edc42b440639cd20958bc0e5f58d88c7925cdd8563a01ebd2</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>L19577588</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
         <is>
           <t>1785123830</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>1785438000</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>65.979381</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="U90" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
+      <c r="V90" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V90"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xb25e4ba5b290a3a9d1569a873de49e2e7804f94728fefb25bc1b8eb95be5415f</t>
+          <t>0x1aea7ce83ddf2c16d6d78808082e2a4447df99dad359f5db36f9cdef821b971c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.27999</t>
+          <t>49.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
+          <t>0x6abf1fe8c0ab5d6643454c0862ea120137474f1adf2ddb35a78e06cee0a1e961</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785369276</t>
+          <t>1785374463</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.61005</t>
+          <t>91.631336</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xd467c62d6aa2ecab07ea59a887f62479dd15fab24cad69c0a3ebcfd8511ee9f2</t>
+          <t>0x0d60e14be6485d6af0a032b19bfc014d50bdd434c6f2c1a5557d1a7320edd82e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -650,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>59.20997</t>
+          <t>36.74</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.8825</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>PAOK -0.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
+          <t>0xc273fb0d8cb04f7d1e39a7dc030231f54f40d91616b1ffb8e41b34c74f3712de</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785368865</t>
+          <t>1785374440</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>67.09345</t>
+          <t>67.723502</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x40b0eae71c0a0bd0cb5ff7ac8cacb47e388bf7fa99c7ce39154934066cd1ef74</t>
+          <t>0x5f8c940baa6470cf16ca3dc71e0168bd2f26563ea996fc4cd0d03926f6f73b73</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,22 +770,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>64.57</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Maccabi Tel Aviv -1.5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -787,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PAOK vs FC Dynamo Kyiv</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FC Dynamo Kyiv</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xb96335c20a7cfa4ae2dd89e2cd8cdb045cc2ade055bdd75f1c34b0d83e0c1570</t>
+          <t>0x367cf8e90c51f0117ab2bbcf8ae8d0fe38dd56a5b21aaf98a94d7e6d6eda4df6</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19577850</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785367844</t>
+          <t>1785374215</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785433500</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>249.545894</t>
+          <t>2.686717</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,39 +867,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x1ab3b75ef95b12db8d5d9c9f939cc0282aa6560cab50e9a374e87a1498fdd1c3</t>
+          <t>0x3c260355924102caec0b38bcb930951d38289f2f82dee3c74f62f48685499052</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>38.96</t>
+          <t>30.01999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.5625</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -899,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
+          <t>0x8b7152b0bd00d827f374ce80d037c7f4423fc9121c18baeb864ae421a667b40f</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785367720</t>
+          <t>1785373649</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>63.738241</t>
+          <t>53.368871</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x95dd162a39f741daf09ec1ee6ce0f034aac56839a6ef1644143d50d2c5960b5a</t>
+          <t>0x99448357b2426bacd925223de1d6f212b927193aaf4c97f727b6ce05761ee389</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.5938</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1011,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PAOK vs FC Dynamo Kyiv</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>FC Dynamo Kyiv</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xb96335c20a7cfa4ae2dd89e2cd8cdb045cc2ade055bdd75f1c34b0d83e0c1570</t>
+          <t>0x781f333038176cef4c0433e190179bdff06422f2827828187d4d3847de53f791</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19577850</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785367020</t>
+          <t>1785372954</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785433500</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>26.357488</t>
+          <t>3.873684</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x1cd4bc7ac782dfeb41e63fec20d8a9bf3592fd0bf81350409e2147d40aed1252</t>
+          <t>0xb1d69406483c4d5da20cd936d46b4201485f7dab32ebd7e9e43c87c5a5828c7a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.1838</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
+          <t>0x49e2852fda6d5fbb44e4cc626e2ace2f31139b2b56c37dc1493a8b51cc66820e</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785366635</t>
+          <t>1785372862</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>9.681356</t>
+          <t>54.802721</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,39 +1195,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x21690cd9f64beaf84ff39e5d9167ff61ec45c3a6878ca6af24f70cb7a7dac51f</t>
+          <t>0xf253ffdfa6bd50e48d7bda60ad225c2ee338b86b6e56850ade26b1a3b4d009bf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9737E0E3E8EE2DD6B8A7E19D1507EcB3221b5483</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1235,27 +1227,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
+          <t>0x4c9723bc7def26f86e0656a3de22257af36e6760bd8d8ed81a5f8b03d2039e77</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1272,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785366550</t>
+          <t>1785370874</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>5.423729</t>
+          <t>11.666667</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,39 +1299,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xc21d414dfe738f0cc4050e3ca76880dd3b107f7b1f09fcb635b8321fb5dc0edf</t>
+          <t>0xe8f885df4c805c1f7e67de64b4b6965f588f95ad27de1ec6c34b82740207ca09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1347,27 +1331,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
+          <t>0x4c9723bc7def26f86e0656a3de22257af36e6760bd8d8ed81a5f8b03d2039e77</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1392,17 +1376,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785366547</t>
+          <t>1785370874</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>8.623729</t>
+          <t>4.761905</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,28 +1403,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x8c9dfb9ff69df47c8ea5940a21855ffdd8eda4b64dc38fe98e2e2934f3d87538</t>
+          <t>0x162a97e4490bb57d534ff14799f7e19ae8f7956798df9232d7abbb1965e19b36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x06a603b688E676702ec63D735CAe4A57ff71B3e1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5625</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1451,27 +1435,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x8b7152b0bd00d827f374ce80d037c7f4423fc9121c18baeb864ae421a667b40f</t>
+          <t>0x4c9723bc7def26f86e0656a3de22257af36e6760bd8d8ed81a5f8b03d2039e77</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1480,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785365217</t>
+          <t>1785370869</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.275556</t>
+          <t>11.904762</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,28 +1507,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x3657290ba2b8218d1552b68d792780f1911e7dc3600c885e6f81b7b21a4f4771</t>
+          <t>0x6aef40c5e87de9ce8b5065247616823179fafefd3d12456fea34f6103b9b0111</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.66999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.4125</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1555,27 +1539,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PAOK vs FC Dynamo Kyiv</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>FC Dynamo Kyiv</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
+          <t>0x4c9723bc7def26f86e0656a3de22257af36e6760bd8d8ed81a5f8b03d2039e77</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19577850</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1600,17 +1584,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785365171</t>
+          <t>1785370858</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785433500</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.113911</t>
+          <t>12.121212</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,7 +1611,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x41aafd361fbdbc090304c361aa96e3d7d1986ad198e757cc1ed42d3a36d60feb</t>
+          <t>0xb25e4ba5b290a3a9d1569a873de49e2e7804f94728fefb25bc1b8eb95be5415f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1638,17 +1622,17 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>1.27999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.795</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1659,27 +1643,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x38894b4e2a8e5d7e486f731ef1c20c3f048cafb9a2d74debe9378b5d273c6bae</t>
+          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,17 +1688,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785362098</t>
+          <t>1785369276</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>37.641278</t>
+          <t>1.61005</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,7 +1715,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xe548f2f667138f07fba5f8b56872f6e05a380228941a477ad0be28b68346322c</t>
+          <t>0xd467c62d6aa2ecab07ea59a887f62479dd15fab24cad69c0a3ebcfd8511ee9f2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1746,12 +1730,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.82999</t>
+          <t>59.20997</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.7163</t>
+          <t>1.8825</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1761,7 +1745,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pafos FC 0</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1771,27 +1755,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x372966a20c1cb92145662d4191d1ea402efa119df308298395ad72ee4927083e</t>
+          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1816,17 +1800,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785362057</t>
+          <t>1785368865</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>6.743442</t>
+          <t>67.09345</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,12 +1827,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xe8695e613b59508aa7ca7d5747a15d00bcfbed5e4f9653ed44f2df97fd577dfc</t>
+          <t>0x40b0eae71c0a0bd0cb5ff7ac8cacb47e388bf7fa99c7ce39154934066cd1ef74</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1858,12 +1842,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>64.57</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1873,7 +1857,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1883,27 +1867,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xb7cd00a89de154596fb5ed105b39373600b95939a4d9c11792f78fa57728b1fc</t>
+          <t>0xb96335c20a7cfa4ae2dd89e2cd8cdb045cc2ade055bdd75f1c34b0d83e0c1570</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1928,17 +1912,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785362047</t>
+          <t>1785367844</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>18.306636</t>
+          <t>249.545894</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,7 +1939,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x592ca05e5d2e598f37fef187e9bd4564705367d06c16f7ed3162e4659d773d8d</t>
+          <t>0x1ab3b75ef95b12db8d5d9c9f939cc0282aa6560cab50e9a374e87a1498fdd1c3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1970,22 +1954,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30.67998</t>
+          <t>38.96</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.7125</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1995,27 +1979,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
+          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2040,17 +2024,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785362047</t>
+          <t>1785367720</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>43.059621</t>
+          <t>63.738241</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2067,12 +2051,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x57f4d612536438737c246a83cb4a06a364b2ba5f0d5bffa44b2d450c599f005c</t>
+          <t>0x95dd162a39f741daf09ec1ee6ce0f034aac56839a6ef1644143d50d2c5960b5a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2082,22 +2066,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pafos FC -1</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2107,27 +2091,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x963e029345e2eec87a8efe31b92941a4225d7b0339bd00d1d2b34c4b1ef0c388</t>
+          <t>0xb96335c20a7cfa4ae2dd89e2cd8cdb045cc2ade055bdd75f1c34b0d83e0c1570</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2152,17 +2136,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785362047</t>
+          <t>1785367020</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>25.723473</t>
+          <t>26.357488</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2179,7 +2163,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xa8f611211f253b096f6e8910a8e6d6614836d3fec79ca646c8cff14aa6cf4fe3</t>
+          <t>0x1cd4bc7ac782dfeb41e63fec20d8a9bf3592fd0bf81350409e2147d40aed1252</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2194,22 +2178,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.2888</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2234,7 +2218,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x76c9ba7a74843dcbf4f3d6b5e6055a7b6d28e43c811b91c405bc0dbc814a4a23</t>
+          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2264,7 +2248,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785360745</t>
+          <t>1785366635</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2274,7 +2258,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>6.337662</t>
+          <t>9.681356</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2291,12 +2275,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xe8d3398ff301339e290daf01ae6876fd68d47e759c9d409ef00bbc858bae53d1</t>
+          <t>0x21690cd9f64beaf84ff39e5d9167ff61ec45c3a6878ca6af24f70cb7a7dac51f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2306,7 +2290,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2376,7 +2360,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785358486</t>
+          <t>1785366550</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2386,7 +2370,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>15.023729</t>
+          <t>5.423729</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2403,7 +2387,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x6caf1354e289f361f3527f9fab48eb02c23c0756ae001e45930362caf84237dc</t>
+          <t>0xc21d414dfe738f0cc4050e3ca76880dd3b107f7b1f09fcb635b8321fb5dc0edf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2411,23 +2395,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.7887</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2435,27 +2427,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PAOK vs FC Dynamo Kyiv</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>FC Dynamo Kyiv</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
+          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19577850</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2480,17 +2472,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785358266</t>
+          <t>1785366547</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785433500</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>39.03645</t>
+          <t>8.623729</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2507,7 +2499,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x93785b3a7d055c5e2c869f1c6ed046a0c16cd38f39a06deaefeabb59967bf72c</t>
+          <t>0x8c9dfb9ff69df47c8ea5940a21855ffdd8eda4b64dc38fe98e2e2934f3d87538</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2515,31 +2507,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9.5122</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.5625</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2562,7 +2546,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x4ab76a4a1fa597ca197135de1fba0710473970c8adaef292b0acea5fe28788f8</t>
+          <t>0x8b7152b0bd00d827f374ce80d037c7f4423fc9121c18baeb864ae421a667b40f</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2592,7 +2576,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785358055</t>
+          <t>1785365217</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2602,7 +2586,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>19.512205</t>
+          <t>2.275556</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2619,39 +2603,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xe9c4a1ecf56e1210003b8a7c5c9dedc347ba38e18d81ea653d600cfae0406ee7</t>
+          <t>0x3657290ba2b8218d1552b68d792780f1911e7dc3600c885e6f81b7b21a4f4771</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.99999</t>
+          <t>1.66999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2659,27 +2635,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
+          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2704,17 +2680,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785357507</t>
+          <t>1785365171</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>3.278672</t>
+          <t>2.113911</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2731,7 +2707,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x91839b38bfe01bb58e0542f3e4844d2996af26b2e1159a45b719e543c59d0061</t>
+          <t>0x41aafd361fbdbc090304c361aa96e3d7d1986ad198e757cc1ed42d3a36d60feb</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2739,31 +2715,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2771,27 +2739,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
+          <t>0x38894b4e2a8e5d7e486f731ef1c20c3f048cafb9a2d74debe9378b5d273c6bae</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2816,17 +2784,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785357504</t>
+          <t>1785362098</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>18.721311</t>
+          <t>37.641278</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2843,31 +2811,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x12fa97e26b4d1fe9bc62fd353b41531c2d1e3636d5808e00f72cda223c5b7275</t>
+          <t>0xe548f2f667138f07fba5f8b56872f6e05a380228941a477ad0be28b68346322c</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>4.82999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.7637</t>
+          <t>1.7163</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pafos FC 0</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2890,7 +2866,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xba7019cc98094442aac3dcde57fe2ab308f401a1a9e55c251da54769aa97bf2b</t>
+          <t>0x372966a20c1cb92145662d4191d1ea402efa119df308298395ad72ee4927083e</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2920,7 +2896,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785357342</t>
+          <t>1785362057</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2930,7 +2906,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>30.180033</t>
+          <t>6.743442</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2947,7 +2923,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x580c7d1b576d43e738d64f6bb0fc1b2a6d6762d7d285da29ae6814cfcd809ae2</t>
+          <t>0xe8695e613b59508aa7ca7d5747a15d00bcfbed5e4f9653ed44f2df97fd577dfc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2967,7 +2943,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2977,32 +2953,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>Pafos FC</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Pafos FC vs Hajduk Split</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Pafos FC</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>Hajduk Split</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Pafos FC vs Hajduk Split</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Pafos FC</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Hajduk Split</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xd794b506219d24bb3d154b82e776aef773d5c44cbbd3c35da4709144cfa915ea</t>
+          <t>0xb7cd00a89de154596fb5ed105b39373600b95939a4d9c11792f78fa57728b1fc</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3032,7 +3008,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785357285</t>
+          <t>1785362047</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3042,7 +3018,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>43.715847</t>
+          <t>18.306636</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3059,7 +3035,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x001e676afb8025a177fca2fafbab0c4b0588ee71a31776ebbfe2be57ac5db06e</t>
+          <t>0x592ca05e5d2e598f37fef187e9bd4564705367d06c16f7ed3162e4659d773d8d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3074,12 +3050,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>30.67998</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.7125</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3089,7 +3065,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3099,27 +3075,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x781f333038176cef4c0433e190179bdff06422f2827828187d4d3847de53f791</t>
+          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3144,17 +3120,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785352509</t>
+          <t>1785362047</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>3.585624</t>
+          <t>43.059621</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3171,7 +3147,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x9bc12eeb5e62fdab19026dd9c59a6d3d812a1647d656ec82e9b08932d05fc32a</t>
+          <t>0x57f4d612536438737c246a83cb4a06a364b2ba5f0d5bffa44b2d450c599f005c</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3186,22 +3162,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>104.66</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Pafos FC -1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3211,27 +3187,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x963e029345e2eec87a8efe31b92941a4225d7b0339bd00d1d2b34c4b1ef0c388</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3256,7 +3232,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785350915</t>
+          <t>1785362047</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3266,7 +3242,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>230.655647</t>
+          <t>25.723473</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3283,7 +3259,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x4cc9256963002abc26b03e2de5c65df247f06de8cd8caaeab5e5ab26e126b583</t>
+          <t>0xa8f611211f253b096f6e8910a8e6d6614836d3fec79ca646c8cff14aa6cf4fe3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3298,22 +3274,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>200.71</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3323,27 +3299,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x76c9ba7a74843dcbf4f3d6b5e6055a7b6d28e43c811b91c405bc0dbc814a4a23</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3368,7 +3344,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785350884</t>
+          <t>1785360745</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3378,7 +3354,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>442.336088</t>
+          <t>6.337662</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3395,7 +3371,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x24e8cf815969b014ea0bedb7d75a94f636bc090bb24e1787d78815f3e5a70920</t>
+          <t>0xe8d3398ff301339e290daf01ae6876fd68d47e759c9d409ef00bbc858bae53d1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3410,22 +3386,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>222.91</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3435,27 +3411,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3480,7 +3456,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785350854</t>
+          <t>1785358486</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3490,7 +3466,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>491.261708</t>
+          <t>15.023729</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3507,7 +3483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x3729578f30b77e303f3460fb30277c2fcf85fb2049107b0dec479803d11515fe</t>
+          <t>0x6caf1354e289f361f3527f9fab48eb02c23c0756ae001e45930362caf84237dc</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3515,19 +3491,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>246.56</t>
+          <t>30.79</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3535,11 +3507,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3547,27 +3515,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3592,17 +3560,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785350824</t>
+          <t>1785358266</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>543.38292</t>
+          <t>39.03645</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3619,7 +3587,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xc94c50f0e5b4951b58fe15e51011784173d7fa5dea7800432eb5745354486b80</t>
+          <t>0x93785b3a7d055c5e2c869f1c6ed046a0c16cd38f39a06deaefeabb59967bf72c</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3634,22 +3602,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>9.5122</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3659,27 +3627,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4ab76a4a1fa597ca197135de1fba0710473970c8adaef292b0acea5fe28788f8</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3704,17 +3672,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785350560</t>
+          <t>1785358055</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>128.391304</t>
+          <t>19.512205</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3731,31 +3699,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xb98b07f3ed69cfe4b366fe2382029c20e5298a2c928a846c34e22585174d22a2</t>
+          <t>0xe9c4a1ecf56e1210003b8a7c5c9dedc347ba38e18d81ea653d600cfae0406ee7</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>503.79999</t>
+          <t>1.99999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3763,27 +3739,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3808,17 +3784,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785350534</t>
+          <t>1785357507</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>920.18263</t>
+          <t>3.278672</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3835,31 +3811,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xab48fb1edf1fe158898059d349b71fde37cf3bd3d854ff788e8cd23ed34410e3</t>
+          <t>0x91839b38bfe01bb58e0542f3e4844d2996af26b2e1159a45b719e543c59d0061</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1364.53</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3867,27 +3851,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3912,17 +3896,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785350511</t>
+          <t>1785357504</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2515.262673</t>
+          <t>18.721311</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3939,39 +3923,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x54afc83137f5b39b38053c7ac6e311ead709a66ed6180c1bd3071eec1df83367</t>
+          <t>0x12fa97e26b4d1fe9bc62fd353b41531c2d1e3636d5808e00f72cda223c5b7275</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>82.98999</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.8613</t>
+          <t>1.7637</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Maccabi Tel Aviv</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3979,27 +3955,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
+          <t>0xba7019cc98094442aac3dcde57fe2ab308f401a1a9e55c251da54769aa97bf2b</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4024,17 +4000,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785348315</t>
+          <t>1785357342</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>96.35993</t>
+          <t>30.180033</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4051,7 +4027,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x0dd08bf1a086493c6e680404308a2ef5ba5a320909569533d0dc8e4ad8fdea6a</t>
+          <t>0x580c7d1b576d43e738d64f6bb0fc1b2a6d6762d7d285da29ae6814cfcd809ae2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4066,39 +4042,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.6925</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Pafos FC vs Hajduk Split</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>Pafos FC</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Pafos FC vs Hajduk Split</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Pafos FC</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Hajduk Split</t>
@@ -4106,7 +4082,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
+          <t>0xd794b506219d24bb3d154b82e776aef773d5c44cbbd3c35da4709144cfa915ea</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4136,7 +4112,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785347423</t>
+          <t>1785357285</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4146,7 +4122,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>72.750903</t>
+          <t>43.715847</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4163,12 +4139,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x993556c3cf15426b02b61df75d8fd0060a5e7634bee1409d10b85861b937670f</t>
+          <t>0x001e676afb8025a177fca2fafbab0c4b0588ee71a31776ebbfe2be57ac5db06e</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4178,22 +4154,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5112</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4203,27 +4179,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0x781f333038176cef4c0433e190179bdff06422f2827828187d4d3847de53f791</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4248,17 +4224,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785327349</t>
+          <t>1785352509</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1.95599</t>
+          <t>3.585624</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4275,31 +4251,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x4faded42a032bd6a91d4916349230f502e8759f9944cbfef78288354f9340944</t>
+          <t>0x9bc12eeb5e62fdab19026dd9c59a6d3d812a1647d656ec82e9b08932d05fc32a</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5.80275</t>
+          <t>104.66</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4307,27 +4291,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4352,17 +4336,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785325667</t>
+          <t>1785350915</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>12.120627</t>
+          <t>230.655647</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4379,31 +4363,39 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x39c74108b106ba600e266454471670d092342df7435c478a184f31c5880fcb1c</t>
+          <t>0x4cc9256963002abc26b03e2de5c65df247f06de8cd8caaeab5e5ab26e126b583</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>200.71</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4411,27 +4403,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4456,17 +4448,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785325592</t>
+          <t>1785350884</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>378.067885</t>
+          <t>442.336088</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4483,31 +4475,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x6e97ae46202c322fcc5e7c70be0be87e1574709ea5cf0024a945e7d45d548728</t>
+          <t>0x24e8cf815969b014ea0bedb7d75a94f636bc090bb24e1787d78815f3e5a70920</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>179.29</t>
+          <t>222.91</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4763</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4515,27 +4515,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4560,17 +4560,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785325549</t>
+          <t>1785350854</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>376.461942</t>
+          <t>491.261708</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4587,31 +4587,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x36f17b5f896b8f5c9301b3600be88ac0007d3ce06403ffe9b13d7389417fa953</t>
+          <t>0x3729578f30b77e303f3460fb30277c2fcf85fb2049107b0dec479803d11515fe</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>246.56</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4775</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4619,27 +4627,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4664,17 +4672,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785325496</t>
+          <t>1785350824</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>379.057592</t>
+          <t>543.38292</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4691,31 +4699,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xf2a45c2970e6d3af37fabd0ad34ce6efeecfe1f77cb4d5f43515fb342f7fcca2</t>
+          <t>0xc94c50f0e5b4951b58fe15e51011784173d7fa5dea7800432eb5745354486b80</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4723,27 +4739,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4768,17 +4784,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785325423</t>
+          <t>1785350560</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>378.067885</t>
+          <t>128.391304</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4795,28 +4811,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xdd031e5f334a60c24ea47a7a807f20a2bead2b80c0227808f5afa24fa77a3d06</t>
+          <t>0xb98b07f3ed69cfe4b366fe2382029c20e5298a2c928a846c34e22585174d22a2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>503.79999</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4827,27 +4843,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4872,17 +4888,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785325348</t>
+          <t>1785350534</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>394.805195</t>
+          <t>920.18263</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4899,28 +4915,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x4c7bd245dd4665e7f9285a58768875e4fa752d61dfc244e87f7283d2907dcb15</t>
+          <t>0xab48fb1edf1fe158898059d349b71fde37cf3bd3d854ff788e8cd23ed34410e3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>1364.53</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4775</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4931,27 +4947,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4976,17 +4992,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785325203</t>
+          <t>1785350511</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>383.246073</t>
+          <t>2515.262673</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5003,23 +5019,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x13f73d60f1f96dd112ac2a53fa2a1a53f2e55f9bc0782a0d92732337ef7e7519</t>
+          <t>0x54afc83137f5b39b38053c7ac6e311ead709a66ed6180c1bd3071eec1df83367</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>82.98999</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.8613</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5027,7 +5047,11 @@
           <t>Europa League</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5035,27 +5059,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5080,17 +5104,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785325120</t>
+          <t>1785348315</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>166.287263</t>
+          <t>96.35993</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5107,12 +5131,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xd5759db5ffa02ee1c17bc11bdfbffb2bb73c6ff16a4fa6bf670dafa016fad84a</t>
+          <t>0x0dd08bf1a086493c6e680404308a2ef5ba5a320909569533d0dc8e4ad8fdea6a</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5122,22 +5146,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.6925</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5147,27 +5171,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5192,7 +5216,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785319802</t>
+          <t>1785347423</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5202,7 +5226,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>21.949861</t>
+          <t>72.750903</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5219,12 +5243,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x0fc529171c6c4f0c441f19435054a73905e5f2d2ed326778ddb79cd108c6ede1</t>
+          <t>0x993556c3cf15426b02b61df75d8fd0060a5e7634bee1409d10b85861b937670f</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5234,12 +5258,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5249,7 +5273,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5259,27 +5283,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xec30d6ed85c3851d5938108fae681432d7a35f2c741191462472aaa11d35b165</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5304,7 +5328,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785317013</t>
+          <t>1785327349</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5314,7 +5338,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>7.929825</t>
+          <t>1.95599</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5331,39 +5355,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x2d47f0e85c65fcb84f5de7818b5845226e8638c4dc49fb9093b9a86fe895116b</t>
+          <t>0x4faded42a032bd6a91d4916349230f502e8759f9944cbfef78288354f9340944</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11.26</t>
+          <t>5.80275</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5371,27 +5387,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5416,17 +5432,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785316734</t>
+          <t>1785325667</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>20.38009</t>
+          <t>12.120627</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5443,39 +5459,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xe8fb252bc279aab31e6c6f4de96e27aca4bae9402699e12add62fecf7cc6090d</t>
+          <t>0x39c74108b106ba600e266454471670d092342df7435c478a184f31c5880fcb1c</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5483,27 +5491,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5528,17 +5536,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785314887</t>
+          <t>1785325592</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>14.280543</t>
+          <t>378.067885</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5555,39 +5563,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x988d12bce5f972af9ca3a2a7a91ba784d379a454873fb5ad9267f635cfeabaae</t>
+          <t>0x6e97ae46202c322fcc5e7c70be0be87e1574709ea5cf0024a945e7d45d548728</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>122.7</t>
+          <t>179.29</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4763</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5595,27 +5595,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5640,17 +5640,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785314533</t>
+          <t>1785325549</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>273.426184</t>
+          <t>376.461942</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5667,39 +5667,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x78d34863dc5be51d39c855d3868e1af787b7281b3a9ba704567d82456b113d15</t>
+          <t>0x36f17b5f896b8f5c9301b3600be88ac0007d3ce06403ffe9b13d7389417fa953</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>178.48</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5707,27 +5699,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5752,17 +5744,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785313946</t>
+          <t>1785325496</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>397.727019</t>
+          <t>379.057592</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5779,39 +5771,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x5106f8b58142e7b5c50eb3e00b44385652098e82742605b478cd59c2271a33a0</t>
+          <t>0xf2a45c2970e6d3af37fabd0ad34ce6efeecfe1f77cb4d5f43515fb342f7fcca2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5819,27 +5803,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5864,17 +5848,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785313924</t>
+          <t>1785325423</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>668.523677</t>
+          <t>378.067885</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5891,39 +5875,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x6e2b82838c81a4891a03953f0ebaca7a027f4125fe2deaed52b0a95c44206dab</t>
+          <t>0xdd031e5f334a60c24ea47a7a807f20a2bead2b80c0227808f5afa24fa77a3d06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>190</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5931,27 +5907,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5976,17 +5952,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785313712</t>
+          <t>1785325348</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>311.977716</t>
+          <t>394.805195</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6003,28 +5979,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x6a19a9357d731588796a01e05f4e8808a84076b6662f83356dcf6c6b00474e65</t>
+          <t>0x4c7bd245dd4665e7f9285a58768875e4fa752d61dfc244e87f7283d2907dcb15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>183</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -6035,27 +6011,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6080,17 +6056,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785313623</t>
+          <t>1785325203</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>240.723982</t>
+          <t>383.246073</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6107,39 +6083,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x6484f0585336dfe74c291be479560bddc0741e80877c77ec5ca7fcb16d4374a5</t>
+          <t>0x13f73d60f1f96dd112ac2a53fa2a1a53f2e55f9bc0782a0d92732337ef7e7519</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>48.19</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6147,27 +6115,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6192,17 +6160,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785313622</t>
+          <t>1785325120</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>107.387187</t>
+          <t>166.287263</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6219,12 +6187,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x6906ce6d1047273d710579bf3d98367dbf415d0e24ecb41a8a528337a9506d3a</t>
+          <t>0xd5759db5ffa02ee1c17bc11bdfbffb2bb73c6ff16a4fa6bf670dafa016fad84a</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6234,7 +6202,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6304,7 +6272,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785313432</t>
+          <t>1785319802</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6314,7 +6282,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>12.612813</t>
+          <t>21.949861</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6331,12 +6299,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x2c365a540f836041b72448aca3516556411b341658244ff388c1692fa15d2af0</t>
+          <t>0x0fc529171c6c4f0c441f19435054a73905e5f2d2ed326778ddb79cd108c6ede1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6346,12 +6314,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6361,32 +6329,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>Tromso</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove vs Tromso</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xec30d6ed85c3851d5938108fae681432d7a35f2c741191462472aaa11d35b165</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6416,7 +6384,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785313327</t>
+          <t>1785317013</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6426,7 +6394,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>20.43454</t>
+          <t>7.929825</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6443,12 +6411,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xe917c05092f572e2e95fee59d14b544fb6d4c549a9e9e7399b744a830680c0ef</t>
+          <t>0x2d47f0e85c65fcb84f5de7818b5845226e8638c4dc49fb9093b9a86fe895116b</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xd22BD9e1B7916fFE0ad765642788c86b6aa29075</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6458,22 +6426,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6483,27 +6451,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6528,17 +6496,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785313211</t>
+          <t>1785316734</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>13.894737</t>
+          <t>20.38009</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6555,12 +6523,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x8d92cbf4088d40c4b2b67cbb02c218ebad12e894eda090162e17c4b4ec2423ec</t>
+          <t>0xe8fb252bc279aab31e6c6f4de96e27aca4bae9402699e12add62fecf7cc6090d</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6570,22 +6538,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6595,27 +6563,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6640,17 +6608,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785313190</t>
+          <t>1785314887</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>11.390582</t>
+          <t>14.280543</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6667,12 +6635,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x4858e2eb7b8bfa0a43a468cd0f4c8c41ecc4c6f3ede73f30251c7922e1a658eb</t>
+          <t>0x988d12bce5f972af9ca3a2a7a91ba784d379a454873fb5ad9267f635cfeabaae</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6682,12 +6650,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6752,7 +6720,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785313173</t>
+          <t>1785314533</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6762,7 +6730,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>20.387812</t>
+          <t>273.426184</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6779,23 +6747,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xf0b6c79ec7c1905e25f5ff4b6433e8122df6bb18a211b77a66cc1962804b95cb</t>
+          <t>0x78d34863dc5be51d39c855d3868e1af787b7281b3a9ba704567d82456b113d15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>56.13118</t>
+          <t>178.48</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6803,7 +6775,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6856,7 +6832,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785313133</t>
+          <t>1785313946</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6866,7 +6842,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>102.992991</t>
+          <t>397.727019</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6883,23 +6859,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
+          <t>0x5106f8b58142e7b5c50eb3e00b44385652098e82742605b478cd59c2271a33a0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6907,7 +6887,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6915,27 +6899,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6960,7 +6944,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785282599</t>
+          <t>1785313924</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6970,7 +6954,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>101.012788</t>
+          <t>668.523677</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6987,23 +6971,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
+          <t>0x6e2b82838c81a4891a03953f0ebaca7a027f4125fe2deaed52b0a95c44206dab</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7011,7 +6999,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7064,7 +7056,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785282154</t>
+          <t>1785313712</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7074,7 +7066,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>9.181132</t>
+          <t>311.977716</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7091,23 +7083,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
+          <t>0x6a19a9357d731588796a01e05f4e8808a84076b6662f83356dcf6c6b00474e65</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7168,7 +7160,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785281829</t>
+          <t>1785313623</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7178,7 +7170,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>9.181132</t>
+          <t>240.723982</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7195,31 +7187,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
+          <t>0x6484f0585336dfe74c291be479560bddc0741e80877c77ec5ca7fcb16d4374a5</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4.7855</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7227,27 +7227,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7272,17 +7272,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785267733</t>
+          <t>1785313622</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>14.446792</t>
+          <t>107.387187</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7299,31 +7299,39 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
+          <t>0x6906ce6d1047273d710579bf3d98367dbf415d0e24ecb41a8a528337a9506d3a</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4.8535</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7331,27 +7339,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7376,17 +7384,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785265830</t>
+          <t>1785313432</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>14.327675</t>
+          <t>12.612813</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7403,12 +7411,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
+          <t>0x2c365a540f836041b72448aca3516556411b341658244ff388c1692fa15d2af0</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7418,22 +7426,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SL Benfica FC -3</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7443,27 +7451,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7488,17 +7496,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785261286</t>
+          <t>1785313327</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>20.43454</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7515,23 +7523,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
+          <t>0xe917c05092f572e2e95fee59d14b544fb6d4c549a9e9e7399b744a830680c0ef</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>0xd22BD9e1B7916fFE0ad765642788c86b6aa29075</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7539,7 +7551,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7592,7 +7608,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785258767</t>
+          <t>1785313211</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7602,7 +7618,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>15.179487</t>
+          <t>13.894737</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7619,31 +7635,39 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
+          <t>0x8d92cbf4088d40c4b2b67cbb02c218ebad12e894eda090162e17c4b4ec2423ec</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.3425</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7651,27 +7675,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7696,17 +7720,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785253987</t>
+          <t>1785313190</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>15.737226</t>
+          <t>11.390582</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7723,12 +7747,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
+          <t>0x4858e2eb7b8bfa0a43a468cd0f4c8c41ecc4c6f3ede73f30251c7922e1a658eb</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7738,22 +7762,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>142.02999</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.6663</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7763,27 +7787,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7808,7 +7832,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785232812</t>
+          <t>1785313173</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7818,7 +7842,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>213.178221</t>
+          <t>20.387812</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7835,39 +7859,31 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
+          <t>0xf0b6c79ec7c1905e25f5ff4b6433e8122df6bb18a211b77a66cc1962804b95cb</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>193.23</t>
+          <t>56.13118</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.545</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7875,27 +7891,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7920,7 +7936,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785231712</t>
+          <t>1785313133</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7930,7 +7946,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>285.737523</t>
+          <t>102.992991</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7947,23 +7963,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
+          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7979,27 +7995,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -8024,7 +8040,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785227020</t>
+          <t>1785282599</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8034,7 +8050,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>20.185185</t>
+          <t>101.012788</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8051,39 +8067,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
+          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>104.47</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -8091,27 +8099,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8136,7 +8144,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785224116</t>
+          <t>1785282154</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8146,7 +8154,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>155.925373</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8163,39 +8171,31 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
+          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -8203,27 +8203,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785223916</t>
+          <t>1785281829</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>144.089552</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8275,28 +8275,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
+          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>70.47999</t>
+          <t>4.7855</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8307,27 +8307,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8352,17 +8352,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785220497</t>
+          <t>1785267733</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>133.295489</t>
+          <t>14.446792</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8379,39 +8379,31 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
+          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>4.8535</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -8419,27 +8411,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8464,17 +8456,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785218406</t>
+          <t>1785265830</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>14.327675</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8491,7 +8483,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
+          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8499,23 +8491,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SL Benfica FC -3</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -8523,27 +8523,27 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
+          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -8568,17 +8568,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785213181</t>
+          <t>1785261286</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>254.185874</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8595,23 +8595,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
+          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785189317</t>
+          <t>1785258767</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>15.179487</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8699,28 +8699,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
+          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -8731,27 +8731,27 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -8776,17 +8776,17 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785188885</t>
+          <t>1785253987</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>15.737226</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8803,12 +8803,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
+          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8818,22 +8818,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>142.02999</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.6663</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8843,27 +8843,27 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8888,17 +8888,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785186773</t>
+          <t>1785232812</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>213.178221</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8915,12 +8915,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
+          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8930,22 +8930,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>193.23</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8955,27 +8955,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -9000,17 +9000,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785186621</t>
+          <t>1785231712</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>285.737523</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9027,27 +9027,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9055,11 +9051,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -9067,27 +9059,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -9112,17 +9104,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785186464</t>
+          <t>1785227020</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>20.185185</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9139,12 +9131,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -9154,22 +9146,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>104.47</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9179,27 +9171,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -9224,17 +9216,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785186313</t>
+          <t>1785224116</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>155.925373</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9251,12 +9243,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9266,22 +9258,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9291,27 +9283,27 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -9336,17 +9328,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785185868</t>
+          <t>1785223916</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>144.089552</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9363,28 +9355,28 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>70.47999</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -9395,27 +9387,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9440,17 +9432,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785182082</t>
+          <t>1785220497</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>101.408451</t>
+          <t>133.295489</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9467,12 +9459,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9482,22 +9474,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>98.9699</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.9187</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9507,27 +9499,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9552,17 +9544,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785178276</t>
+          <t>1785218406</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>107.72234</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9579,7 +9571,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9590,17 +9582,17 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>85.47</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -9626,7 +9618,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9656,7 +9648,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785157337</t>
+          <t>1785213181</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9666,7 +9658,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>254.185874</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9683,27 +9675,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9711,11 +9699,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Besiktas</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -9723,27 +9707,27 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -9768,7 +9752,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785154148</t>
+          <t>1785189317</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9778,7 +9762,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9795,27 +9779,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2.36789</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9823,11 +9803,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Besiktas</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -9835,27 +9811,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9880,7 +9856,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785188885</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9890,7 +9866,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>9.866208</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9907,12 +9883,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9922,12 +9898,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -9937,7 +9913,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9947,27 +9923,27 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9992,17 +9968,17 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785186773</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -10019,12 +9995,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -10034,22 +10010,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>65.95</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -10059,27 +10035,27 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -10104,17 +10080,17 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785131538</t>
+          <t>1785186621</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>177.643098</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10131,110 +10107,1214 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1785186464</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>1785186313</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1785185868</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.2662</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs FC Twente</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>L19578664</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>1785182082</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>1785436200</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>101.408451</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>98.9699</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.9187</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>FC St. Gallen</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>L19577588</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1785178276</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1785438000</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>107.72234</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>1785157337</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>1785154148</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2.36789</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>9.866208</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>65.95</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.3713</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>1785131538</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>177.643098</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>0x4a21e608f2a49d0d290d56e481810827c36c3a33b3cdfa52f47a9d205c9195a6</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>1.1213</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>SL Benfica FC</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>FC St. Gallen</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>0xfc195ce6529fc46edc42b440639cd20958bc0e5f58d88c7925cdd8563a01ebd2</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>L19577588</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
         <is>
           <t>1785123830</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>1785438000</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="T100" t="inlineStr">
         <is>
           <t>65.979381</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="U100" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr">
+      <c r="V100" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Europa League_UEFA/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V100"/>
+  <dimension ref="A1:V105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x1aea7ce83ddf2c16d6d78808082e2a4447df99dad359f5db36f9cdef821b971c</t>
+          <t>0x5f9f15d73b1fdb6b395efbf0d6ca307cd12164f81c741f3458d6da20f3aa5697</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>49.71</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PAOK</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PAOK vs FC Dynamo Kyiv</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FC Dynamo Kyiv</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x6abf1fe8c0ab5d6643454c0862ea120137474f1adf2ddb35a78e06cee0a1e961</t>
+          <t>0x8c586329562e43001ecf507fb2b143e65f29afff1fc642f6a8274ecbbd123be4</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19577850</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785374463</t>
+          <t>1785379632</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785433500</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>91.631336</t>
+          <t>4.255319</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x0d60e14be6485d6af0a032b19bfc014d50bdd434c6f2c1a5557d1a7320edd82e</t>
+          <t>0x5190421262a0141de446583e3f63e39446135261f5853949434641ba6299b1f5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,12 +650,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>36.74</t>
+          <t>108.71999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,7 +665,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>PAOK -0.5</t>
+          <t>Pafos FC -0.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PAOK vs FC Dynamo Kyiv</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>FC Dynamo Kyiv</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xc273fb0d8cb04f7d1e39a7dc030231f54f40d91616b1ffb8e41b34c74f3712de</t>
+          <t>0x8c586329562e43001ecf507fb2b143e65f29afff1fc642f6a8274ecbbd123be4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19577850</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785374440</t>
+          <t>1785379629</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785433500</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>67.723502</t>
+          <t>199.944809</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5f8c940baa6470cf16ca3dc71e0168bd2f26563ea996fc4cd0d03926f6f73b73</t>
+          <t>0xd5d5a792d09ab13b3542227492e28266cbccbecdc5e9f4b60f61fe1d75c6d856</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,22 +762,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.5825</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv -1.5</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x367cf8e90c51f0117ab2bbcf8ae8d0fe38dd56a5b21aaf98a94d7e6d6eda4df6</t>
+          <t>0x08ff4ee90ad16db823405692fb665c17bc113cf75d84feeb88380da846dbbd0d</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785374215</t>
+          <t>1785378958</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.686717</t>
+          <t>3.193133</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,31 +859,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x3c260355924102caec0b38bcb930951d38289f2f82dee3c74f62f48685499052</t>
+          <t>0x1f9b0ca8269cc5b8078f0519987e2055395d7a23c4db9ccfd57aa052f53fc651</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30.01999</t>
+          <t>12.8775</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5625</t>
+          <t>1.5825</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -899,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x8b7152b0bd00d827f374ce80d037c7f4423fc9121c18baeb864ae421a667b40f</t>
+          <t>0x08ff4ee90ad16db823405692fb665c17bc113cf75d84feeb88380da846dbbd0d</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785373649</t>
+          <t>1785378940</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>53.368871</t>
+          <t>22.107296</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,54 +971,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x99448357b2426bacd925223de1d6f212b927193aaf4c97f727b6ce05761ee389</t>
+          <t>0x941337366e51e311f63e6e8d688426b1faf7768afa14dda2e5a25b0eba0398e6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.04349</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5938</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht vs Hammarby IF</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>RSC Anderlecht</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>RSC Anderlecht</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Hammarby IF</t>
@@ -1026,7 +1018,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x781f333038176cef4c0433e190179bdff06422f2827828187d4d3847de53f791</t>
+          <t>0xe63091e1ff8f454423c5ec33054be6b47f313f484d136aa5104583d15765275f</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785372954</t>
+          <t>1785377121</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3.873684</t>
+          <t>1.830684</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,12 +1075,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xb1d69406483c4d5da20cd936d46b4201485f7dab32ebd7e9e43c87c5a5828c7a</t>
+          <t>0x1aea7ce83ddf2c16d6d78808082e2a4447df99dad359f5db36f9cdef821b971c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1098,22 +1090,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>49.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.1838</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,27 +1115,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x49e2852fda6d5fbb44e4cc626e2ace2f31139b2b56c37dc1493a8b51cc66820e</t>
+          <t>0x6abf1fe8c0ab5d6643454c0862ea120137474f1adf2ddb35a78e06cee0a1e961</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1160,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785372862</t>
+          <t>1785374463</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>54.802721</t>
+          <t>91.631336</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,31 +1187,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xf253ffdfa6bd50e48d7bda60ad225c2ee338b86b6e56850ade26b1a3b4d009bf</t>
+          <t>0x0d60e14be6485d6af0a032b19bfc014d50bdd434c6f2c1a5557d1a7320edd82e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x9737E0E3E8EE2DD6B8A7E19D1507EcB3221b5483</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>36.74</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PAOK -0.5</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1227,27 +1227,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x4c9723bc7def26f86e0656a3de22257af36e6760bd8d8ed81a5f8b03d2039e77</t>
+          <t>0xc273fb0d8cb04f7d1e39a7dc030231f54f40d91616b1ffb8e41b34c74f3712de</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785370874</t>
+          <t>1785374440</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>11.666667</t>
+          <t>67.723502</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,31 +1299,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xe8f885df4c805c1f7e67de64b4b6965f588f95ad27de1ec6c34b82740207ca09</t>
+          <t>0x5f8c940baa6470cf16ca3dc71e0168bd2f26563ea996fc4cd0d03926f6f73b73</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv -1.5</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1331,27 +1339,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x4c9723bc7def26f86e0656a3de22257af36e6760bd8d8ed81a5f8b03d2039e77</t>
+          <t>0x367cf8e90c51f0117ab2bbcf8ae8d0fe38dd56a5b21aaf98a94d7e6d6eda4df6</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1384,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785370874</t>
+          <t>1785374215</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>4.761905</t>
+          <t>2.686717</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,28 +1411,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x162a97e4490bb57d534ff14799f7e19ae8f7956798df9232d7abbb1965e19b36</t>
+          <t>0x3c260355924102caec0b38bcb930951d38289f2f82dee3c74f62f48685499052</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x06a603b688E676702ec63D735CAe4A57ff71B3e1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30.01999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5625</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1435,27 +1443,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x4c9723bc7def26f86e0656a3de22257af36e6760bd8d8ed81a5f8b03d2039e77</t>
+          <t>0x8b7152b0bd00d827f374ce80d037c7f4423fc9121c18baeb864ae421a667b40f</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1480,17 +1488,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785370869</t>
+          <t>1785373649</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>11.904762</t>
+          <t>53.368871</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,31 +1515,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x6aef40c5e87de9ce8b5065247616823179fafefd3d12456fea34f6103b9b0111</t>
+          <t>0x99448357b2426bacd925223de1d6f212b927193aaf4c97f727b6ce05761ee389</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.5938</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1539,27 +1555,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x4c9723bc7def26f86e0656a3de22257af36e6760bd8d8ed81a5f8b03d2039e77</t>
+          <t>0x781f333038176cef4c0433e190179bdff06422f2827828187d4d3847de53f791</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1584,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785370858</t>
+          <t>1785372954</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>12.121212</t>
+          <t>3.873684</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xb25e4ba5b290a3a9d1569a873de49e2e7804f94728fefb25bc1b8eb95be5415f</t>
+          <t>0xb1d69406483c4d5da20cd936d46b4201485f7dab32ebd7e9e43c87c5a5828c7a</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1619,23 +1635,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.27999</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1.1838</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1643,27 +1667,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PAOK vs FC Dynamo Kyiv</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>FC Dynamo Kyiv</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
+          <t>0x49e2852fda6d5fbb44e4cc626e2ace2f31139b2b56c37dc1493a8b51cc66820e</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19577850</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1688,17 +1712,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785369276</t>
+          <t>1785372862</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785433500</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.61005</t>
+          <t>54.802721</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,39 +1739,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xd467c62d6aa2ecab07ea59a887f62479dd15fab24cad69c0a3ebcfd8511ee9f2</t>
+          <t>0xf253ffdfa6bd50e48d7bda60ad225c2ee338b86b6e56850ade26b1a3b4d009bf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9737E0E3E8EE2DD6B8A7E19D1507EcB3221b5483</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>59.20997</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.8825</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Maccabi Tel Aviv</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1755,27 +1771,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
+          <t>0x4c9723bc7def26f86e0656a3de22257af36e6760bd8d8ed81a5f8b03d2039e77</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1800,17 +1816,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785368865</t>
+          <t>1785370874</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>67.09345</t>
+          <t>11.666667</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1827,39 +1843,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x40b0eae71c0a0bd0cb5ff7ac8cacb47e388bf7fa99c7ce39154934066cd1ef74</t>
+          <t>0xe8f885df4c805c1f7e67de64b4b6965f588f95ad27de1ec6c34b82740207ca09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>64.57</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1867,27 +1875,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PAOK vs FC Dynamo Kyiv</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>FC Dynamo Kyiv</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xb96335c20a7cfa4ae2dd89e2cd8cdb045cc2ade055bdd75f1c34b0d83e0c1570</t>
+          <t>0x4c9723bc7def26f86e0656a3de22257af36e6760bd8d8ed81a5f8b03d2039e77</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19577850</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1912,17 +1920,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785367844</t>
+          <t>1785370874</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785433500</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>249.545894</t>
+          <t>4.761905</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,39 +1947,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x1ab3b75ef95b12db8d5d9c9f939cc0282aa6560cab50e9a374e87a1498fdd1c3</t>
+          <t>0x162a97e4490bb57d534ff14799f7e19ae8f7956798df9232d7abbb1965e19b36</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x06a603b688E676702ec63D735CAe4A57ff71B3e1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>38.96</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -1979,27 +1979,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
+          <t>0x4c9723bc7def26f86e0656a3de22257af36e6760bd8d8ed81a5f8b03d2039e77</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2024,17 +2024,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785367720</t>
+          <t>1785370869</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>63.738241</t>
+          <t>11.904762</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,39 +2051,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x95dd162a39f741daf09ec1ee6ce0f034aac56839a6ef1644143d50d2c5960b5a</t>
+          <t>0x6aef40c5e87de9ce8b5065247616823179fafefd3d12456fea34f6103b9b0111</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.4125</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2091,27 +2083,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PAOK vs FC Dynamo Kyiv</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>FC Dynamo Kyiv</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xb96335c20a7cfa4ae2dd89e2cd8cdb045cc2ade055bdd75f1c34b0d83e0c1570</t>
+          <t>0x4c9723bc7def26f86e0656a3de22257af36e6760bd8d8ed81a5f8b03d2039e77</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19577850</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2136,17 +2128,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785367020</t>
+          <t>1785370858</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785433500</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>26.357488</t>
+          <t>12.121212</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2163,7 +2155,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x1cd4bc7ac782dfeb41e63fec20d8a9bf3592fd0bf81350409e2147d40aed1252</t>
+          <t>0xb25e4ba5b290a3a9d1569a873de49e2e7804f94728fefb25bc1b8eb95be5415f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2171,31 +2163,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>1.27999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.795</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2203,27 +2187,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
+          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2248,17 +2232,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785366635</t>
+          <t>1785369276</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>9.681356</t>
+          <t>1.61005</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2275,12 +2259,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x21690cd9f64beaf84ff39e5d9167ff61ec45c3a6878ca6af24f70cb7a7dac51f</t>
+          <t>0xd467c62d6aa2ecab07ea59a887f62479dd15fab24cad69c0a3ebcfd8511ee9f2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2290,22 +2274,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>59.20997</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.8825</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2315,27 +2299,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
+          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2360,17 +2344,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785366550</t>
+          <t>1785368865</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>5.423729</t>
+          <t>67.09345</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2387,12 +2371,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xc21d414dfe738f0cc4050e3ca76880dd3b107f7b1f09fcb635b8321fb5dc0edf</t>
+          <t>0x40b0eae71c0a0bd0cb5ff7ac8cacb47e388bf7fa99c7ce39154934066cd1ef74</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2402,22 +2386,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>64.57</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2427,27 +2411,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
+          <t>0xb96335c20a7cfa4ae2dd89e2cd8cdb045cc2ade055bdd75f1c34b0d83e0c1570</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2472,17 +2456,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785366547</t>
+          <t>1785367844</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>8.623729</t>
+          <t>249.545894</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2499,7 +2483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x8c9dfb9ff69df47c8ea5940a21855ffdd8eda4b64dc38fe98e2e2934f3d87538</t>
+          <t>0x1ab3b75ef95b12db8d5d9c9f939cc0282aa6560cab50e9a374e87a1498fdd1c3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2507,23 +2491,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>38.96</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5625</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2531,27 +2523,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x8b7152b0bd00d827f374ce80d037c7f4423fc9121c18baeb864ae421a667b40f</t>
+          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2576,17 +2568,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785365217</t>
+          <t>1785367720</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2.275556</t>
+          <t>63.738241</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2603,23 +2595,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x3657290ba2b8218d1552b68d792780f1911e7dc3600c885e6f81b7b21a4f4771</t>
+          <t>0x95dd162a39f741daf09ec1ee6ce0f034aac56839a6ef1644143d50d2c5960b5a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.66999</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2627,7 +2623,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
+          <t>0xb96335c20a7cfa4ae2dd89e2cd8cdb045cc2ade055bdd75f1c34b0d83e0c1570</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785365171</t>
+          <t>1785367020</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2.113911</t>
+          <t>26.357488</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2707,7 +2707,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x41aafd361fbdbc090304c361aa96e3d7d1986ad198e757cc1ed42d3a36d60feb</t>
+          <t>0x1cd4bc7ac782dfeb41e63fec20d8a9bf3592fd0bf81350409e2147d40aed1252</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2715,23 +2715,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -2739,27 +2747,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x38894b4e2a8e5d7e486f731ef1c20c3f048cafb9a2d74debe9378b5d273c6bae</t>
+          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2784,7 +2792,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785362098</t>
+          <t>1785366635</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2794,7 +2802,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>37.641278</t>
+          <t>9.681356</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2811,12 +2819,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xe548f2f667138f07fba5f8b56872f6e05a380228941a477ad0be28b68346322c</t>
+          <t>0x21690cd9f64beaf84ff39e5d9167ff61ec45c3a6878ca6af24f70cb7a7dac51f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2826,22 +2834,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.82999</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.7163</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pafos FC 0</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2866,7 +2874,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x372966a20c1cb92145662d4191d1ea402efa119df308298395ad72ee4927083e</t>
+          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2896,7 +2904,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785362057</t>
+          <t>1785366550</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2906,7 +2914,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>6.743442</t>
+          <t>5.423729</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2923,7 +2931,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xe8695e613b59508aa7ca7d5747a15d00bcfbed5e4f9653ed44f2df97fd577dfc</t>
+          <t>0xc21d414dfe738f0cc4050e3ca76880dd3b107f7b1f09fcb635b8321fb5dc0edf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2938,39 +2946,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Pafos FC vs Hajduk Split</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>Pafos FC</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Pafos FC vs Hajduk Split</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Pafos FC</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Hajduk Split</t>
@@ -2978,7 +2986,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xb7cd00a89de154596fb5ed105b39373600b95939a4d9c11792f78fa57728b1fc</t>
+          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3008,7 +3016,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785362047</t>
+          <t>1785366547</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3018,7 +3026,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>18.306636</t>
+          <t>8.623729</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3035,7 +3043,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x592ca05e5d2e598f37fef187e9bd4564705367d06c16f7ed3162e4659d773d8d</t>
+          <t>0x8c9dfb9ff69df47c8ea5940a21855ffdd8eda4b64dc38fe98e2e2934f3d87538</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3043,31 +3051,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30.67998</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.7125</t>
+          <t>1.5625</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Pafos FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3075,27 +3075,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
+          <t>0x8b7152b0bd00d827f374ce80d037c7f4423fc9121c18baeb864ae421a667b40f</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3120,17 +3120,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785362047</t>
+          <t>1785365217</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>43.059621</t>
+          <t>2.275556</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3147,7 +3147,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x57f4d612536438737c246a83cb4a06a364b2ba5f0d5bffa44b2d450c599f005c</t>
+          <t>0x3657290ba2b8218d1552b68d792780f1911e7dc3600c885e6f81b7b21a4f4771</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3155,31 +3155,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.66999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Pafos FC -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3187,27 +3179,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x963e029345e2eec87a8efe31b92941a4225d7b0339bd00d1d2b34c4b1ef0c388</t>
+          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3232,17 +3224,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785362047</t>
+          <t>1785365171</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>25.723473</t>
+          <t>2.113911</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3259,7 +3251,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xa8f611211f253b096f6e8910a8e6d6614836d3fec79ca646c8cff14aa6cf4fe3</t>
+          <t>0x41aafd361fbdbc090304c361aa96e3d7d1986ad198e757cc1ed42d3a36d60feb</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3267,31 +3259,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.2888</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3299,27 +3283,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x76c9ba7a74843dcbf4f3d6b5e6055a7b6d28e43c811b91c405bc0dbc814a4a23</t>
+          <t>0x38894b4e2a8e5d7e486f731ef1c20c3f048cafb9a2d74debe9378b5d273c6bae</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3344,7 +3328,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785360745</t>
+          <t>1785362098</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3354,7 +3338,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>6.337662</t>
+          <t>37.641278</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3371,7 +3355,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xe8d3398ff301339e290daf01ae6876fd68d47e759c9d409ef00bbc858bae53d1</t>
+          <t>0xe548f2f667138f07fba5f8b56872f6e05a380228941a477ad0be28b68346322c</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3386,22 +3370,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>4.82999</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.7163</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Pafos FC 0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3426,7 +3410,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
+          <t>0x372966a20c1cb92145662d4191d1ea402efa119df308298395ad72ee4927083e</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3456,7 +3440,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785358486</t>
+          <t>1785362057</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3466,7 +3450,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>15.023729</t>
+          <t>6.743442</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3483,7 +3467,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x6caf1354e289f361f3527f9fab48eb02c23c0756ae001e45930362caf84237dc</t>
+          <t>0xe8695e613b59508aa7ca7d5747a15d00bcfbed5e4f9653ed44f2df97fd577dfc</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3491,15 +3475,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.7887</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3507,7 +3495,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pafos FC</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3515,27 +3507,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PAOK vs FC Dynamo Kyiv</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>FC Dynamo Kyiv</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
+          <t>0xb7cd00a89de154596fb5ed105b39373600b95939a4d9c11792f78fa57728b1fc</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19577850</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3560,17 +3552,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785358266</t>
+          <t>1785362047</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785433500</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>39.03645</t>
+          <t>18.306636</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3587,7 +3579,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x93785b3a7d055c5e2c869f1c6ed046a0c16cd38f39a06deaefeabb59967bf72c</t>
+          <t>0x592ca05e5d2e598f37fef187e9bd4564705367d06c16f7ed3162e4659d773d8d</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3602,22 +3594,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9.5122</t>
+          <t>30.67998</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.7125</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3627,27 +3619,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x4ab76a4a1fa597ca197135de1fba0710473970c8adaef292b0acea5fe28788f8</t>
+          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3672,17 +3664,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785358055</t>
+          <t>1785362047</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>19.512205</t>
+          <t>43.059621</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3699,12 +3691,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xe9c4a1ecf56e1210003b8a7c5c9dedc347ba38e18d81ea653d600cfae0406ee7</t>
+          <t>0x57f4d612536438737c246a83cb4a06a364b2ba5f0d5bffa44b2d450c599f005c</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3714,22 +3706,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.99999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Pafos FC -1</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3739,27 +3731,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
+          <t>0x963e029345e2eec87a8efe31b92941a4225d7b0339bd00d1d2b34c4b1ef0c388</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3784,17 +3776,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785357507</t>
+          <t>1785362047</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>3.278672</t>
+          <t>25.723473</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3811,7 +3803,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x91839b38bfe01bb58e0542f3e4844d2996af26b2e1159a45b719e543c59d0061</t>
+          <t>0xa8f611211f253b096f6e8910a8e6d6614836d3fec79ca646c8cff14aa6cf4fe3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3826,22 +3818,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3851,27 +3843,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
+          <t>0x76c9ba7a74843dcbf4f3d6b5e6055a7b6d28e43c811b91c405bc0dbc814a4a23</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3896,17 +3888,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785357504</t>
+          <t>1785360745</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>18.721311</t>
+          <t>6.337662</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3923,31 +3915,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x12fa97e26b4d1fe9bc62fd353b41531c2d1e3636d5808e00f72cda223c5b7275</t>
+          <t>0xe8d3398ff301339e290daf01ae6876fd68d47e759c9d409ef00bbc858bae53d1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.7637</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xba7019cc98094442aac3dcde57fe2ab308f401a1a9e55c251da54769aa97bf2b</t>
+          <t>0x91163c750bee7db9ae12a043fe8b54facd33bd5c58dcdff2d014cdc215c90e0d</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785357342</t>
+          <t>1785358486</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>30.180033</t>
+          <t>15.023729</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4027,7 +4027,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x580c7d1b576d43e738d64f6bb0fc1b2a6d6762d7d285da29ae6814cfcd809ae2</t>
+          <t>0x6caf1354e289f361f3527f9fab48eb02c23c0756ae001e45930362caf84237dc</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4035,19 +4035,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30.79</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4055,11 +4051,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Hajduk Split</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4067,27 +4059,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>PAOK vs FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>FC Dynamo Kyiv</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xd794b506219d24bb3d154b82e776aef773d5c44cbbd3c35da4709144cfa915ea</t>
+          <t>0xd7f92bb01fc76372ae2d3dc88c6bbbc5ea9d3f1f24a2536c9608e9628c7c15a4</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577850</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4112,17 +4104,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785357285</t>
+          <t>1785358266</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785433500</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>43.715847</t>
+          <t>39.03645</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4139,7 +4131,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x001e676afb8025a177fca2fafbab0c4b0588ee71a31776ebbfe2be57ac5db06e</t>
+          <t>0x93785b3a7d055c5e2c869f1c6ed046a0c16cd38f39a06deaefeabb59967bf72c</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4154,22 +4146,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>9.5122</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4179,27 +4171,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x781f333038176cef4c0433e190179bdff06422f2827828187d4d3847de53f791</t>
+          <t>0x4ab76a4a1fa597ca197135de1fba0710473970c8adaef292b0acea5fe28788f8</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4224,17 +4216,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785352509</t>
+          <t>1785358055</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>3.585624</t>
+          <t>19.512205</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4251,12 +4243,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x9bc12eeb5e62fdab19026dd9c59a6d3d812a1647d656ec82e9b08932d05fc32a</t>
+          <t>0xe9c4a1ecf56e1210003b8a7c5c9dedc347ba38e18d81ea653d600cfae0406ee7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4266,22 +4258,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>104.66</t>
+          <t>1.99999</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4291,27 +4283,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4336,17 +4328,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785350915</t>
+          <t>1785357507</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>230.655647</t>
+          <t>3.278672</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4363,7 +4355,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x4cc9256963002abc26b03e2de5c65df247f06de8cd8caaeab5e5ab26e126b583</t>
+          <t>0x91839b38bfe01bb58e0542f3e4844d2996af26b2e1159a45b719e543c59d0061</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4378,22 +4370,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>200.71</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4403,27 +4395,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x829b110588016fc29a7bb993f85f557cd698e58d046490c5294466921214ac81</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4448,17 +4440,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785350884</t>
+          <t>1785357504</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>442.336088</t>
+          <t>18.721311</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4475,27 +4467,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x24e8cf815969b014ea0bedb7d75a94f636bc090bb24e1787d78815f3e5a70920</t>
+          <t>0x12fa97e26b4d1fe9bc62fd353b41531c2d1e3636d5808e00f72cda223c5b7275</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>222.91</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.7637</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4503,11 +4491,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4515,27 +4499,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xba7019cc98094442aac3dcde57fe2ab308f401a1a9e55c251da54769aa97bf2b</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4560,7 +4544,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785350854</t>
+          <t>1785357342</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4570,7 +4554,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>491.261708</t>
+          <t>30.180033</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4587,7 +4571,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x3729578f30b77e303f3460fb30277c2fcf85fb2049107b0dec479803d11515fe</t>
+          <t>0x580c7d1b576d43e738d64f6bb0fc1b2a6d6762d7d285da29ae6814cfcd809ae2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4602,12 +4586,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>246.56</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4617,7 +4601,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4627,27 +4611,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd794b506219d24bb3d154b82e776aef773d5c44cbbd3c35da4709144cfa915ea</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4672,7 +4656,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785350824</t>
+          <t>1785357285</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4682,7 +4666,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>543.38292</t>
+          <t>43.715847</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4699,7 +4683,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xc94c50f0e5b4951b58fe15e51011784173d7fa5dea7800432eb5745354486b80</t>
+          <t>0x001e676afb8025a177fca2fafbab0c4b0588ee71a31776ebbfe2be57ac5db06e</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4714,22 +4698,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4739,27 +4723,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x781f333038176cef4c0433e190179bdff06422f2827828187d4d3847de53f791</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4784,17 +4768,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785350560</t>
+          <t>1785352509</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>128.391304</t>
+          <t>3.585624</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4811,23 +4795,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xb98b07f3ed69cfe4b366fe2382029c20e5298a2c928a846c34e22585174d22a2</t>
+          <t>0x9bc12eeb5e62fdab19026dd9c59a6d3d812a1647d656ec82e9b08932d05fc32a</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>503.79999</t>
+          <t>104.66</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4835,7 +4823,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4888,7 +4880,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785350534</t>
+          <t>1785350915</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4898,7 +4890,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>920.18263</t>
+          <t>230.655647</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4915,23 +4907,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xab48fb1edf1fe158898059d349b71fde37cf3bd3d854ff788e8cd23ed34410e3</t>
+          <t>0x4cc9256963002abc26b03e2de5c65df247f06de8cd8caaeab5e5ab26e126b583</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1364.53</t>
+          <t>200.71</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4939,7 +4935,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785350511</t>
+          <t>1785350884</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2515.262673</t>
+          <t>442.336088</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5019,7 +5019,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x54afc83137f5b39b38053c7ac6e311ead709a66ed6180c1bd3071eec1df83367</t>
+          <t>0x24e8cf815969b014ea0bedb7d75a94f636bc090bb24e1787d78815f3e5a70920</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5034,22 +5034,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>82.98999</t>
+          <t>222.91</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.8613</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5059,27 +5059,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>FC Sheriff Tiraspol</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19578631</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5104,17 +5104,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785348315</t>
+          <t>1785350854</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>96.35993</t>
+          <t>491.261708</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5131,7 +5131,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x0dd08bf1a086493c6e680404308a2ef5ba5a320909569533d0dc8e4ad8fdea6a</t>
+          <t>0x3729578f30b77e303f3460fb30277c2fcf85fb2049107b0dec479803d11515fe</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5146,22 +5146,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>246.56</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.6925</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5171,27 +5171,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Pafos FC vs Hajduk Split</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19578535</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785347423</t>
+          <t>1785350824</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>72.750903</t>
+          <t>543.38292</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5243,12 +5243,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x993556c3cf15426b02b61df75d8fd0060a5e7634bee1409d10b85861b937670f</t>
+          <t>0xc94c50f0e5b4951b58fe15e51011784173d7fa5dea7800432eb5745354486b80</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5112</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5283,27 +5283,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785327349</t>
+          <t>1785350560</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1.95599</t>
+          <t>128.391304</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5355,28 +5355,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x4faded42a032bd6a91d4916349230f502e8759f9944cbfef78288354f9340944</t>
+          <t>0xb98b07f3ed69cfe4b366fe2382029c20e5298a2c928a846c34e22585174d22a2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5.80275</t>
+          <t>503.79999</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5387,27 +5387,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5432,17 +5432,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785325667</t>
+          <t>1785350534</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>12.120627</t>
+          <t>920.18263</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5459,28 +5459,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x39c74108b106ba600e266454471670d092342df7435c478a184f31c5880fcb1c</t>
+          <t>0xab48fb1edf1fe158898059d349b71fde37cf3bd3d854ff788e8cd23ed34410e3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>1364.53</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5491,27 +5491,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5536,17 +5536,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785325592</t>
+          <t>1785350511</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>378.067885</t>
+          <t>2515.262673</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5563,23 +5563,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x6e97ae46202c322fcc5e7c70be0be87e1574709ea5cf0024a945e7d45d548728</t>
+          <t>0x54afc83137f5b39b38053c7ac6e311ead709a66ed6180c1bd3071eec1df83367</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>179.29</t>
+          <t>82.98999</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4763</t>
+          <t>1.8613</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5587,7 +5591,11 @@
           <t>Europa League</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5595,27 +5603,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>Maccabi Tel Aviv vs FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>FC Sheriff Tiraspol</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0xc8c2a97756aef3ba71a257ad35225c415ec16d6f7c11d5e10fd309b54c904a5c</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19578631</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5640,17 +5648,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785325549</t>
+          <t>1785348315</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>376.461942</t>
+          <t>96.35993</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5667,23 +5675,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x36f17b5f896b8f5c9301b3600be88ac0007d3ce06403ffe9b13d7389417fa953</t>
+          <t>0x0dd08bf1a086493c6e680404308a2ef5ba5a320909569533d0dc8e4ad8fdea6a</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4775</t>
+          <t>1.6925</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5691,7 +5703,11 @@
           <t>Europa League</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pafos FC</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5699,27 +5715,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>Pafos FC vs Hajduk Split</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0x8bb7d7494ad901f464d6f8ec8714fb45401d79319dba96f7e9851848918ccf28</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19578535</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5744,17 +5760,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785325496</t>
+          <t>1785347423</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>379.057592</t>
+          <t>72.750903</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5771,31 +5787,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xf2a45c2970e6d3af37fabd0ad34ce6efeecfe1f77cb4d5f43515fb342f7fcca2</t>
+          <t>0x993556c3cf15426b02b61df75d8fd0060a5e7634bee1409d10b85861b937670f</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -5803,27 +5827,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia vs Qarabag</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>PFC CSKA Sofia</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19576890</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5848,17 +5872,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785325423</t>
+          <t>1785327349</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1785434400</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>378.067885</t>
+          <t>1.95599</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5875,23 +5899,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xdd031e5f334a60c24ea47a7a807f20a2bead2b80c0227808f5afa24fa77a3d06</t>
+          <t>0x4faded42a032bd6a91d4916349230f502e8759f9944cbfef78288354f9340944</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>5.80275</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5922,7 +5946,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5952,7 +5976,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785325348</t>
+          <t>1785325667</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5962,7 +5986,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>394.805195</t>
+          <t>12.120627</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5979,7 +6003,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x4c7bd245dd4665e7f9285a58768875e4fa752d61dfc244e87f7283d2907dcb15</t>
+          <t>0x39c74108b106ba600e266454471670d092342df7435c478a184f31c5880fcb1c</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5990,12 +6014,12 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4775</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6056,7 +6080,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785325203</t>
+          <t>1785325592</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6066,7 +6090,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>383.246073</t>
+          <t>378.067885</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6083,23 +6107,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x13f73d60f1f96dd112ac2a53fa2a1a53f2e55f9bc0782a0d92732337ef7e7519</t>
+          <t>0x6e97ae46202c322fcc5e7c70be0be87e1574709ea5cf0024a945e7d45d548728</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>179.29</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.4763</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6160,7 +6184,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785325120</t>
+          <t>1785325549</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6170,7 +6194,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>166.287263</t>
+          <t>376.461942</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6187,39 +6211,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xd5759db5ffa02ee1c17bc11bdfbffb2bb73c6ff16a4fa6bf670dafa016fad84a</t>
+          <t>0x36f17b5f896b8f5c9301b3600be88ac0007d3ce06403ffe9b13d7389417fa953</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6227,27 +6243,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6272,17 +6288,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785319802</t>
+          <t>1785325496</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>21.949861</t>
+          <t>379.057592</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6299,39 +6315,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x0fc529171c6c4f0c441f19435054a73905e5f2d2ed326778ddb79cd108c6ede1</t>
+          <t>0xf2a45c2970e6d3af37fabd0ad34ce6efeecfe1f77cb4d5f43515fb342f7fcca2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6339,27 +6347,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xec30d6ed85c3851d5938108fae681432d7a35f2c741191462472aaa11d35b165</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6384,17 +6392,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785317013</t>
+          <t>1785325423</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>7.929825</t>
+          <t>378.067885</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6411,39 +6419,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x2d47f0e85c65fcb84f5de7818b5845226e8638c4dc49fb9093b9a86fe895116b</t>
+          <t>0xdd031e5f334a60c24ea47a7a807f20a2bead2b80c0227808f5afa24fa77a3d06</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD9f8C3ddc681f06E786f2E17de46753B248C5E9e</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>11.26</t>
+          <t>190</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6451,27 +6451,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6496,17 +6496,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785316734</t>
+          <t>1785325348</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>20.38009</t>
+          <t>394.805195</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6523,39 +6523,31 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xe8fb252bc279aab31e6c6f4de96e27aca4bae9402699e12add62fecf7cc6090d</t>
+          <t>0x4c7bd245dd4665e7f9285a58768875e4fa752d61dfc244e87f7283d2907dcb15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>183</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6563,27 +6555,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs Hammarby IF</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
+          <t>0x4bb0081218c62b504bd2ce1b17054b0c598f7a0172d20fe84a9f352136f99368</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19577223</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6608,17 +6600,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785314887</t>
+          <t>1785325203</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>14.280543</t>
+          <t>383.246073</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6635,39 +6627,31 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x988d12bce5f972af9ca3a2a7a91ba784d379a454873fb5ad9267f635cfeabaae</t>
+          <t>0x13f73d60f1f96dd112ac2a53fa2a1a53f2e55f9bc0782a0d92732337ef7e7519</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>122.7</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -6675,27 +6659,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>PFC CSKA Sofia vs Qarabag</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>PFC CSKA Sofia</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x042b2167cfc32f6748075e813136d07bc7bc6b4c2d5db1ccd0f14ab7a26df0a9</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19576890</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6720,17 +6704,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785314533</t>
+          <t>1785325120</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785434400</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>273.426184</t>
+          <t>166.287263</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6747,12 +6731,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x78d34863dc5be51d39c855d3868e1af787b7281b3a9ba704567d82456b113d15</t>
+          <t>0xd5759db5ffa02ee1c17bc11bdfbffb2bb73c6ff16a4fa6bf670dafa016fad84a</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6762,7 +6746,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>178.48</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6832,7 +6816,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785313946</t>
+          <t>1785319802</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6842,7 +6826,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>397.727019</t>
+          <t>21.949861</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6859,12 +6843,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x5106f8b58142e7b5c50eb3e00b44385652098e82742605b478cd59c2271a33a0</t>
+          <t>0x0fc529171c6c4f0c441f19435054a73905e5f2d2ed326778ddb79cd108c6ede1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
+          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6874,12 +6858,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6889,32 +6873,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>Tromso</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove vs Tromso</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xec30d6ed85c3851d5938108fae681432d7a35f2c741191462472aaa11d35b165</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6944,7 +6928,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785313924</t>
+          <t>1785317013</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6954,7 +6938,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>668.523677</t>
+          <t>7.929825</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6971,12 +6955,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x6e2b82838c81a4891a03953f0ebaca7a027f4125fe2deaed52b0a95c44206dab</t>
+          <t>0x2d47f0e85c65fcb84f5de7818b5845226e8638c4dc49fb9093b9a86fe895116b</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6986,22 +6970,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7011,27 +6995,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -7056,17 +7040,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785313712</t>
+          <t>1785316734</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>311.977716</t>
+          <t>20.38009</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7083,18 +7067,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x6a19a9357d731588796a01e05f4e8808a84076b6662f83356dcf6c6b00474e65</t>
+          <t>0xe8fb252bc279aab31e6c6f4de96e27aca4bae9402699e12add62fecf7cc6090d</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7104,10 +7092,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7115,27 +7107,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>RSC Anderlecht vs Hammarby IF</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0xd2eec2b8df5b902470bd02284bc3e660c9cc5eff74f371ef555934c71ab27eb0</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577223</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7160,17 +7152,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785313623</t>
+          <t>1785314887</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>240.723982</t>
+          <t>14.280543</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7187,12 +7179,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x6484f0585336dfe74c291be479560bddc0741e80877c77ec5ca7fcb16d4374a5</t>
+          <t>0x988d12bce5f972af9ca3a2a7a91ba784d379a454873fb5ad9267f635cfeabaae</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
+          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7202,7 +7194,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>48.19</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7272,7 +7264,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785313622</t>
+          <t>1785314533</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7282,7 +7274,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>107.387187</t>
+          <t>273.426184</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7299,12 +7291,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x6906ce6d1047273d710579bf3d98367dbf415d0e24ecb41a8a528337a9506d3a</t>
+          <t>0x78d34863dc5be51d39c855d3868e1af787b7281b3a9ba704567d82456b113d15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7314,7 +7306,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>178.48</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7384,7 +7376,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785313432</t>
+          <t>1785313946</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7394,7 +7386,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>12.612813</t>
+          <t>397.727019</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7411,12 +7403,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x2c365a540f836041b72448aca3516556411b341658244ff388c1692fa15d2af0</t>
+          <t>0x5106f8b58142e7b5c50eb3e00b44385652098e82742605b478cd59c2271a33a0</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7426,7 +7418,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7496,7 +7488,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785313327</t>
+          <t>1785313924</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7506,7 +7498,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>20.43454</t>
+          <t>668.523677</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7523,12 +7515,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xe917c05092f572e2e95fee59d14b544fb6d4c549a9e9e7399b744a830680c0ef</t>
+          <t>0x6e2b82838c81a4891a03953f0ebaca7a027f4125fe2deaed52b0a95c44206dab</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xd22BD9e1B7916fFE0ad765642788c86b6aa29075</t>
+          <t>0x797D61eBb38D3cb93d3a52fEA6c34e409de079ee</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7538,12 +7530,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7608,7 +7600,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785313211</t>
+          <t>1785313712</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7618,7 +7610,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>13.894737</t>
+          <t>311.977716</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7635,27 +7627,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x8d92cbf4088d40c4b2b67cbb02c218ebad12e894eda090162e17c4b4ec2423ec</t>
+          <t>0x6a19a9357d731588796a01e05f4e8808a84076b6662f83356dcf6c6b00474e65</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7663,31 +7651,27 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>Tromso</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Europa League_UEFA</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove vs Tromso</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>FC Hradec Kralove</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Tromso</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
@@ -7720,7 +7704,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785313190</t>
+          <t>1785313623</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7730,7 +7714,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>11.390582</t>
+          <t>240.723982</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7747,12 +7731,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x4858e2eb7b8bfa0a43a468cd0f4c8c41ecc4c6f3ede73f30251c7922e1a658eb</t>
+          <t>0x6484f0585336dfe74c291be479560bddc0741e80877c77ec5ca7fcb16d4374a5</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x23aBD2f3084d276F0a861398dE3899D01894B83F</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7762,12 +7746,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7832,7 +7816,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785313173</t>
+          <t>1785313622</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7842,7 +7826,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>20.387812</t>
+          <t>107.387187</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7859,23 +7843,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xf0b6c79ec7c1905e25f5ff4b6433e8122df6bb18a211b77a66cc1962804b95cb</t>
+          <t>0x6906ce6d1047273d710579bf3d98367dbf415d0e24ecb41a8a528337a9506d3a</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>56.13118</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7883,7 +7871,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7936,7 +7928,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785313133</t>
+          <t>1785313432</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7946,7 +7938,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>102.992991</t>
+          <t>12.612813</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7963,23 +7955,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
+          <t>0x2c365a540f836041b72448aca3516556411b341658244ff388c1692fa15d2af0</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7987,7 +7983,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -7995,27 +7995,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785282599</t>
+          <t>1785313327</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>101.012788</t>
+          <t>20.43454</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8067,23 +8067,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
+          <t>0xe917c05092f572e2e95fee59d14b544fb6d4c549a9e9e7399b744a830680c0ef</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>0xd22BD9e1B7916fFE0ad765642788c86b6aa29075</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8091,7 +8095,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -8144,7 +8152,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785282154</t>
+          <t>1785313211</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8154,7 +8162,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>9.181132</t>
+          <t>13.894737</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8171,23 +8179,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
+          <t>0x8d92cbf4088d40c4b2b67cbb02c218ebad12e894eda090162e17c4b4ec2423ec</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8195,7 +8207,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -8248,7 +8264,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785281829</t>
+          <t>1785313190</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8258,7 +8274,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>9.181132</t>
+          <t>11.390582</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8275,31 +8291,39 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
+          <t>0x4858e2eb7b8bfa0a43a468cd0f4c8c41ecc4c6f3ede73f30251c7922e1a658eb</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>4.7855</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.4512</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -8307,27 +8331,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8352,17 +8376,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785267733</t>
+          <t>1785313173</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>14.446792</t>
+          <t>20.387812</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8379,28 +8403,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
+          <t>0xf0b6c79ec7c1905e25f5ff4b6433e8122df6bb18a211b77a66cc1962804b95cb</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0x06a093a3A59Ea8C48045fA50224c6c6700bcF052</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4.8535</t>
+          <t>56.13118</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.545</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -8411,27 +8435,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8456,17 +8480,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785265830</t>
+          <t>1785313133</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>14.327675</t>
+          <t>102.992991</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8483,39 +8507,31 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
+          <t>0x323fe088b6623b1b9ec23c8eeba70c607482fc7be3b04653f9e5fab908942fb4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>SL Benfica FC -3</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -8523,27 +8539,27 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -8568,17 +8584,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785261286</t>
+          <t>1785282599</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>101.012788</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8595,23 +8611,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
+          <t>0x64bdf59a5762a396152ddc4c45c813ca4ead71c5d536b463ec8dc2b39b60c06b</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8672,7 +8688,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785258767</t>
+          <t>1785282154</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8682,7 +8698,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>15.179487</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8699,28 +8715,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
+          <t>0x5d88c9bf55f74048f6a69933e3eef4727b34b90ee35d37de3bb9a05476b96c4e</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>4.866</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.3425</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -8731,27 +8747,27 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -8776,17 +8792,17 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785253987</t>
+          <t>1785281829</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>15.737226</t>
+          <t>9.181132</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8803,39 +8819,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
+          <t>0xd2cceb1fd8e75ebd5064f75ca1a02dbaa217edb663ccc3c68bb03698365f7212</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>142.02999</t>
+          <t>4.7855</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.6663</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -8843,27 +8851,27 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8888,17 +8896,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785232812</t>
+          <t>1785267733</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>213.178221</t>
+          <t>14.446792</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8915,39 +8923,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
+          <t>0xced247f7493ba9f2ded65c1d0cec7bceeb1b4e0499882beb63f974877d173278</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>193.23</t>
+          <t>4.8535</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -8955,27 +8955,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -9000,17 +9000,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785231712</t>
+          <t>1785265830</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>285.737523</t>
+          <t>14.327675</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9027,31 +9027,39 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
+          <t>0xe279d56fae01030bc6102e6c91875e30fab4ca74352b803e5e251f8b7e94548a</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>SL Benfica FC -3</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -9059,27 +9067,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x8adbd6bb9e9ad87c919886cb7960701cf57a7698ed3578b8d28dd47131960ee8</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -9104,17 +9112,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785227020</t>
+          <t>1785261286</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>20.185185</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9131,39 +9139,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
+          <t>0x14c922071a5ab6fbbb08da1e605611359068181ba3df6ee811e1b0d7fa29d896</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>104.47</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -9171,27 +9171,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785224116</t>
+          <t>1785258767</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>155.925373</t>
+          <t>15.179487</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9243,39 +9243,31 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
+          <t>0x9e9aa5c67caefa7b6245f5765d40e430f611a0f6e43fdc57fd933b7fcbacc156</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Europa League</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>FC Midtjylland</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -9283,27 +9275,27 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
+          <t>0x2767b479f8b8acc38966c52e52e206d4141508d19d1c7fe6e048023fd39e34e6</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -9328,17 +9320,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785223916</t>
+          <t>1785253987</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>144.089552</t>
+          <t>15.737226</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9355,31 +9347,39 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
+          <t>0x5b9af63c5725778fa8715fec08b7397c09f53eb358b72546a56bc49a09ede5cc</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>70.47999</t>
+          <t>142.02999</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.6663</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -9387,27 +9387,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785220497</t>
+          <t>1785232812</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>133.295489</t>
+          <t>213.178221</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9459,12 +9459,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
+          <t>0x6c09e3e7210d83a76913ce501fe47cdeb56af423b366465eced54e7fe5c928c8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9474,22 +9474,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>193.23</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9499,27 +9499,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9544,17 +9544,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785218406</t>
+          <t>1785231712</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>285.737523</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9571,28 +9571,28 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
+          <t>0x48ac55426f694bdf3a16cabad44e789e8abb89d3984db5a3e886a222372d0145</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x73744622d71843A17e7CE3b9b0241AC776baC5bD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>85.47</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -9603,27 +9603,27 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785213181</t>
+          <t>1785227020</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>254.185874</t>
+          <t>20.185185</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9675,31 +9675,39 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
+          <t>0x885c406b02670b86a148e689b9938d8e785e5704f28af70303bb3aef7f6c7b82</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>104.47</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -9707,27 +9715,27 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -9752,7 +9760,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785189317</t>
+          <t>1785224116</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9762,7 +9770,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>155.925373</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9779,31 +9787,39 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
+          <t>0xa9086b2a7ec89ecd1c6174888e0f5bc803e9c0bc8a10ac6884f1784dae54a2a2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -9811,27 +9827,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
+          <t>0x4a55a2f0090a43830b1ad6efc04e3bf7a84f7e0aa2bcd1a80d7d51910165541a</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9856,7 +9872,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785188885</t>
+          <t>1785223916</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9866,7 +9882,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>9.144731</t>
+          <t>144.089552</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9883,27 +9899,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
+          <t>0x33629072d294c777753d4f0901c1a103d9a8351673ecfc006ec713710c194429</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3Bd04051C13fcC95955fBA999a81b549DC1AaD6D</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>70.47999</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -9911,11 +9923,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -9923,27 +9931,27 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9968,17 +9976,17 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785186773</t>
+          <t>1785220497</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>133.295489</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9995,7 +10003,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
+          <t>0xca988989ba0a99335f19af5ab577f6640bf20ceaa254429962c758daa3ff0c0c</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10080,7 +10088,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785186621</t>
+          <t>1785218406</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10107,7 +10115,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
+          <t>0x4afd29fa21cf73928533235449b4ada4ed33982b7d01229bef2dcf99368da4ca</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10115,31 +10123,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>85.47</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -10147,27 +10147,27 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Midtjylland vs Besiktas</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0x158b3cb30055ece93c8939659bae73b26e24f9856d9863a174210fcbbd5c7593</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577560</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -10192,17 +10192,17 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785186464</t>
+          <t>1785213181</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>254.185874</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10219,27 +10219,23 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
+          <t>0x9eb4b01eefa201544b1ccdb4c5c6604e0714ac629344d4d2b7b17cc1464fb5c7</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10247,11 +10243,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -10259,27 +10251,27 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -10304,17 +10296,17 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785186313</t>
+          <t>1785189317</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10331,27 +10323,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
+          <t>0x72247e16c302aa1a252495938a15e1d60e4b267830f4978c0b1e53c944fe7833</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFbF8d0BCccedDdAc69C0DC38823fE24842afa03C</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>4.881</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -10359,11 +10347,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -10371,27 +10355,27 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Ferencvaros vs FC Twente</t>
+          <t>FC Hradec Kralove vs Tromso</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>FC Hradec Kralove</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
+          <t>0xc43fb7b2993be2553cb93dc8bab291577c90b4aa7ac359f3b83149bfa631bb40</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>L19578664</t>
+          <t>L19577176</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -10416,17 +10400,17 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785185868</t>
+          <t>1785188885</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>9.144731</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10443,31 +10427,39 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
+          <t>0x605d65f217cfad8dba3fc5fc8ba81f33c522bb6d2702ab1896e28f2a043e7284</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -10490,7 +10482,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10520,7 +10512,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1785182082</t>
+          <t>1785186773</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10530,7 +10522,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>101.408451</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10547,12 +10539,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
+          <t>0x31389f85488fa9e54013f64ac333a2b550d2412b8db664b843e4ce83e7ac4987</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10562,22 +10554,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>98.9699</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.9187</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -10587,27 +10579,27 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs FC St. Gallen</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>FC St. Gallen</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>L19577588</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -10632,17 +10624,17 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785178276</t>
+          <t>1785186621</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>1785438000</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>107.72234</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10659,7 +10651,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+          <t>0xfb23cf678aafc207af69fb8dfa1e83d0a06b41177f42b72e0eb9221a27e820ba</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10667,15 +10659,19 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10683,7 +10679,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -10691,27 +10691,27 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -10736,12 +10736,12 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1785157337</t>
+          <t>1785186464</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
@@ -10763,12 +10763,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+          <t>0x3138a3ad46ea4c79099bef4064759debf254c0f7929452594d354137a19e0673</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10778,12 +10778,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10803,27 +10803,27 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -10848,17 +10848,17 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1785154148</t>
+          <t>1785186313</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10875,12 +10875,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+          <t>0x2f2706b1ff85c18b198514da422a74b19942ac8b11089fe8ede6b98b57fcd6fd</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2.36789</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10915,27 +10915,27 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0xe84ac6325784d17111f3c60f2ba80ccbf3ba57796f09390d50991fbef4aa01e7</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -10960,17 +10960,17 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785185868</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>9.866208</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10987,39 +10987,31 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+          <t>0x75d4a8cc9d03da588fcd6106f912b7eb69342da973970aa5144a52fd652df720</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8b3809dd81A411A1CcC110e23281D3861E41D439</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Besiktas</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
@@ -11027,27 +11019,27 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Besiktas</t>
+          <t>Ferencvaros vs FC Twente</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>FC Midtjylland</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+          <t>0x31485d66881ea25fc18ee05567734ae7ae66fb87f6fcca8575303fab366000be</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>L19577560</t>
+          <t>L19578664</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -11072,17 +11064,17 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1785153790</t>
+          <t>1785182082</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>5.041667</t>
+          <t>101.408451</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -11099,12 +11091,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+          <t>0xd994586c2c89af6ad574d50a0f8c8700e90e7f22d20bf49a633feaa989af50bf</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -11114,12 +11106,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>65.95</t>
+          <t>98.9699</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.9187</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -11129,7 +11121,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -11139,27 +11131,27 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove vs Tromso</t>
+          <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>FC Hradec Kralove</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>FC St. Gallen</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+          <t>0xf1cfaffefafaf6e63eaa25f347bda991a38fb6aa57e14fa84b386fed55a3f99b</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>L19577176</t>
+          <t>L19577588</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -11184,17 +11176,17 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1785131538</t>
+          <t>1785178276</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>177.643098</t>
+          <t>107.72234</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11211,110 +11203,662 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>0xcfc2858bc694fbf8557c05f8f7fd20f59fd4990088d7f08f96947050324a2e61</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>0xda06ff264d51913dfda755a8c4a477b88663ff22d289eb6f556018e55bf68d04</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>1785157337</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0x6d9c715f878347d23b5132d44c3d76e250960d8a888670fe9b446ebcef8c5cef</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>1785154148</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0xc10cd30f1ad9ff73882f16291a9858024418214eb562a5dbbad80c0ecae1c52f</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2.36789</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>9.866208</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>0x72c1b3c5fcfde9fcf9031572e4700cad5504a7350908921543fd656f10cf9747</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Besiktas</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>0xd45cdb893a2b175b1fae5101e51318244d81038ac8cdd664f9d6b1c4b589d532</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>L19577560</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>1785153790</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>5.041667</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>0xfe31a156d44f9e3b282c8377721b24b01c0625a47209ef8f421fc350af3dac0f</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>65.95</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1.3713</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Europa League</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Europa League_UEFA</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove vs Tromso</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>0x0d9f7cd21696b245b975157ec565ba91ba0db43a168fd64ff0caebbbec205950</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>L19577176</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>1785131538</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>1785430800</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>177.643098</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>0x4a21e608f2a49d0d290d56e481810827c36c3a33b3cdfa52f47a9d205c9195a6</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>1.1213</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>Europa League_UEFA</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>SL Benfica FC vs FC St. Gallen</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>SL Benfica FC</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>FC St. Gallen</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t>0xfc195ce6529fc46edc42b440639cd20958bc0e5f58d88c7925cdd8563a01ebd2</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t>L19577588</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr">
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
         <is>
           <t>1785123830</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
+      <c r="S105" t="inlineStr">
         <is>
           <t>1785438000</t>
         </is>
       </c>
-      <c r="T100" t="inlineStr">
+      <c r="T105" t="inlineStr">
         <is>
           <t>65.979381</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="U105" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
+      <c r="V105" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
